--- a/test/BugReports.xlsx
+++ b/test/BugReports.xlsx
@@ -1,17 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\9Months\QA\Project\QA-project-tool\QA-project-tool\test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDC381B-6236-4124-B048-600B7C748DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Bug Reports" sheetId="1" r:id="rId5"/>
+    <sheet name="Bug Reports" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="5">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="5">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <si>
     <t>Defect_ID</t>
   </si>
@@ -62,70 +138,250 @@
   </si>
   <si>
     <t>Created by</t>
+  </si>
+  <si>
+    <t>BUG-PD-01</t>
+  </si>
+  <si>
+    <t>Full Name accepts less than 3 characters</t>
+  </si>
+  <si>
+    <t>User on Passenger Details page</t>
+  </si>
+  <si>
+    <t>Name = “ab”</t>
+  </si>
+  <si>
+    <t>1- Enter “ab” in Full Name field 2- Submit form</t>
+  </si>
+  <si>
+    <t>Error message should appear for invalid minimum length</t>
+  </si>
+  <si>
+    <t>System accepts name with less than 3 characters without validation message</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>TC-PassangerDetails-07</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>PD-09</t>
+  </si>
+  <si>
+    <t>Abdelrahman Khaled</t>
+  </si>
+  <si>
+    <t>BUG-PD-02</t>
+  </si>
+  <si>
+    <t>Full Name accepts more than 30 characters</t>
+  </si>
+  <si>
+    <t>Name &gt; 30 chars</t>
+  </si>
+  <si>
+    <t>1- Enter long name exceeding 30 chars 2- Submit form</t>
+  </si>
+  <si>
+    <t>Error message should appear for invalid maximum length</t>
+  </si>
+  <si>
+    <t>System accepts name longer than allowed limit</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC-PassangerDetails-08</t>
+  </si>
+  <si>
+    <t>BUG-PD-03</t>
+  </si>
+  <si>
+    <t>Date of Birth field accepts future dates</t>
+  </si>
+  <si>
+    <t>Future DOB</t>
+  </si>
+  <si>
+    <t>1- Enter future date in DOB field 2- Submit form</t>
+  </si>
+  <si>
+    <t>Error message should appear preventing future DOB</t>
+  </si>
+  <si>
+    <t>System accepts future date without validation</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>TC-PassangerDetails-11</t>
+  </si>
+  <si>
+    <t>PD-12</t>
+  </si>
+  <si>
+    <t>BUG-UM-01</t>
+  </si>
+  <si>
+    <t>Existing multi-page users</t>
+  </si>
+  <si>
+    <t>1- Open User Management page 2- Navigate between pages</t>
+  </si>
+  <si>
+    <t>User list should update correctly per page</t>
+  </si>
+  <si>
+    <t>TC-UserManagement-02</t>
+  </si>
+  <si>
+    <t>UM-03</t>
+  </si>
+  <si>
+    <t>BUG-BH-01</t>
+  </si>
+  <si>
+    <t>Existing bookings</t>
+  </si>
+  <si>
+    <t>1- Open Booking History page 2- Navigate pages</t>
+  </si>
+  <si>
+    <t>Booking list should update correctly for each page</t>
+  </si>
+  <si>
+    <t>Booking list does not refresh correctly during pagination</t>
+  </si>
+  <si>
+    <t>TC-BookingHistory-02</t>
+  </si>
+  <si>
+    <t>BH-03</t>
+  </si>
+  <si>
+    <t>Admin in user management page</t>
+  </si>
+  <si>
+    <t>Pagination buttons do not appear</t>
+  </si>
+  <si>
+    <t>Pagination is not functioning on the User Management page</t>
+  </si>
+  <si>
+    <t>Pagination is not functioning on the Booking History page</t>
+  </si>
+  <si>
+    <t>Admin in bookin history page</t>
+  </si>
+  <si>
+    <t>BUG-PAY-01</t>
+  </si>
+  <si>
+    <t>User on Payment page</t>
+  </si>
+  <si>
+    <t>Valid payment data</t>
+  </si>
+  <si>
+    <t>1- Enter valid card details 2- Click Pay &amp; Confirm</t>
+  </si>
+  <si>
+    <t>Payment should process successfully</t>
+  </si>
+  <si>
+    <t>Payment process fails or no success confirmation displayed</t>
+  </si>
+  <si>
+    <t>TC-Payment-01</t>
+  </si>
+  <si>
+    <t>PAY-01</t>
+  </si>
+  <si>
+    <t>Cardholder Name field is missing on Payment page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF4A86E8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -136,7 +392,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -188,7 +444,13 @@
     </fill>
   </fills>
   <borders count="4">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -202,6 +464,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -216,6 +479,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -230,354 +494,140 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="52">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>847725</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3400425" cy="3438525"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4924425" cy="2438400"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="صورة"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1000125</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4772025" cy="2733675"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.png" title="صورة"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1657350</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4619625" cy="1390650"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.png" title="صورة"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3952875</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3552825</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3714750" cy="3067050"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1495425</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4733925" cy="1609725"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="صورة"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3952875</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>3400425</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3819525" cy="3267075"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -588,11 +638,17 @@
     <xdr:ext cx="3762375" cy="1390650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="9" name="image2.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -616,11 +672,17 @@
     <xdr:ext cx="1323975" cy="2619375"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="10" name="image4.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -644,11 +706,17 @@
     <xdr:ext cx="2981325" cy="3267075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="صورة"/>
+        <xdr:cNvPr id="11" name="image3.png" title="صورة">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -672,11 +740,17 @@
     <xdr:ext cx="5286375" cy="2209800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
+        <xdr:cNvPr id="12" name="image7.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -700,11 +774,17 @@
     <xdr:ext cx="2914650" cy="1495425"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png" title="Image"/>
+        <xdr:cNvPr id="13" name="image8.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -728,11 +808,17 @@
     <xdr:ext cx="4295775" cy="1009650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.png" title="Image"/>
+        <xdr:cNvPr id="14" name="image11.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -749,12 +835,92 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -944,32 +1110,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AE912"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.13"/>
-    <col customWidth="1" min="2" max="2" width="84.13"/>
-    <col customWidth="1" min="3" max="3" width="68.0"/>
-    <col customWidth="1" min="4" max="4" width="34.25"/>
-    <col customWidth="1" min="5" max="5" width="58.38"/>
-    <col customWidth="1" min="6" max="6" width="116.63"/>
-    <col customWidth="1" min="7" max="7" width="51.88"/>
-    <col customWidth="1" min="8" max="8" width="68.75"/>
-    <col customWidth="1" min="12" max="13" width="21.25"/>
-    <col customWidth="1" min="14" max="14" width="54.63"/>
-    <col customWidth="1" min="15" max="15" width="21.75"/>
-    <col customWidth="1" min="16" max="17" width="95.88"/>
-    <col customWidth="1" min="18" max="18" width="23.38"/>
+    <col min="1" max="1" width="35.85546875" customWidth="1"/>
+    <col min="2" max="2" width="84.140625" customWidth="1"/>
+    <col min="3" max="3" width="68" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" customWidth="1"/>
+    <col min="6" max="6" width="116.5703125" customWidth="1"/>
+    <col min="7" max="7" width="51.85546875" customWidth="1"/>
+    <col min="8" max="8" width="68.7109375" customWidth="1"/>
+    <col min="12" max="13" width="21.28515625" customWidth="1"/>
+    <col min="14" max="14" width="54.5703125" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" customWidth="1"/>
+    <col min="16" max="17" width="95.85546875" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,13 +1184,13 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
@@ -1031,24 +1200,56 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
+    <row r="2" spans="1:31" ht="167.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="50" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1064,24 +1265,56 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
     </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
+    <row r="3" spans="1:31" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="50" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -1097,24 +1330,56 @@
       <c r="AD3" s="6"/>
       <c r="AE3" s="6"/>
     </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
+    <row r="4" spans="1:31" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="50" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
@@ -1130,53 +1395,121 @@
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="4"/>
+    <row r="5" spans="1:31" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="50" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I5" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
+      <c r="AC5" s="22"/>
+      <c r="AD5" s="22"/>
+      <c r="AE5" s="22"/>
+    </row>
+    <row r="6" spans="1:31" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="50" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I6" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
@@ -1192,24 +1525,56 @@
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
     </row>
-    <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+    <row r="7" spans="1:31" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="50" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -1225,7 +1590,7 @@
       <c r="AD7" s="6"/>
       <c r="AE7" s="6"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1258,7 +1623,7 @@
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1291,7 +1656,7 @@
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1324,7 +1689,7 @@
       <c r="AD10" s="6"/>
       <c r="AE10" s="6"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1357,7 +1722,7 @@
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1390,7 +1755,7 @@
       <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1423,7 +1788,7 @@
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1438,31 +1803,31 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="7"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:31" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1495,7 +1860,7 @@
       <c r="AD23" s="11"/>
       <c r="AE23" s="11"/>
     </row>
-    <row r="24" ht="231.75" customHeight="1">
+    <row r="24" spans="1:31" ht="231.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="13"/>
       <c r="C24" s="12"/>
@@ -1515,7 +1880,7 @@
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" ht="165.0" customHeight="1">
+    <row r="25" spans="1:31" ht="165" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="12"/>
@@ -1535,82 +1900,82 @@
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -1643,20 +2008,20 @@
       <c r="AD51" s="16"/>
       <c r="AE51" s="16"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B53" s="17"/>
       <c r="O53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B54" s="17"/>
       <c r="O54" s="9"/>
       <c r="P54" s="17"/>
       <c r="Q54" s="17"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="18"/>
       <c r="B55" s="19"/>
       <c r="C55" s="18"/>
@@ -1689,7 +2054,7 @@
       <c r="AD55" s="20"/>
       <c r="AE55" s="20"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -1722,7 +2087,7 @@
       <c r="AD56" s="16"/>
       <c r="AE56" s="16"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -1755,7 +2120,7 @@
       <c r="AD57" s="21"/>
       <c r="AE57" s="21"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -1788,13 +2153,13 @@
       <c r="AD58" s="21"/>
       <c r="AE58" s="21"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O60" s="9"/>
     </row>
-    <row r="61" ht="24.0" customHeight="1">
+    <row r="61" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
       <c r="B61" s="24"/>
       <c r="C61" s="24"/>
@@ -1827,7 +2192,7 @@
       <c r="AD61" s="24"/>
       <c r="AE61" s="24"/>
     </row>
-    <row r="62" ht="31.5" customHeight="1">
+    <row r="62" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="25"/>
       <c r="B62" s="26"/>
       <c r="C62" s="26"/>
@@ -1860,7 +2225,7 @@
       <c r="AD62" s="24"/>
       <c r="AE62" s="24"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -1879,7 +2244,7 @@
       <c r="AD63" s="30"/>
       <c r="AE63" s="30"/>
     </row>
-    <row r="64" ht="375.0" customHeight="1">
+    <row r="64" spans="1:31" ht="375" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -1897,10 +2262,10 @@
       <c r="Q64" s="29"/>
       <c r="R64" s="4"/>
     </row>
-    <row r="65" ht="54.0" customHeight="1">
+    <row r="65" spans="1:31" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -1933,56 +2298,56 @@
       <c r="AD66" s="11"/>
       <c r="AE66" s="11"/>
     </row>
-    <row r="67" ht="75.0" customHeight="1">
+    <row r="67" spans="1:31" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="17"/>
       <c r="E67" s="4"/>
       <c r="G67" s="17"/>
       <c r="H67" s="8"/>
       <c r="O67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B68" s="17"/>
       <c r="E68" s="4"/>
       <c r="G68" s="17"/>
       <c r="H68" s="8"/>
       <c r="O68" s="9"/>
     </row>
-    <row r="69" ht="182.25" customHeight="1">
+    <row r="69" spans="1:31" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="17"/>
       <c r="E69" s="4"/>
       <c r="G69" s="17"/>
       <c r="H69" s="8"/>
       <c r="O69" s="9"/>
     </row>
-    <row r="70" ht="189.75" customHeight="1">
+    <row r="70" spans="1:31" ht="189.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="17"/>
       <c r="E70" s="4"/>
       <c r="G70" s="17"/>
       <c r="H70" s="8"/>
       <c r="O70" s="9"/>
     </row>
-    <row r="71" ht="162.0" customHeight="1">
+    <row r="71" spans="1:31" ht="162" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="17"/>
       <c r="E71" s="4"/>
       <c r="G71" s="17"/>
       <c r="H71" s="7"/>
       <c r="O71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B72" s="17"/>
       <c r="E72" s="4"/>
       <c r="G72" s="17"/>
       <c r="H72" s="8"/>
       <c r="O72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B73" s="17"/>
       <c r="E73" s="4"/>
       <c r="G73" s="17"/>
       <c r="H73" s="8"/>
       <c r="O73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2010,7 +2375,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B75" s="17"/>
       <c r="C75" s="31"/>
       <c r="E75" s="29"/>
@@ -2018,7 +2383,7 @@
       <c r="M75" s="5"/>
       <c r="O75" s="9"/>
     </row>
-    <row r="76" ht="122.25" customHeight="1">
+    <row r="76" spans="1:31" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="32"/>
       <c r="C76" s="31"/>
       <c r="E76" s="29"/>
@@ -2026,7 +2391,7 @@
       <c r="M76" s="5"/>
       <c r="O76" s="9"/>
     </row>
-    <row r="77" ht="90.75" customHeight="1">
+    <row r="77" spans="1:31" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="33"/>
       <c r="C77" s="31"/>
       <c r="E77" s="29"/>
@@ -2034,25 +2399,25 @@
       <c r="M77" s="5"/>
       <c r="O77" s="9"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O79" s="9"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O80" s="9"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O81" s="9"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O82" s="9"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O83" s="9"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O84" s="9"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="34"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -2085,101 +2450,101 @@
       <c r="AD85" s="35"/>
       <c r="AE85" s="35"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="G86" s="17"/>
       <c r="O86" s="9"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O87" s="9"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O88" s="9"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O89" s="9"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O90" s="9"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O91" s="9"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O92" s="9"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O93" s="9"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O94" s="9"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O95" s="9"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O96" s="9"/>
     </row>
-    <row r="97">
+    <row r="97" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O97" s="9"/>
     </row>
-    <row r="98">
+    <row r="98" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O98" s="9"/>
     </row>
-    <row r="99">
+    <row r="99" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O99" s="9"/>
     </row>
-    <row r="100">
+    <row r="100" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O100" s="9"/>
     </row>
-    <row r="101">
+    <row r="101" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O101" s="9"/>
     </row>
-    <row r="102">
+    <row r="102" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O102" s="9"/>
     </row>
-    <row r="103">
+    <row r="103" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O103" s="9"/>
     </row>
-    <row r="104">
+    <row r="104" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O104" s="9"/>
     </row>
-    <row r="105">
+    <row r="105" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O105" s="9"/>
     </row>
-    <row r="106">
+    <row r="106" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O106" s="9"/>
     </row>
-    <row r="107">
+    <row r="107" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O107" s="9"/>
     </row>
-    <row r="108">
+    <row r="108" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O108" s="9"/>
     </row>
-    <row r="109">
+    <row r="109" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O109" s="9"/>
     </row>
-    <row r="110">
+    <row r="110" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O110" s="9"/>
     </row>
-    <row r="111">
+    <row r="111" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O111" s="9"/>
     </row>
-    <row r="112">
+    <row r="112" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O112" s="9"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O113" s="9"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O114" s="9"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O115" s="9"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O116" s="9"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="36"/>
       <c r="B117" s="37"/>
       <c r="C117" s="37"/>
@@ -2212,7 +2577,7 @@
       <c r="AD117" s="37"/>
       <c r="AE117" s="37"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A118" s="38"/>
       <c r="B118" s="38"/>
       <c r="C118" s="38"/>
@@ -2245,7 +2610,7 @@
       <c r="AD118" s="37"/>
       <c r="AE118" s="37"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -2278,58 +2643,58 @@
       <c r="AD119" s="14"/>
       <c r="AE119" s="14"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O120" s="9"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O121" s="9"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O122" s="9"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O123" s="9"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O124" s="9"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O125" s="9"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O126" s="9"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O127" s="9"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O128" s="9"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O129" s="9"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O130" s="9"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O131" s="9"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O132" s="9"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O133" s="9"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O134" s="9"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O135" s="9"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O136" s="9"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="41"/>
       <c r="B137" s="42"/>
       <c r="C137" s="42"/>
@@ -2362,32 +2727,32 @@
       <c r="AD137" s="42"/>
       <c r="AE137" s="42"/>
     </row>
-    <row r="138" ht="279.0" customHeight="1">
+    <row r="138" spans="1:31" ht="279" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="43"/>
       <c r="O138" s="9"/>
     </row>
-    <row r="139" ht="165.75" customHeight="1">
+    <row r="139" spans="1:31" ht="165.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O139" s="9"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O140" s="9"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O141" s="9"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O142" s="9"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O143" s="9"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O144" s="9"/>
     </row>
-    <row r="145" ht="1.5" customHeight="1">
+    <row r="145" spans="1:31" ht="1.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O145" s="9"/>
     </row>
-    <row r="146" ht="28.5" customHeight="1">
+    <row r="146" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="15"/>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
@@ -2420,7 +2785,7 @@
       <c r="AD146" s="16"/>
       <c r="AE146" s="16"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A147" s="44"/>
       <c r="B147" s="44"/>
       <c r="C147" s="44"/>
@@ -2453,7 +2818,7 @@
       <c r="AD147" s="16"/>
       <c r="AE147" s="16"/>
     </row>
-    <row r="148" ht="133.5" customHeight="1">
+    <row r="148" spans="1:31" ht="133.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="19"/>
       <c r="B148" s="19"/>
       <c r="C148" s="19"/>
@@ -2486,7 +2851,7 @@
       <c r="AD148" s="47"/>
       <c r="AE148" s="47"/>
     </row>
-    <row r="149" ht="198.0" customHeight="1">
+    <row r="149" spans="1:31" ht="198" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="19"/>
       <c r="B149" s="19"/>
       <c r="C149" s="19"/>
@@ -2519,7 +2884,7 @@
       <c r="AD149" s="47"/>
       <c r="AE149" s="47"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -2547,54 +2912,54 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" ht="174.75" customHeight="1">
+    <row r="151" spans="1:31" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="43"/>
       <c r="O151" s="9"/>
     </row>
-    <row r="152" ht="174.75" customHeight="1">
+    <row r="152" spans="1:31" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="43"/>
       <c r="O152" s="9"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O153" s="9"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O154" s="9"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O155" s="9"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O156" s="9"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O157" s="9"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O158" s="9"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O159" s="9"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O160" s="9"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O161" s="9"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O162" s="9"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O163" s="9"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O164" s="9"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O165" s="9"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="48"/>
       <c r="B166" s="49"/>
       <c r="C166" s="49"/>
@@ -2611,15 +2976,15 @@
       <c r="N166" s="49"/>
       <c r="O166" s="9"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E167" s="43"/>
       <c r="O167" s="9"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E168" s="43"/>
       <c r="O168" s="9"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="34"/>
       <c r="B169" s="35"/>
       <c r="C169" s="35"/>
@@ -2643,2256 +3008,2257 @@
       <c r="U169" s="35"/>
       <c r="V169" s="35"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E170" s="43"/>
       <c r="O170" s="9"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E171" s="43"/>
       <c r="O171" s="9"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E172" s="43"/>
       <c r="O172" s="9"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E173" s="43"/>
       <c r="O173" s="9"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E174" s="43"/>
       <c r="O174" s="9"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E175" s="43"/>
       <c r="O175" s="9"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E176" s="43"/>
       <c r="O176" s="9"/>
     </row>
-    <row r="177">
+    <row r="177" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E177" s="43"/>
       <c r="O177" s="9"/>
     </row>
-    <row r="178">
+    <row r="178" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="E178" s="43"/>
       <c r="O178" s="9"/>
     </row>
-    <row r="179">
+    <row r="179" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O179" s="9"/>
     </row>
-    <row r="180">
+    <row r="180" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O180" s="9"/>
     </row>
-    <row r="181">
+    <row r="181" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O181" s="9"/>
     </row>
-    <row r="182">
+    <row r="182" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O182" s="9"/>
     </row>
-    <row r="183">
+    <row r="183" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O183" s="9"/>
     </row>
-    <row r="184">
+    <row r="184" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O184" s="9"/>
     </row>
-    <row r="185">
+    <row r="185" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O185" s="9"/>
     </row>
-    <row r="186">
+    <row r="186" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O186" s="9"/>
     </row>
-    <row r="187">
+    <row r="187" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O187" s="9"/>
     </row>
-    <row r="188">
+    <row r="188" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O188" s="9"/>
     </row>
-    <row r="189">
+    <row r="189" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O189" s="9"/>
     </row>
-    <row r="190">
+    <row r="190" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O190" s="9"/>
     </row>
-    <row r="191">
+    <row r="191" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O191" s="9"/>
     </row>
-    <row r="192">
+    <row r="192" spans="5:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O192" s="9"/>
     </row>
-    <row r="193">
+    <row r="193" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O193" s="9"/>
     </row>
-    <row r="194">
+    <row r="194" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O194" s="9"/>
     </row>
-    <row r="195">
+    <row r="195" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O195" s="9"/>
     </row>
-    <row r="196">
+    <row r="196" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O196" s="9"/>
     </row>
-    <row r="197">
+    <row r="197" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O197" s="9"/>
     </row>
-    <row r="198">
+    <row r="198" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O198" s="9"/>
     </row>
-    <row r="199">
+    <row r="199" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O199" s="9"/>
     </row>
-    <row r="200">
+    <row r="200" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O200" s="9"/>
     </row>
-    <row r="201">
+    <row r="201" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O201" s="9"/>
     </row>
-    <row r="202">
+    <row r="202" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O202" s="9"/>
     </row>
-    <row r="203">
+    <row r="203" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O203" s="9"/>
     </row>
-    <row r="204">
+    <row r="204" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O204" s="9"/>
     </row>
-    <row r="205">
+    <row r="205" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O205" s="9"/>
     </row>
-    <row r="206">
+    <row r="206" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O206" s="9"/>
     </row>
-    <row r="207">
+    <row r="207" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O207" s="9"/>
     </row>
-    <row r="208">
+    <row r="208" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O208" s="9"/>
     </row>
-    <row r="209">
+    <row r="209" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O209" s="9"/>
     </row>
-    <row r="210">
+    <row r="210" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O210" s="9"/>
     </row>
-    <row r="211">
+    <row r="211" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O211" s="9"/>
     </row>
-    <row r="212">
+    <row r="212" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O212" s="9"/>
     </row>
-    <row r="213">
+    <row r="213" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O213" s="9"/>
     </row>
-    <row r="214">
+    <row r="214" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O214" s="9"/>
     </row>
-    <row r="215">
+    <row r="215" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O215" s="9"/>
     </row>
-    <row r="216">
+    <row r="216" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O216" s="9"/>
     </row>
-    <row r="217">
+    <row r="217" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O217" s="9"/>
     </row>
-    <row r="218">
+    <row r="218" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O218" s="9"/>
     </row>
-    <row r="219">
+    <row r="219" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O219" s="9"/>
     </row>
-    <row r="220">
+    <row r="220" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O220" s="9"/>
     </row>
-    <row r="221">
+    <row r="221" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O221" s="9"/>
     </row>
-    <row r="222">
+    <row r="222" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O222" s="9"/>
     </row>
-    <row r="223">
+    <row r="223" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O223" s="9"/>
     </row>
-    <row r="224">
+    <row r="224" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O224" s="9"/>
     </row>
-    <row r="225">
+    <row r="225" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O225" s="9"/>
     </row>
-    <row r="226">
+    <row r="226" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O226" s="9"/>
     </row>
-    <row r="227">
+    <row r="227" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O227" s="9"/>
     </row>
-    <row r="228">
+    <row r="228" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O228" s="9"/>
     </row>
-    <row r="229">
+    <row r="229" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O229" s="9"/>
     </row>
-    <row r="230">
+    <row r="230" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O230" s="9"/>
     </row>
-    <row r="231">
+    <row r="231" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O231" s="9"/>
     </row>
-    <row r="232">
+    <row r="232" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O232" s="9"/>
     </row>
-    <row r="233">
+    <row r="233" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O233" s="9"/>
     </row>
-    <row r="234">
+    <row r="234" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O234" s="9"/>
     </row>
-    <row r="235">
+    <row r="235" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O235" s="9"/>
     </row>
-    <row r="236">
+    <row r="236" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O236" s="9"/>
     </row>
-    <row r="237">
+    <row r="237" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O237" s="9"/>
     </row>
-    <row r="238">
+    <row r="238" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O238" s="9"/>
     </row>
-    <row r="239">
+    <row r="239" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O239" s="9"/>
     </row>
-    <row r="240">
+    <row r="240" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O240" s="9"/>
     </row>
-    <row r="241">
+    <row r="241" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O241" s="9"/>
     </row>
-    <row r="242">
+    <row r="242" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O242" s="9"/>
     </row>
-    <row r="243">
+    <row r="243" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O243" s="9"/>
     </row>
-    <row r="244">
+    <row r="244" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O244" s="9"/>
     </row>
-    <row r="245">
+    <row r="245" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O245" s="9"/>
     </row>
-    <row r="246">
+    <row r="246" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O246" s="9"/>
     </row>
-    <row r="247">
+    <row r="247" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O247" s="9"/>
     </row>
-    <row r="248">
+    <row r="248" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O248" s="9"/>
     </row>
-    <row r="249">
+    <row r="249" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O249" s="9"/>
     </row>
-    <row r="250">
+    <row r="250" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O250" s="9"/>
     </row>
-    <row r="251">
+    <row r="251" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O251" s="9"/>
     </row>
-    <row r="252">
+    <row r="252" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O252" s="9"/>
     </row>
-    <row r="253">
+    <row r="253" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O253" s="9"/>
     </row>
-    <row r="254">
+    <row r="254" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O254" s="9"/>
     </row>
-    <row r="255">
+    <row r="255" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O255" s="9"/>
     </row>
-    <row r="256">
+    <row r="256" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O256" s="9"/>
     </row>
-    <row r="257">
+    <row r="257" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O257" s="9"/>
     </row>
-    <row r="258">
+    <row r="258" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O258" s="9"/>
     </row>
-    <row r="259">
+    <row r="259" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O259" s="9"/>
     </row>
-    <row r="260">
+    <row r="260" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O260" s="9"/>
     </row>
-    <row r="261">
+    <row r="261" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O261" s="9"/>
     </row>
-    <row r="262">
+    <row r="262" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O262" s="9"/>
     </row>
-    <row r="263">
+    <row r="263" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O263" s="9"/>
     </row>
-    <row r="264">
+    <row r="264" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O264" s="9"/>
     </row>
-    <row r="265">
+    <row r="265" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O265" s="9"/>
     </row>
-    <row r="266">
+    <row r="266" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O266" s="9"/>
     </row>
-    <row r="267">
+    <row r="267" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O267" s="9"/>
     </row>
-    <row r="268">
+    <row r="268" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O268" s="9"/>
     </row>
-    <row r="269">
+    <row r="269" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O269" s="9"/>
     </row>
-    <row r="270">
+    <row r="270" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O270" s="9"/>
     </row>
-    <row r="271">
+    <row r="271" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O271" s="9"/>
     </row>
-    <row r="272">
+    <row r="272" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O272" s="9"/>
     </row>
-    <row r="273">
+    <row r="273" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O273" s="9"/>
     </row>
-    <row r="274">
+    <row r="274" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O274" s="9"/>
     </row>
-    <row r="275">
+    <row r="275" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O275" s="9"/>
     </row>
-    <row r="276">
+    <row r="276" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O276" s="9"/>
     </row>
-    <row r="277">
+    <row r="277" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O277" s="9"/>
     </row>
-    <row r="278">
+    <row r="278" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O278" s="9"/>
     </row>
-    <row r="279">
+    <row r="279" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O279" s="9"/>
     </row>
-    <row r="280">
+    <row r="280" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O280" s="9"/>
     </row>
-    <row r="281">
+    <row r="281" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O281" s="9"/>
     </row>
-    <row r="282">
+    <row r="282" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O282" s="9"/>
     </row>
-    <row r="283">
+    <row r="283" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O283" s="9"/>
     </row>
-    <row r="284">
+    <row r="284" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O284" s="9"/>
     </row>
-    <row r="285">
+    <row r="285" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O285" s="9"/>
     </row>
-    <row r="286">
+    <row r="286" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O286" s="9"/>
     </row>
-    <row r="287">
+    <row r="287" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O287" s="9"/>
     </row>
-    <row r="288">
+    <row r="288" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O288" s="9"/>
     </row>
-    <row r="289">
+    <row r="289" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O289" s="9"/>
     </row>
-    <row r="290">
+    <row r="290" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O290" s="9"/>
     </row>
-    <row r="291">
+    <row r="291" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O291" s="9"/>
     </row>
-    <row r="292">
+    <row r="292" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O292" s="9"/>
     </row>
-    <row r="293">
+    <row r="293" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O293" s="9"/>
     </row>
-    <row r="294">
+    <row r="294" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O294" s="9"/>
     </row>
-    <row r="295">
+    <row r="295" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O295" s="9"/>
     </row>
-    <row r="296">
+    <row r="296" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O296" s="9"/>
     </row>
-    <row r="297">
+    <row r="297" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O297" s="9"/>
     </row>
-    <row r="298">
+    <row r="298" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O298" s="9"/>
     </row>
-    <row r="299">
+    <row r="299" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O299" s="9"/>
     </row>
-    <row r="300">
+    <row r="300" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O300" s="9"/>
     </row>
-    <row r="301">
+    <row r="301" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O301" s="9"/>
     </row>
-    <row r="302">
+    <row r="302" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O302" s="9"/>
     </row>
-    <row r="303">
+    <row r="303" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O303" s="9"/>
     </row>
-    <row r="304">
+    <row r="304" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O304" s="9"/>
     </row>
-    <row r="305">
+    <row r="305" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O305" s="9"/>
     </row>
-    <row r="306">
+    <row r="306" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O306" s="9"/>
     </row>
-    <row r="307">
+    <row r="307" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O307" s="9"/>
     </row>
-    <row r="308">
+    <row r="308" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O308" s="9"/>
     </row>
-    <row r="309">
+    <row r="309" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O309" s="9"/>
     </row>
-    <row r="310">
+    <row r="310" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O310" s="9"/>
     </row>
-    <row r="311">
+    <row r="311" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O311" s="9"/>
     </row>
-    <row r="312">
+    <row r="312" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O312" s="9"/>
     </row>
-    <row r="313">
+    <row r="313" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O313" s="9"/>
     </row>
-    <row r="314">
+    <row r="314" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O314" s="9"/>
     </row>
-    <row r="315">
+    <row r="315" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O315" s="9"/>
     </row>
-    <row r="316">
+    <row r="316" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O316" s="9"/>
     </row>
-    <row r="317">
+    <row r="317" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O317" s="9"/>
     </row>
-    <row r="318">
+    <row r="318" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O318" s="9"/>
     </row>
-    <row r="319">
+    <row r="319" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O319" s="9"/>
     </row>
-    <row r="320">
+    <row r="320" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O320" s="9"/>
     </row>
-    <row r="321">
+    <row r="321" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O321" s="9"/>
     </row>
-    <row r="322">
+    <row r="322" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O322" s="9"/>
     </row>
-    <row r="323">
+    <row r="323" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O323" s="9"/>
     </row>
-    <row r="324">
+    <row r="324" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O324" s="9"/>
     </row>
-    <row r="325">
+    <row r="325" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O325" s="9"/>
     </row>
-    <row r="326">
+    <row r="326" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O326" s="9"/>
     </row>
-    <row r="327">
+    <row r="327" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O327" s="9"/>
     </row>
-    <row r="328">
+    <row r="328" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O328" s="9"/>
     </row>
-    <row r="329">
+    <row r="329" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O329" s="9"/>
     </row>
-    <row r="330">
+    <row r="330" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O330" s="9"/>
     </row>
-    <row r="331">
+    <row r="331" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O331" s="9"/>
     </row>
-    <row r="332">
+    <row r="332" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O332" s="9"/>
     </row>
-    <row r="333">
+    <row r="333" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O333" s="9"/>
     </row>
-    <row r="334">
+    <row r="334" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O334" s="9"/>
     </row>
-    <row r="335">
+    <row r="335" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O335" s="9"/>
     </row>
-    <row r="336">
+    <row r="336" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O336" s="9"/>
     </row>
-    <row r="337">
+    <row r="337" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O337" s="9"/>
     </row>
-    <row r="338">
+    <row r="338" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O338" s="9"/>
     </row>
-    <row r="339">
+    <row r="339" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O339" s="9"/>
     </row>
-    <row r="340">
+    <row r="340" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O340" s="9"/>
     </row>
-    <row r="341">
+    <row r="341" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O341" s="9"/>
     </row>
-    <row r="342">
+    <row r="342" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O342" s="9"/>
     </row>
-    <row r="343">
+    <row r="343" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O343" s="9"/>
     </row>
-    <row r="344">
+    <row r="344" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O344" s="9"/>
     </row>
-    <row r="345">
+    <row r="345" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O345" s="9"/>
     </row>
-    <row r="346">
+    <row r="346" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O346" s="9"/>
     </row>
-    <row r="347">
+    <row r="347" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O347" s="9"/>
     </row>
-    <row r="348">
+    <row r="348" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O348" s="9"/>
     </row>
-    <row r="349">
+    <row r="349" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O349" s="9"/>
     </row>
-    <row r="350">
+    <row r="350" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O350" s="9"/>
     </row>
-    <row r="351">
+    <row r="351" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O351" s="9"/>
     </row>
-    <row r="352">
+    <row r="352" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O352" s="9"/>
     </row>
-    <row r="353">
+    <row r="353" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O353" s="9"/>
     </row>
-    <row r="354">
+    <row r="354" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O354" s="9"/>
     </row>
-    <row r="355">
+    <row r="355" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O355" s="9"/>
     </row>
-    <row r="356">
+    <row r="356" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O356" s="9"/>
     </row>
-    <row r="357">
+    <row r="357" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O357" s="9"/>
     </row>
-    <row r="358">
+    <row r="358" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O358" s="9"/>
     </row>
-    <row r="359">
+    <row r="359" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O359" s="9"/>
     </row>
-    <row r="360">
+    <row r="360" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O360" s="9"/>
     </row>
-    <row r="361">
+    <row r="361" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O361" s="9"/>
     </row>
-    <row r="362">
+    <row r="362" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O362" s="9"/>
     </row>
-    <row r="363">
+    <row r="363" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O363" s="9"/>
     </row>
-    <row r="364">
+    <row r="364" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O364" s="9"/>
     </row>
-    <row r="365">
+    <row r="365" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O365" s="9"/>
     </row>
-    <row r="366">
+    <row r="366" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O366" s="9"/>
     </row>
-    <row r="367">
+    <row r="367" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O367" s="9"/>
     </row>
-    <row r="368">
+    <row r="368" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O368" s="9"/>
     </row>
-    <row r="369">
+    <row r="369" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O369" s="9"/>
     </row>
-    <row r="370">
+    <row r="370" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O370" s="9"/>
     </row>
-    <row r="371">
+    <row r="371" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O371" s="9"/>
     </row>
-    <row r="372">
+    <row r="372" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O372" s="9"/>
     </row>
-    <row r="373">
+    <row r="373" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O373" s="9"/>
     </row>
-    <row r="374">
+    <row r="374" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O374" s="9"/>
     </row>
-    <row r="375">
+    <row r="375" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O375" s="9"/>
     </row>
-    <row r="376">
+    <row r="376" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O376" s="9"/>
     </row>
-    <row r="377">
+    <row r="377" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O377" s="9"/>
     </row>
-    <row r="378">
+    <row r="378" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O378" s="9"/>
     </row>
-    <row r="379">
+    <row r="379" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O379" s="9"/>
     </row>
-    <row r="380">
+    <row r="380" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O380" s="9"/>
     </row>
-    <row r="381">
+    <row r="381" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O381" s="9"/>
     </row>
-    <row r="382">
+    <row r="382" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O382" s="9"/>
     </row>
-    <row r="383">
+    <row r="383" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O383" s="9"/>
     </row>
-    <row r="384">
+    <row r="384" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O384" s="9"/>
     </row>
-    <row r="385">
+    <row r="385" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O385" s="9"/>
     </row>
-    <row r="386">
+    <row r="386" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O386" s="9"/>
     </row>
-    <row r="387">
+    <row r="387" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O387" s="9"/>
     </row>
-    <row r="388">
+    <row r="388" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O388" s="9"/>
     </row>
-    <row r="389">
+    <row r="389" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O389" s="9"/>
     </row>
-    <row r="390">
+    <row r="390" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O390" s="9"/>
     </row>
-    <row r="391">
+    <row r="391" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O391" s="9"/>
     </row>
-    <row r="392">
+    <row r="392" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O392" s="9"/>
     </row>
-    <row r="393">
+    <row r="393" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O393" s="9"/>
     </row>
-    <row r="394">
+    <row r="394" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O394" s="9"/>
     </row>
-    <row r="395">
+    <row r="395" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O395" s="9"/>
     </row>
-    <row r="396">
+    <row r="396" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O396" s="9"/>
     </row>
-    <row r="397">
+    <row r="397" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O397" s="9"/>
     </row>
-    <row r="398">
+    <row r="398" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O398" s="9"/>
     </row>
-    <row r="399">
+    <row r="399" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O399" s="9"/>
     </row>
-    <row r="400">
+    <row r="400" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O400" s="9"/>
     </row>
-    <row r="401">
+    <row r="401" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O401" s="9"/>
     </row>
-    <row r="402">
+    <row r="402" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O402" s="9"/>
     </row>
-    <row r="403">
+    <row r="403" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O403" s="9"/>
     </row>
-    <row r="404">
+    <row r="404" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O404" s="9"/>
     </row>
-    <row r="405">
+    <row r="405" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O405" s="9"/>
     </row>
-    <row r="406">
+    <row r="406" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O406" s="9"/>
     </row>
-    <row r="407">
+    <row r="407" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O407" s="9"/>
     </row>
-    <row r="408">
+    <row r="408" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O408" s="9"/>
     </row>
-    <row r="409">
+    <row r="409" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O409" s="9"/>
     </row>
-    <row r="410">
+    <row r="410" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O410" s="9"/>
     </row>
-    <row r="411">
+    <row r="411" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O411" s="9"/>
     </row>
-    <row r="412">
+    <row r="412" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O412" s="9"/>
     </row>
-    <row r="413">
+    <row r="413" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O413" s="9"/>
     </row>
-    <row r="414">
+    <row r="414" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O414" s="9"/>
     </row>
-    <row r="415">
+    <row r="415" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O415" s="9"/>
     </row>
-    <row r="416">
+    <row r="416" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O416" s="9"/>
     </row>
-    <row r="417">
+    <row r="417" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O417" s="9"/>
     </row>
-    <row r="418">
+    <row r="418" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O418" s="9"/>
     </row>
-    <row r="419">
+    <row r="419" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O419" s="9"/>
     </row>
-    <row r="420">
+    <row r="420" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O420" s="9"/>
     </row>
-    <row r="421">
+    <row r="421" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O421" s="9"/>
     </row>
-    <row r="422">
+    <row r="422" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O422" s="9"/>
     </row>
-    <row r="423">
+    <row r="423" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O423" s="9"/>
     </row>
-    <row r="424">
+    <row r="424" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O424" s="9"/>
     </row>
-    <row r="425">
+    <row r="425" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O425" s="9"/>
     </row>
-    <row r="426">
+    <row r="426" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O426" s="9"/>
     </row>
-    <row r="427">
+    <row r="427" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O427" s="9"/>
     </row>
-    <row r="428">
+    <row r="428" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O428" s="9"/>
     </row>
-    <row r="429">
+    <row r="429" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O429" s="9"/>
     </row>
-    <row r="430">
+    <row r="430" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O430" s="9"/>
     </row>
-    <row r="431">
+    <row r="431" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O431" s="9"/>
     </row>
-    <row r="432">
+    <row r="432" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O432" s="9"/>
     </row>
-    <row r="433">
+    <row r="433" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O433" s="9"/>
     </row>
-    <row r="434">
+    <row r="434" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O434" s="9"/>
     </row>
-    <row r="435">
+    <row r="435" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O435" s="9"/>
     </row>
-    <row r="436">
+    <row r="436" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O436" s="9"/>
     </row>
-    <row r="437">
+    <row r="437" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O437" s="9"/>
     </row>
-    <row r="438">
+    <row r="438" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O438" s="9"/>
     </row>
-    <row r="439">
+    <row r="439" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O439" s="9"/>
     </row>
-    <row r="440">
+    <row r="440" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O440" s="9"/>
     </row>
-    <row r="441">
+    <row r="441" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O441" s="9"/>
     </row>
-    <row r="442">
+    <row r="442" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O442" s="9"/>
     </row>
-    <row r="443">
+    <row r="443" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O443" s="9"/>
     </row>
-    <row r="444">
+    <row r="444" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O444" s="9"/>
     </row>
-    <row r="445">
+    <row r="445" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O445" s="9"/>
     </row>
-    <row r="446">
+    <row r="446" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O446" s="9"/>
     </row>
-    <row r="447">
+    <row r="447" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O447" s="9"/>
     </row>
-    <row r="448">
+    <row r="448" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O448" s="9"/>
     </row>
-    <row r="449">
+    <row r="449" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O449" s="9"/>
     </row>
-    <row r="450">
+    <row r="450" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O450" s="9"/>
     </row>
-    <row r="451">
+    <row r="451" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O451" s="9"/>
     </row>
-    <row r="452">
+    <row r="452" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O452" s="9"/>
     </row>
-    <row r="453">
+    <row r="453" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O453" s="9"/>
     </row>
-    <row r="454">
+    <row r="454" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O454" s="9"/>
     </row>
-    <row r="455">
+    <row r="455" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O455" s="9"/>
     </row>
-    <row r="456">
+    <row r="456" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O456" s="9"/>
     </row>
-    <row r="457">
+    <row r="457" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O457" s="9"/>
     </row>
-    <row r="458">
+    <row r="458" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O458" s="9"/>
     </row>
-    <row r="459">
+    <row r="459" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O459" s="9"/>
     </row>
-    <row r="460">
+    <row r="460" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O460" s="9"/>
     </row>
-    <row r="461">
+    <row r="461" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O461" s="9"/>
     </row>
-    <row r="462">
+    <row r="462" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O462" s="9"/>
     </row>
-    <row r="463">
+    <row r="463" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O463" s="9"/>
     </row>
-    <row r="464">
+    <row r="464" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O464" s="9"/>
     </row>
-    <row r="465">
+    <row r="465" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O465" s="9"/>
     </row>
-    <row r="466">
+    <row r="466" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O466" s="9"/>
     </row>
-    <row r="467">
+    <row r="467" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O467" s="9"/>
     </row>
-    <row r="468">
+    <row r="468" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O468" s="9"/>
     </row>
-    <row r="469">
+    <row r="469" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O469" s="9"/>
     </row>
-    <row r="470">
+    <row r="470" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O470" s="9"/>
     </row>
-    <row r="471">
+    <row r="471" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O471" s="9"/>
     </row>
-    <row r="472">
+    <row r="472" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O472" s="9"/>
     </row>
-    <row r="473">
+    <row r="473" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O473" s="9"/>
     </row>
-    <row r="474">
+    <row r="474" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O474" s="9"/>
     </row>
-    <row r="475">
+    <row r="475" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O475" s="9"/>
     </row>
-    <row r="476">
+    <row r="476" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O476" s="9"/>
     </row>
-    <row r="477">
+    <row r="477" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O477" s="9"/>
     </row>
-    <row r="478">
+    <row r="478" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O478" s="9"/>
     </row>
-    <row r="479">
+    <row r="479" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O479" s="9"/>
     </row>
-    <row r="480">
+    <row r="480" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O480" s="9"/>
     </row>
-    <row r="481">
+    <row r="481" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O481" s="9"/>
     </row>
-    <row r="482">
+    <row r="482" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O482" s="9"/>
     </row>
-    <row r="483">
+    <row r="483" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O483" s="9"/>
     </row>
-    <row r="484">
+    <row r="484" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O484" s="9"/>
     </row>
-    <row r="485">
+    <row r="485" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O485" s="9"/>
     </row>
-    <row r="486">
+    <row r="486" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O486" s="9"/>
     </row>
-    <row r="487">
+    <row r="487" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O487" s="9"/>
     </row>
-    <row r="488">
+    <row r="488" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O488" s="9"/>
     </row>
-    <row r="489">
+    <row r="489" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O489" s="9"/>
     </row>
-    <row r="490">
+    <row r="490" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O490" s="9"/>
     </row>
-    <row r="491">
+    <row r="491" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O491" s="9"/>
     </row>
-    <row r="492">
+    <row r="492" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O492" s="9"/>
     </row>
-    <row r="493">
+    <row r="493" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O493" s="9"/>
     </row>
-    <row r="494">
+    <row r="494" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O494" s="9"/>
     </row>
-    <row r="495">
+    <row r="495" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O495" s="9"/>
     </row>
-    <row r="496">
+    <row r="496" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O496" s="9"/>
     </row>
-    <row r="497">
+    <row r="497" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O497" s="9"/>
     </row>
-    <row r="498">
+    <row r="498" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O498" s="9"/>
     </row>
-    <row r="499">
+    <row r="499" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O499" s="9"/>
     </row>
-    <row r="500">
+    <row r="500" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O500" s="9"/>
     </row>
-    <row r="501">
+    <row r="501" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O501" s="9"/>
     </row>
-    <row r="502">
+    <row r="502" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O502" s="9"/>
     </row>
-    <row r="503">
+    <row r="503" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O503" s="9"/>
     </row>
-    <row r="504">
+    <row r="504" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O504" s="9"/>
     </row>
-    <row r="505">
+    <row r="505" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O505" s="9"/>
     </row>
-    <row r="506">
+    <row r="506" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O506" s="9"/>
     </row>
-    <row r="507">
+    <row r="507" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O507" s="9"/>
     </row>
-    <row r="508">
+    <row r="508" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O508" s="9"/>
     </row>
-    <row r="509">
+    <row r="509" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O509" s="9"/>
     </row>
-    <row r="510">
+    <row r="510" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O510" s="9"/>
     </row>
-    <row r="511">
+    <row r="511" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O511" s="9"/>
     </row>
-    <row r="512">
+    <row r="512" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O512" s="9"/>
     </row>
-    <row r="513">
+    <row r="513" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O513" s="9"/>
     </row>
-    <row r="514">
+    <row r="514" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O514" s="9"/>
     </row>
-    <row r="515">
+    <row r="515" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O515" s="9"/>
     </row>
-    <row r="516">
+    <row r="516" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O516" s="9"/>
     </row>
-    <row r="517">
+    <row r="517" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O517" s="9"/>
     </row>
-    <row r="518">
+    <row r="518" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O518" s="9"/>
     </row>
-    <row r="519">
+    <row r="519" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O519" s="9"/>
     </row>
-    <row r="520">
+    <row r="520" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O520" s="9"/>
     </row>
-    <row r="521">
+    <row r="521" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O521" s="9"/>
     </row>
-    <row r="522">
+    <row r="522" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O522" s="9"/>
     </row>
-    <row r="523">
+    <row r="523" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O523" s="9"/>
     </row>
-    <row r="524">
+    <row r="524" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O524" s="9"/>
     </row>
-    <row r="525">
+    <row r="525" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O525" s="9"/>
     </row>
-    <row r="526">
+    <row r="526" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O526" s="9"/>
     </row>
-    <row r="527">
+    <row r="527" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O527" s="9"/>
     </row>
-    <row r="528">
+    <row r="528" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O528" s="9"/>
     </row>
-    <row r="529">
+    <row r="529" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O529" s="9"/>
     </row>
-    <row r="530">
+    <row r="530" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O530" s="9"/>
     </row>
-    <row r="531">
+    <row r="531" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O531" s="9"/>
     </row>
-    <row r="532">
+    <row r="532" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O532" s="9"/>
     </row>
-    <row r="533">
+    <row r="533" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O533" s="9"/>
     </row>
-    <row r="534">
+    <row r="534" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O534" s="9"/>
     </row>
-    <row r="535">
+    <row r="535" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O535" s="9"/>
     </row>
-    <row r="536">
+    <row r="536" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O536" s="9"/>
     </row>
-    <row r="537">
+    <row r="537" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O537" s="9"/>
     </row>
-    <row r="538">
+    <row r="538" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O538" s="9"/>
     </row>
-    <row r="539">
+    <row r="539" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O539" s="9"/>
     </row>
-    <row r="540">
+    <row r="540" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O540" s="9"/>
     </row>
-    <row r="541">
+    <row r="541" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O541" s="9"/>
     </row>
-    <row r="542">
+    <row r="542" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O542" s="9"/>
     </row>
-    <row r="543">
+    <row r="543" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O543" s="9"/>
     </row>
-    <row r="544">
+    <row r="544" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O544" s="9"/>
     </row>
-    <row r="545">
+    <row r="545" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O545" s="9"/>
     </row>
-    <row r="546">
+    <row r="546" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O546" s="9"/>
     </row>
-    <row r="547">
+    <row r="547" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O547" s="9"/>
     </row>
-    <row r="548">
+    <row r="548" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O548" s="9"/>
     </row>
-    <row r="549">
+    <row r="549" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O549" s="9"/>
     </row>
-    <row r="550">
+    <row r="550" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O550" s="9"/>
     </row>
-    <row r="551">
+    <row r="551" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O551" s="9"/>
     </row>
-    <row r="552">
+    <row r="552" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O552" s="9"/>
     </row>
-    <row r="553">
+    <row r="553" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O553" s="9"/>
     </row>
-    <row r="554">
+    <row r="554" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O554" s="9"/>
     </row>
-    <row r="555">
+    <row r="555" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O555" s="9"/>
     </row>
-    <row r="556">
+    <row r="556" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O556" s="9"/>
     </row>
-    <row r="557">
+    <row r="557" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O557" s="9"/>
     </row>
-    <row r="558">
+    <row r="558" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O558" s="9"/>
     </row>
-    <row r="559">
+    <row r="559" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O559" s="9"/>
     </row>
-    <row r="560">
+    <row r="560" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O560" s="9"/>
     </row>
-    <row r="561">
+    <row r="561" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O561" s="9"/>
     </row>
-    <row r="562">
+    <row r="562" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O562" s="9"/>
     </row>
-    <row r="563">
+    <row r="563" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O563" s="9"/>
     </row>
-    <row r="564">
+    <row r="564" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O564" s="9"/>
     </row>
-    <row r="565">
+    <row r="565" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O565" s="9"/>
     </row>
-    <row r="566">
+    <row r="566" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O566" s="9"/>
     </row>
-    <row r="567">
+    <row r="567" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O567" s="9"/>
     </row>
-    <row r="568">
+    <row r="568" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O568" s="9"/>
     </row>
-    <row r="569">
+    <row r="569" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O569" s="9"/>
     </row>
-    <row r="570">
+    <row r="570" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O570" s="9"/>
     </row>
-    <row r="571">
+    <row r="571" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O571" s="9"/>
     </row>
-    <row r="572">
+    <row r="572" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O572" s="9"/>
     </row>
-    <row r="573">
+    <row r="573" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O573" s="9"/>
     </row>
-    <row r="574">
+    <row r="574" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O574" s="9"/>
     </row>
-    <row r="575">
+    <row r="575" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O575" s="9"/>
     </row>
-    <row r="576">
+    <row r="576" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O576" s="9"/>
     </row>
-    <row r="577">
+    <row r="577" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O577" s="9"/>
     </row>
-    <row r="578">
+    <row r="578" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O578" s="9"/>
     </row>
-    <row r="579">
+    <row r="579" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O579" s="9"/>
     </row>
-    <row r="580">
+    <row r="580" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O580" s="9"/>
     </row>
-    <row r="581">
+    <row r="581" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O581" s="9"/>
     </row>
-    <row r="582">
+    <row r="582" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O582" s="9"/>
     </row>
-    <row r="583">
+    <row r="583" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O583" s="9"/>
     </row>
-    <row r="584">
+    <row r="584" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O584" s="9"/>
     </row>
-    <row r="585">
+    <row r="585" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O585" s="9"/>
     </row>
-    <row r="586">
+    <row r="586" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O586" s="9"/>
     </row>
-    <row r="587">
+    <row r="587" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O587" s="9"/>
     </row>
-    <row r="588">
+    <row r="588" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O588" s="9"/>
     </row>
-    <row r="589">
+    <row r="589" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O589" s="9"/>
     </row>
-    <row r="590">
+    <row r="590" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O590" s="9"/>
     </row>
-    <row r="591">
+    <row r="591" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O591" s="9"/>
     </row>
-    <row r="592">
+    <row r="592" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O592" s="9"/>
     </row>
-    <row r="593">
+    <row r="593" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O593" s="9"/>
     </row>
-    <row r="594">
+    <row r="594" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O594" s="9"/>
     </row>
-    <row r="595">
+    <row r="595" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O595" s="9"/>
     </row>
-    <row r="596">
+    <row r="596" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O596" s="9"/>
     </row>
-    <row r="597">
+    <row r="597" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O597" s="9"/>
     </row>
-    <row r="598">
+    <row r="598" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O598" s="9"/>
     </row>
-    <row r="599">
+    <row r="599" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O599" s="9"/>
     </row>
-    <row r="600">
+    <row r="600" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O600" s="9"/>
     </row>
-    <row r="601">
+    <row r="601" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O601" s="9"/>
     </row>
-    <row r="602">
+    <row r="602" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O602" s="9"/>
     </row>
-    <row r="603">
+    <row r="603" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O603" s="9"/>
     </row>
-    <row r="604">
+    <row r="604" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O604" s="9"/>
     </row>
-    <row r="605">
+    <row r="605" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O605" s="9"/>
     </row>
-    <row r="606">
+    <row r="606" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O606" s="9"/>
     </row>
-    <row r="607">
+    <row r="607" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O607" s="9"/>
     </row>
-    <row r="608">
+    <row r="608" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O608" s="9"/>
     </row>
-    <row r="609">
+    <row r="609" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O609" s="9"/>
     </row>
-    <row r="610">
+    <row r="610" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O610" s="9"/>
     </row>
-    <row r="611">
+    <row r="611" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O611" s="9"/>
     </row>
-    <row r="612">
+    <row r="612" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O612" s="9"/>
     </row>
-    <row r="613">
+    <row r="613" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O613" s="9"/>
     </row>
-    <row r="614">
+    <row r="614" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O614" s="9"/>
     </row>
-    <row r="615">
+    <row r="615" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O615" s="9"/>
     </row>
-    <row r="616">
+    <row r="616" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O616" s="9"/>
     </row>
-    <row r="617">
+    <row r="617" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O617" s="9"/>
     </row>
-    <row r="618">
+    <row r="618" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O618" s="9"/>
     </row>
-    <row r="619">
+    <row r="619" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O619" s="9"/>
     </row>
-    <row r="620">
+    <row r="620" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O620" s="9"/>
     </row>
-    <row r="621">
+    <row r="621" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O621" s="9"/>
     </row>
-    <row r="622">
+    <row r="622" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O622" s="9"/>
     </row>
-    <row r="623">
+    <row r="623" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O623" s="9"/>
     </row>
-    <row r="624">
+    <row r="624" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O624" s="9"/>
     </row>
-    <row r="625">
+    <row r="625" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O625" s="9"/>
     </row>
-    <row r="626">
+    <row r="626" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O626" s="9"/>
     </row>
-    <row r="627">
+    <row r="627" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O627" s="9"/>
     </row>
-    <row r="628">
+    <row r="628" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O628" s="9"/>
     </row>
-    <row r="629">
+    <row r="629" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O629" s="9"/>
     </row>
-    <row r="630">
+    <row r="630" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O630" s="9"/>
     </row>
-    <row r="631">
+    <row r="631" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O631" s="9"/>
     </row>
-    <row r="632">
+    <row r="632" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O632" s="9"/>
     </row>
-    <row r="633">
+    <row r="633" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O633" s="9"/>
     </row>
-    <row r="634">
+    <row r="634" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O634" s="9"/>
     </row>
-    <row r="635">
+    <row r="635" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O635" s="9"/>
     </row>
-    <row r="636">
+    <row r="636" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O636" s="9"/>
     </row>
-    <row r="637">
+    <row r="637" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O637" s="9"/>
     </row>
-    <row r="638">
+    <row r="638" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O638" s="9"/>
     </row>
-    <row r="639">
+    <row r="639" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O639" s="9"/>
     </row>
-    <row r="640">
+    <row r="640" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O640" s="9"/>
     </row>
-    <row r="641">
+    <row r="641" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O641" s="9"/>
     </row>
-    <row r="642">
+    <row r="642" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O642" s="9"/>
     </row>
-    <row r="643">
+    <row r="643" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O643" s="9"/>
     </row>
-    <row r="644">
+    <row r="644" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O644" s="9"/>
     </row>
-    <row r="645">
+    <row r="645" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O645" s="9"/>
     </row>
-    <row r="646">
+    <row r="646" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O646" s="9"/>
     </row>
-    <row r="647">
+    <row r="647" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O647" s="9"/>
     </row>
-    <row r="648">
+    <row r="648" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O648" s="9"/>
     </row>
-    <row r="649">
+    <row r="649" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O649" s="9"/>
     </row>
-    <row r="650">
+    <row r="650" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O650" s="9"/>
     </row>
-    <row r="651">
+    <row r="651" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O651" s="9"/>
     </row>
-    <row r="652">
+    <row r="652" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O652" s="9"/>
     </row>
-    <row r="653">
+    <row r="653" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O653" s="9"/>
     </row>
-    <row r="654">
+    <row r="654" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O654" s="9"/>
     </row>
-    <row r="655">
+    <row r="655" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O655" s="9"/>
     </row>
-    <row r="656">
+    <row r="656" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O656" s="9"/>
     </row>
-    <row r="657">
+    <row r="657" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O657" s="9"/>
     </row>
-    <row r="658">
+    <row r="658" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O658" s="9"/>
     </row>
-    <row r="659">
+    <row r="659" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O659" s="9"/>
     </row>
-    <row r="660">
+    <row r="660" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O660" s="9"/>
     </row>
-    <row r="661">
+    <row r="661" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O661" s="9"/>
     </row>
-    <row r="662">
+    <row r="662" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O662" s="9"/>
     </row>
-    <row r="663">
+    <row r="663" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O663" s="9"/>
     </row>
-    <row r="664">
+    <row r="664" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O664" s="9"/>
     </row>
-    <row r="665">
+    <row r="665" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O665" s="9"/>
     </row>
-    <row r="666">
+    <row r="666" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O666" s="9"/>
     </row>
-    <row r="667">
+    <row r="667" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O667" s="9"/>
     </row>
-    <row r="668">
+    <row r="668" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O668" s="9"/>
     </row>
-    <row r="669">
+    <row r="669" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O669" s="9"/>
     </row>
-    <row r="670">
+    <row r="670" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O670" s="9"/>
     </row>
-    <row r="671">
+    <row r="671" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O671" s="9"/>
     </row>
-    <row r="672">
+    <row r="672" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O672" s="9"/>
     </row>
-    <row r="673">
+    <row r="673" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O673" s="9"/>
     </row>
-    <row r="674">
+    <row r="674" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O674" s="9"/>
     </row>
-    <row r="675">
+    <row r="675" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O675" s="9"/>
     </row>
-    <row r="676">
+    <row r="676" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O676" s="9"/>
     </row>
-    <row r="677">
+    <row r="677" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O677" s="9"/>
     </row>
-    <row r="678">
+    <row r="678" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O678" s="9"/>
     </row>
-    <row r="679">
+    <row r="679" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O679" s="9"/>
     </row>
-    <row r="680">
+    <row r="680" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O680" s="9"/>
     </row>
-    <row r="681">
+    <row r="681" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O681" s="9"/>
     </row>
-    <row r="682">
+    <row r="682" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O682" s="9"/>
     </row>
-    <row r="683">
+    <row r="683" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O683" s="9"/>
     </row>
-    <row r="684">
+    <row r="684" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O684" s="9"/>
     </row>
-    <row r="685">
+    <row r="685" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O685" s="9"/>
     </row>
-    <row r="686">
+    <row r="686" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O686" s="9"/>
     </row>
-    <row r="687">
+    <row r="687" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O687" s="9"/>
     </row>
-    <row r="688">
+    <row r="688" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O688" s="9"/>
     </row>
-    <row r="689">
+    <row r="689" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O689" s="9"/>
     </row>
-    <row r="690">
+    <row r="690" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O690" s="9"/>
     </row>
-    <row r="691">
+    <row r="691" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O691" s="9"/>
     </row>
-    <row r="692">
+    <row r="692" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O692" s="9"/>
     </row>
-    <row r="693">
+    <row r="693" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O693" s="9"/>
     </row>
-    <row r="694">
+    <row r="694" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O694" s="9"/>
     </row>
-    <row r="695">
+    <row r="695" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O695" s="9"/>
     </row>
-    <row r="696">
+    <row r="696" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O696" s="9"/>
     </row>
-    <row r="697">
+    <row r="697" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O697" s="9"/>
     </row>
-    <row r="698">
+    <row r="698" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O698" s="9"/>
     </row>
-    <row r="699">
+    <row r="699" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O699" s="9"/>
     </row>
-    <row r="700">
+    <row r="700" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O700" s="9"/>
     </row>
-    <row r="701">
+    <row r="701" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O701" s="9"/>
     </row>
-    <row r="702">
+    <row r="702" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O702" s="9"/>
     </row>
-    <row r="703">
+    <row r="703" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O703" s="9"/>
     </row>
-    <row r="704">
+    <row r="704" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O704" s="9"/>
     </row>
-    <row r="705">
+    <row r="705" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O705" s="9"/>
     </row>
-    <row r="706">
+    <row r="706" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O706" s="9"/>
     </row>
-    <row r="707">
+    <row r="707" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O707" s="9"/>
     </row>
-    <row r="708">
+    <row r="708" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O708" s="9"/>
     </row>
-    <row r="709">
+    <row r="709" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O709" s="9"/>
     </row>
-    <row r="710">
+    <row r="710" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O710" s="9"/>
     </row>
-    <row r="711">
+    <row r="711" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O711" s="9"/>
     </row>
-    <row r="712">
+    <row r="712" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O712" s="9"/>
     </row>
-    <row r="713">
+    <row r="713" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O713" s="9"/>
     </row>
-    <row r="714">
+    <row r="714" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O714" s="9"/>
     </row>
-    <row r="715">
+    <row r="715" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O715" s="9"/>
     </row>
-    <row r="716">
+    <row r="716" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O716" s="9"/>
     </row>
-    <row r="717">
+    <row r="717" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O717" s="9"/>
     </row>
-    <row r="718">
+    <row r="718" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O718" s="9"/>
     </row>
-    <row r="719">
+    <row r="719" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O719" s="9"/>
     </row>
-    <row r="720">
+    <row r="720" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O720" s="9"/>
     </row>
-    <row r="721">
+    <row r="721" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O721" s="9"/>
     </row>
-    <row r="722">
+    <row r="722" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O722" s="9"/>
     </row>
-    <row r="723">
+    <row r="723" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O723" s="9"/>
     </row>
-    <row r="724">
+    <row r="724" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O724" s="9"/>
     </row>
-    <row r="725">
+    <row r="725" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O725" s="9"/>
     </row>
-    <row r="726">
+    <row r="726" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O726" s="9"/>
     </row>
-    <row r="727">
+    <row r="727" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O727" s="9"/>
     </row>
-    <row r="728">
+    <row r="728" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O728" s="9"/>
     </row>
-    <row r="729">
+    <row r="729" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O729" s="9"/>
     </row>
-    <row r="730">
+    <row r="730" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O730" s="9"/>
     </row>
-    <row r="731">
+    <row r="731" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O731" s="9"/>
     </row>
-    <row r="732">
+    <row r="732" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O732" s="9"/>
     </row>
-    <row r="733">
+    <row r="733" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O733" s="9"/>
     </row>
-    <row r="734">
+    <row r="734" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O734" s="9"/>
     </row>
-    <row r="735">
+    <row r="735" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O735" s="9"/>
     </row>
-    <row r="736">
+    <row r="736" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O736" s="9"/>
     </row>
-    <row r="737">
+    <row r="737" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O737" s="9"/>
     </row>
-    <row r="738">
+    <row r="738" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O738" s="9"/>
     </row>
-    <row r="739">
+    <row r="739" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O739" s="9"/>
     </row>
-    <row r="740">
+    <row r="740" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O740" s="9"/>
     </row>
-    <row r="741">
+    <row r="741" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O741" s="9"/>
     </row>
-    <row r="742">
+    <row r="742" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O742" s="9"/>
     </row>
-    <row r="743">
+    <row r="743" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O743" s="9"/>
     </row>
-    <row r="744">
+    <row r="744" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O744" s="9"/>
     </row>
-    <row r="745">
+    <row r="745" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O745" s="9"/>
     </row>
-    <row r="746">
+    <row r="746" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O746" s="9"/>
     </row>
-    <row r="747">
+    <row r="747" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O747" s="9"/>
     </row>
-    <row r="748">
+    <row r="748" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O748" s="9"/>
     </row>
-    <row r="749">
+    <row r="749" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O749" s="9"/>
     </row>
-    <row r="750">
+    <row r="750" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O750" s="9"/>
     </row>
-    <row r="751">
+    <row r="751" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O751" s="9"/>
     </row>
-    <row r="752">
+    <row r="752" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O752" s="9"/>
     </row>
-    <row r="753">
+    <row r="753" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O753" s="9"/>
     </row>
-    <row r="754">
+    <row r="754" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O754" s="9"/>
     </row>
-    <row r="755">
+    <row r="755" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O755" s="9"/>
     </row>
-    <row r="756">
+    <row r="756" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O756" s="9"/>
     </row>
-    <row r="757">
+    <row r="757" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O757" s="9"/>
     </row>
-    <row r="758">
+    <row r="758" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O758" s="9"/>
     </row>
-    <row r="759">
+    <row r="759" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O759" s="9"/>
     </row>
-    <row r="760">
+    <row r="760" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O760" s="9"/>
     </row>
-    <row r="761">
+    <row r="761" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O761" s="9"/>
     </row>
-    <row r="762">
+    <row r="762" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O762" s="9"/>
     </row>
-    <row r="763">
+    <row r="763" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O763" s="9"/>
     </row>
-    <row r="764">
+    <row r="764" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O764" s="9"/>
     </row>
-    <row r="765">
+    <row r="765" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O765" s="9"/>
     </row>
-    <row r="766">
+    <row r="766" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O766" s="9"/>
     </row>
-    <row r="767">
+    <row r="767" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O767" s="9"/>
     </row>
-    <row r="768">
+    <row r="768" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O768" s="9"/>
     </row>
-    <row r="769">
+    <row r="769" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O769" s="9"/>
     </row>
-    <row r="770">
+    <row r="770" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O770" s="9"/>
     </row>
-    <row r="771">
+    <row r="771" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O771" s="9"/>
     </row>
-    <row r="772">
+    <row r="772" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O772" s="9"/>
     </row>
-    <row r="773">
+    <row r="773" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O773" s="9"/>
     </row>
-    <row r="774">
+    <row r="774" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O774" s="9"/>
     </row>
-    <row r="775">
+    <row r="775" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O775" s="9"/>
     </row>
-    <row r="776">
+    <row r="776" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O776" s="9"/>
     </row>
-    <row r="777">
+    <row r="777" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O777" s="9"/>
     </row>
-    <row r="778">
+    <row r="778" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O778" s="9"/>
     </row>
-    <row r="779">
+    <row r="779" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O779" s="9"/>
     </row>
-    <row r="780">
+    <row r="780" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O780" s="9"/>
     </row>
-    <row r="781">
+    <row r="781" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O781" s="9"/>
     </row>
-    <row r="782">
+    <row r="782" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O782" s="9"/>
     </row>
-    <row r="783">
+    <row r="783" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O783" s="9"/>
     </row>
-    <row r="784">
+    <row r="784" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O784" s="9"/>
     </row>
-    <row r="785">
+    <row r="785" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O785" s="9"/>
     </row>
-    <row r="786">
+    <row r="786" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O786" s="9"/>
     </row>
-    <row r="787">
+    <row r="787" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O787" s="9"/>
     </row>
-    <row r="788">
+    <row r="788" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O788" s="9"/>
     </row>
-    <row r="789">
+    <row r="789" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O789" s="9"/>
     </row>
-    <row r="790">
+    <row r="790" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O790" s="9"/>
     </row>
-    <row r="791">
+    <row r="791" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O791" s="9"/>
     </row>
-    <row r="792">
+    <row r="792" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O792" s="9"/>
     </row>
-    <row r="793">
+    <row r="793" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O793" s="9"/>
     </row>
-    <row r="794">
+    <row r="794" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O794" s="9"/>
     </row>
-    <row r="795">
+    <row r="795" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O795" s="9"/>
     </row>
-    <row r="796">
+    <row r="796" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O796" s="9"/>
     </row>
-    <row r="797">
+    <row r="797" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O797" s="9"/>
     </row>
-    <row r="798">
+    <row r="798" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O798" s="9"/>
     </row>
-    <row r="799">
+    <row r="799" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O799" s="9"/>
     </row>
-    <row r="800">
+    <row r="800" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O800" s="9"/>
     </row>
-    <row r="801">
+    <row r="801" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O801" s="9"/>
     </row>
-    <row r="802">
+    <row r="802" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O802" s="9"/>
     </row>
-    <row r="803">
+    <row r="803" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O803" s="9"/>
     </row>
-    <row r="804">
+    <row r="804" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O804" s="9"/>
     </row>
-    <row r="805">
+    <row r="805" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O805" s="9"/>
     </row>
-    <row r="806">
+    <row r="806" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O806" s="9"/>
     </row>
-    <row r="807">
+    <row r="807" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O807" s="9"/>
     </row>
-    <row r="808">
+    <row r="808" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O808" s="9"/>
     </row>
-    <row r="809">
+    <row r="809" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O809" s="9"/>
     </row>
-    <row r="810">
+    <row r="810" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O810" s="9"/>
     </row>
-    <row r="811">
+    <row r="811" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O811" s="9"/>
     </row>
-    <row r="812">
+    <row r="812" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O812" s="9"/>
     </row>
-    <row r="813">
+    <row r="813" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O813" s="9"/>
     </row>
-    <row r="814">
+    <row r="814" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O814" s="9"/>
     </row>
-    <row r="815">
+    <row r="815" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O815" s="9"/>
     </row>
-    <row r="816">
+    <row r="816" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O816" s="9"/>
     </row>
-    <row r="817">
+    <row r="817" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O817" s="9"/>
     </row>
-    <row r="818">
+    <row r="818" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O818" s="9"/>
     </row>
-    <row r="819">
+    <row r="819" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O819" s="9"/>
     </row>
-    <row r="820">
+    <row r="820" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O820" s="9"/>
     </row>
-    <row r="821">
+    <row r="821" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O821" s="9"/>
     </row>
-    <row r="822">
+    <row r="822" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O822" s="9"/>
     </row>
-    <row r="823">
+    <row r="823" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O823" s="9"/>
     </row>
-    <row r="824">
+    <row r="824" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O824" s="9"/>
     </row>
-    <row r="825">
+    <row r="825" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O825" s="9"/>
     </row>
-    <row r="826">
+    <row r="826" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O826" s="9"/>
     </row>
-    <row r="827">
+    <row r="827" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O827" s="9"/>
     </row>
-    <row r="828">
+    <row r="828" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O828" s="9"/>
     </row>
-    <row r="829">
+    <row r="829" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O829" s="9"/>
     </row>
-    <row r="830">
+    <row r="830" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O830" s="9"/>
     </row>
-    <row r="831">
+    <row r="831" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O831" s="9"/>
     </row>
-    <row r="832">
+    <row r="832" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O832" s="9"/>
     </row>
-    <row r="833">
+    <row r="833" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O833" s="9"/>
     </row>
-    <row r="834">
+    <row r="834" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O834" s="9"/>
     </row>
-    <row r="835">
+    <row r="835" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O835" s="9"/>
     </row>
-    <row r="836">
+    <row r="836" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O836" s="9"/>
     </row>
-    <row r="837">
+    <row r="837" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O837" s="9"/>
     </row>
-    <row r="838">
+    <row r="838" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O838" s="9"/>
     </row>
-    <row r="839">
+    <row r="839" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O839" s="9"/>
     </row>
-    <row r="840">
+    <row r="840" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O840" s="9"/>
     </row>
-    <row r="841">
+    <row r="841" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O841" s="9"/>
     </row>
-    <row r="842">
+    <row r="842" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O842" s="9"/>
     </row>
-    <row r="843">
+    <row r="843" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O843" s="9"/>
     </row>
-    <row r="844">
+    <row r="844" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O844" s="9"/>
     </row>
-    <row r="845">
+    <row r="845" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O845" s="9"/>
     </row>
-    <row r="846">
+    <row r="846" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O846" s="9"/>
     </row>
-    <row r="847">
+    <row r="847" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O847" s="9"/>
     </row>
-    <row r="848">
+    <row r="848" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O848" s="9"/>
     </row>
-    <row r="849">
+    <row r="849" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O849" s="9"/>
     </row>
-    <row r="850">
+    <row r="850" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O850" s="9"/>
     </row>
-    <row r="851">
+    <row r="851" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O851" s="9"/>
     </row>
-    <row r="852">
+    <row r="852" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O852" s="9"/>
     </row>
-    <row r="853">
+    <row r="853" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O853" s="9"/>
     </row>
-    <row r="854">
+    <row r="854" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O854" s="9"/>
     </row>
-    <row r="855">
+    <row r="855" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O855" s="9"/>
     </row>
-    <row r="856">
+    <row r="856" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O856" s="9"/>
     </row>
-    <row r="857">
+    <row r="857" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O857" s="9"/>
     </row>
-    <row r="858">
+    <row r="858" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O858" s="9"/>
     </row>
-    <row r="859">
+    <row r="859" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O859" s="9"/>
     </row>
-    <row r="860">
+    <row r="860" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O860" s="9"/>
     </row>
-    <row r="861">
+    <row r="861" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O861" s="9"/>
     </row>
-    <row r="862">
+    <row r="862" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O862" s="9"/>
     </row>
-    <row r="863">
+    <row r="863" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O863" s="9"/>
     </row>
-    <row r="864">
+    <row r="864" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O864" s="9"/>
     </row>
-    <row r="865">
+    <row r="865" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O865" s="9"/>
     </row>
-    <row r="866">
+    <row r="866" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O866" s="9"/>
     </row>
-    <row r="867">
+    <row r="867" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O867" s="9"/>
     </row>
-    <row r="868">
+    <row r="868" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O868" s="9"/>
     </row>
-    <row r="869">
+    <row r="869" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O869" s="9"/>
     </row>
-    <row r="870">
+    <row r="870" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O870" s="9"/>
     </row>
-    <row r="871">
+    <row r="871" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O871" s="9"/>
     </row>
-    <row r="872">
+    <row r="872" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O872" s="9"/>
     </row>
-    <row r="873">
+    <row r="873" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O873" s="9"/>
     </row>
-    <row r="874">
+    <row r="874" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O874" s="9"/>
     </row>
-    <row r="875">
+    <row r="875" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O875" s="9"/>
     </row>
-    <row r="876">
+    <row r="876" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O876" s="9"/>
     </row>
-    <row r="877">
+    <row r="877" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O877" s="9"/>
     </row>
-    <row r="878">
+    <row r="878" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O878" s="9"/>
     </row>
-    <row r="879">
+    <row r="879" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O879" s="9"/>
     </row>
-    <row r="880">
+    <row r="880" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O880" s="9"/>
     </row>
-    <row r="881">
+    <row r="881" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O881" s="9"/>
     </row>
-    <row r="882">
+    <row r="882" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O882" s="9"/>
     </row>
-    <row r="883">
+    <row r="883" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O883" s="9"/>
     </row>
-    <row r="884">
+    <row r="884" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O884" s="9"/>
     </row>
-    <row r="885">
+    <row r="885" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O885" s="9"/>
     </row>
-    <row r="886">
+    <row r="886" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O886" s="9"/>
     </row>
-    <row r="887">
+    <row r="887" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O887" s="9"/>
     </row>
-    <row r="888">
+    <row r="888" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O888" s="9"/>
     </row>
-    <row r="889">
+    <row r="889" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O889" s="9"/>
     </row>
-    <row r="890">
+    <row r="890" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O890" s="9"/>
     </row>
-    <row r="891">
+    <row r="891" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O891" s="9"/>
     </row>
-    <row r="892">
+    <row r="892" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O892" s="9"/>
     </row>
-    <row r="893">
+    <row r="893" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O893" s="9"/>
     </row>
-    <row r="894">
+    <row r="894" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O894" s="9"/>
     </row>
-    <row r="895">
+    <row r="895" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O895" s="9"/>
     </row>
-    <row r="896">
+    <row r="896" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O896" s="9"/>
     </row>
-    <row r="897">
+    <row r="897" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O897" s="9"/>
     </row>
-    <row r="898">
+    <row r="898" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O898" s="9"/>
     </row>
-    <row r="899">
+    <row r="899" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O899" s="9"/>
     </row>
-    <row r="900">
+    <row r="900" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O900" s="9"/>
     </row>
-    <row r="901">
+    <row r="901" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O901" s="9"/>
     </row>
-    <row r="902">
+    <row r="902" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O902" s="9"/>
     </row>
-    <row r="903">
+    <row r="903" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O903" s="9"/>
     </row>
-    <row r="904">
+    <row r="904" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O904" s="9"/>
     </row>
-    <row r="905">
+    <row r="905" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O905" s="9"/>
     </row>
-    <row r="906">
+    <row r="906" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O906" s="9"/>
     </row>
-    <row r="907">
+    <row r="907" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O907" s="9"/>
     </row>
-    <row r="908">
+    <row r="908" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O908" s="9"/>
     </row>
-    <row r="909">
+    <row r="909" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O909" s="9"/>
     </row>
-    <row r="910">
+    <row r="910" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O910" s="9"/>
     </row>
-    <row r="911">
+    <row r="911" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O911" s="9"/>
     </row>
-    <row r="912">
+    <row r="912" spans="15:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="O912" s="9"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O61:O62">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O61:O62" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"New,Opened,assigned,fixed,retest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O63">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O63" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"New,Opened,assigned,fixed,retest,reop"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O60 O64:O77 O79:O149 O151:O168 O170:O912">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O170:O912 O64:O77 O79:O149 O151:O168 O8:O60" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"New,Opened,assigned,fixed,retest,reopened,closed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/test/BugReports.xlsx
+++ b/test/BugReports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E545AF-EF02-4D96-B93D-B69F9EF7F9D9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC8A4A9-7674-44F6-91F1-ECE2C35CA52F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
   <si>
     <t>Defect_ID</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>MB-01</t>
+  </si>
+  <si>
+    <t>Fixed</t>
   </si>
 </sst>
 </file>
@@ -569,7 +572,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -580,14 +583,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF99CCFF"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -601,28 +618,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1198,7 +1194,7 @@
         <v>27</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
@@ -1259,7 +1255,7 @@
         <v>37</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>28</v>
@@ -1320,7 +1316,7 @@
         <v>45</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>46</v>
@@ -1381,7 +1377,7 @@
         <v>71</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>72</v>
@@ -1442,7 +1438,7 @@
         <v>51</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>52</v>
@@ -1503,7 +1499,7 @@
         <v>58</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>59</v>
@@ -5247,25 +5243,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"New"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"Opened"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"Fixed"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"Retest"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"Reopened"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Closed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Approved"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/test/BugReports.xlsx
+++ b/test/BugReports.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KING\Desktop\Alaa\QA-project-tool-main\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC8A4A9-7674-44F6-91F1-ECE2C35CA52F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Bug Reports" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
   <si>
     <t>Defect_ID</t>
   </si>
@@ -318,11 +317,46 @@
   <si>
     <t>Fixed</t>
   </si>
+  <si>
+    <t>BUG-HP-02</t>
+  </si>
+  <si>
+    <t>The user is redirected to the "Gallery" instead of "My Bookings" Page when a user isn't logged in and clicks on My Bookings in the nav bar then he sucessfully logs in but after login he is redirected to home/gallery not the My Bookings Page.</t>
+  </si>
+  <si>
+    <t>The User is not logged in and is on the Home(Gallery) Page</t>
+  </si>
+  <si>
+    <t>email:alol1922002@gmail.com
+pass:alol1922002@gmail.comA</t>
+  </si>
+  <si>
+    <t>1- The User Clicks on the "My Bookings"  Button in the navigation bar
+2- the user logs in using login data</t>
+  </si>
+  <si>
+    <t>1- The user is redirected to the "My Bookings" Page to show previous bookings after successful login</t>
+  </si>
+  <si>
+    <t>The user is redirected to the "Gallery" instead of the "My Bookings" page.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TC_HomePage_03</t>
+  </si>
+  <si>
+    <t>HP-02</t>
+  </si>
+  <si>
+    <t>Alaa</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12">
     <font>
       <sz val="10"/>
@@ -482,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -568,11 +602,208 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="35">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1070,28 +1301,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AE912"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="84.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="84.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="68" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="58.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="116.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="51.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="68.6640625" style="1" customWidth="1"/>
-    <col min="9" max="11" width="12.5546875" style="1"/>
-    <col min="12" max="13" width="21.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="54.5546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.6640625" style="1" customWidth="1"/>
-    <col min="16" max="17" width="95.88671875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="23.44140625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="12.5546875" style="1"/>
+    <col min="4" max="4" width="34.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="116.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="51.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="68.7109375" style="1" customWidth="1"/>
+    <col min="9" max="11" width="12.5703125" style="1"/>
+    <col min="12" max="13" width="21.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="54.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" style="1" customWidth="1"/>
+    <col min="16" max="17" width="95.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="12.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="6" customFormat="1" ht="42">
@@ -1585,7 +1816,7 @@
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
     </row>
-    <row r="9" spans="1:31" ht="38.4" customHeight="1">
+    <row r="9" spans="1:31" ht="38.450000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>85</v>
       </c>
@@ -1646,40 +1877,70 @@
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
     </row>
-    <row r="10" spans="1:31" ht="13.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-    </row>
-    <row r="11" spans="1:31" ht="13.2">
+    <row r="10" spans="1:31" customFormat="1" ht="38.25">
+      <c r="A10" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="32"/>
+      <c r="N10" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P10" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="32"/>
+    </row>
+    <row r="11" spans="1:31" ht="12.75">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1712,7 +1973,7 @@
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
     </row>
-    <row r="12" spans="1:31" ht="13.2">
+    <row r="12" spans="1:31" ht="12.75">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1745,7 +2006,7 @@
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
     </row>
-    <row r="13" spans="1:31" ht="13.2">
+    <row r="13" spans="1:31" ht="12.75">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1778,7 +2039,7 @@
       <c r="AD13" s="2"/>
       <c r="AE13" s="2"/>
     </row>
-    <row r="14" spans="1:31" ht="13.2">
+    <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1793,31 +2054,31 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:31" ht="13.2">
+    <row r="15" spans="1:31" ht="12.75">
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:31" ht="13.2">
+    <row r="16" spans="1:31" ht="12.75">
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:31" ht="13.2">
+    <row r="17" spans="1:31" ht="12.75">
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:31" ht="13.2">
+    <row r="18" spans="1:31" ht="12.75">
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:31" ht="13.2">
+    <row r="19" spans="1:31" ht="12.75">
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:31" ht="13.2">
+    <row r="20" spans="1:31" ht="12.75">
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:31" ht="13.2">
+    <row r="21" spans="1:31" ht="12.75">
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:31" ht="13.2">
+    <row r="22" spans="1:31" ht="12.75">
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:31" ht="16.8">
+    <row r="23" spans="1:31" ht="16.5">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1890,82 +2151,82 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:31" ht="13.2">
+    <row r="26" spans="1:31" ht="12.75">
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:31" ht="13.2">
+    <row r="27" spans="1:31" ht="12.75">
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:31" ht="13.2">
+    <row r="28" spans="1:31" ht="12.75">
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:31" ht="13.2">
+    <row r="29" spans="1:31" ht="12.75">
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:31" ht="13.2">
+    <row r="30" spans="1:31" ht="12.75">
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:31" ht="13.2">
+    <row r="31" spans="1:31" ht="12.75">
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:31" ht="13.2">
+    <row r="32" spans="1:31" ht="12.75">
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="15:15" ht="13.2">
+    <row r="33" spans="15:15" ht="12.75">
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="15:15" ht="13.2">
+    <row r="34" spans="15:15" ht="12.75">
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="15:15" ht="13.2">
+    <row r="35" spans="15:15" ht="12.75">
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="15:15" ht="13.2">
+    <row r="36" spans="15:15" ht="12.75">
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="15:15" ht="13.2">
+    <row r="37" spans="15:15" ht="12.75">
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="15:15" ht="13.2">
+    <row r="38" spans="15:15" ht="12.75">
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="15:15" ht="13.2">
+    <row r="39" spans="15:15" ht="12.75">
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="15:15" ht="13.2">
+    <row r="40" spans="15:15" ht="12.75">
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="15:15" ht="13.2">
+    <row r="41" spans="15:15" ht="12.75">
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="15:15" ht="13.2">
+    <row r="42" spans="15:15" ht="12.75">
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="15:15" ht="13.2">
+    <row r="43" spans="15:15" ht="12.75">
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="15:15" ht="13.2">
+    <row r="44" spans="15:15" ht="12.75">
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="15:15" ht="13.2">
+    <row r="45" spans="15:15" ht="12.75">
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="15:15" ht="13.2">
+    <row r="46" spans="15:15" ht="12.75">
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="15:15" ht="13.2">
+    <row r="47" spans="15:15" ht="12.75">
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="15:15" ht="13.2">
+    <row r="48" spans="15:15" ht="12.75">
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:31" ht="13.2">
+    <row r="49" spans="1:31" ht="12.75">
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:31" ht="13.2">
+    <row r="50" spans="1:31" ht="12.75">
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:31" ht="13.2">
+    <row r="51" spans="1:31" ht="12.75">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1998,20 +2259,20 @@
       <c r="AD51" s="9"/>
       <c r="AE51" s="9"/>
     </row>
-    <row r="52" spans="1:31" ht="13.2">
+    <row r="52" spans="1:31" ht="12.75">
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:31" ht="13.2">
+    <row r="53" spans="1:31" ht="12.75">
       <c r="B53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:31" ht="13.2">
+    <row r="54" spans="1:31" ht="12.75">
       <c r="B54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
     </row>
-    <row r="55" spans="1:31" ht="13.2">
+    <row r="55" spans="1:31" ht="12.75">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2044,7 +2305,7 @@
       <c r="AD55" s="2"/>
       <c r="AE55" s="2"/>
     </row>
-    <row r="56" spans="1:31" ht="13.2">
+    <row r="56" spans="1:31" ht="12.75">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -2077,7 +2338,7 @@
       <c r="AD56" s="9"/>
       <c r="AE56" s="9"/>
     </row>
-    <row r="57" spans="1:31" ht="13.2">
+    <row r="57" spans="1:31" ht="12.75">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2110,7 +2371,7 @@
       <c r="AD57" s="2"/>
       <c r="AE57" s="2"/>
     </row>
-    <row r="58" spans="1:31" ht="13.2">
+    <row r="58" spans="1:31" ht="12.75">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2143,10 +2404,10 @@
       <c r="AD58" s="2"/>
       <c r="AE58" s="2"/>
     </row>
-    <row r="59" spans="1:31" ht="13.2">
+    <row r="59" spans="1:31" ht="12.75">
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:31" ht="13.2">
+    <row r="60" spans="1:31" ht="12.75">
       <c r="O60" s="2"/>
     </row>
     <row r="61" spans="1:31" ht="24" customHeight="1">
@@ -2215,7 +2476,7 @@
       <c r="AD62" s="11"/>
       <c r="AE62" s="11"/>
     </row>
-    <row r="63" spans="1:31" ht="13.2">
+    <row r="63" spans="1:31" ht="12.75">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2255,7 +2516,7 @@
     <row r="65" spans="1:31" ht="54" customHeight="1">
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:31" ht="13.2">
+    <row r="66" spans="1:31" ht="12.75">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -2295,7 +2556,7 @@
       <c r="H67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:31" ht="13.2">
+    <row r="68" spans="1:31" ht="12.75">
       <c r="B68" s="2"/>
       <c r="E68" s="2"/>
       <c r="G68" s="2"/>
@@ -2323,14 +2584,14 @@
       <c r="H71" s="2"/>
       <c r="O71" s="2"/>
     </row>
-    <row r="72" spans="1:31" ht="13.2">
+    <row r="72" spans="1:31" ht="12.75">
       <c r="B72" s="2"/>
       <c r="E72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="O72" s="2"/>
     </row>
-    <row r="73" spans="1:31" ht="13.2">
+    <row r="73" spans="1:31" ht="12.75">
       <c r="B73" s="2"/>
       <c r="E73" s="2"/>
       <c r="G73" s="2"/>
@@ -2365,7 +2626,7 @@
       <c r="Y74" s="15"/>
       <c r="Z74" s="15"/>
     </row>
-    <row r="75" spans="1:31" ht="13.2">
+    <row r="75" spans="1:31" ht="12.75">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="E75" s="2"/>
@@ -2389,25 +2650,25 @@
       <c r="M77" s="2"/>
       <c r="O77" s="2"/>
     </row>
-    <row r="79" spans="1:31" ht="13.2">
+    <row r="79" spans="1:31" ht="12.75">
       <c r="O79" s="2"/>
     </row>
-    <row r="80" spans="1:31" ht="13.2">
+    <row r="80" spans="1:31" ht="12.75">
       <c r="O80" s="2"/>
     </row>
-    <row r="81" spans="1:31" ht="13.2">
+    <row r="81" spans="1:31" ht="12.75">
       <c r="O81" s="2"/>
     </row>
-    <row r="82" spans="1:31" ht="13.2">
+    <row r="82" spans="1:31" ht="12.75">
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="1:31" ht="13.2">
+    <row r="83" spans="1:31" ht="12.75">
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="1:31" ht="13.2">
+    <row r="84" spans="1:31" ht="12.75">
       <c r="O84" s="2"/>
     </row>
-    <row r="85" spans="1:31" ht="13.2">
+    <row r="85" spans="1:31" ht="12.75">
       <c r="A85" s="18"/>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -2440,101 +2701,101 @@
       <c r="AD85" s="18"/>
       <c r="AE85" s="18"/>
     </row>
-    <row r="86" spans="1:31" ht="13.2">
+    <row r="86" spans="1:31" ht="12.75">
       <c r="G86" s="2"/>
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="1:31" ht="13.2">
+    <row r="87" spans="1:31" ht="12.75">
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="1:31" ht="13.2">
+    <row r="88" spans="1:31" ht="12.75">
       <c r="O88" s="2"/>
     </row>
-    <row r="89" spans="1:31" ht="13.2">
+    <row r="89" spans="1:31" ht="12.75">
       <c r="O89" s="2"/>
     </row>
-    <row r="90" spans="1:31" ht="13.2">
+    <row r="90" spans="1:31" ht="12.75">
       <c r="O90" s="2"/>
     </row>
-    <row r="91" spans="1:31" ht="13.2">
+    <row r="91" spans="1:31" ht="12.75">
       <c r="O91" s="2"/>
     </row>
-    <row r="92" spans="1:31" ht="13.2">
+    <row r="92" spans="1:31" ht="12.75">
       <c r="O92" s="2"/>
     </row>
-    <row r="93" spans="1:31" ht="13.2">
+    <row r="93" spans="1:31" ht="12.75">
       <c r="O93" s="2"/>
     </row>
-    <row r="94" spans="1:31" ht="13.2">
+    <row r="94" spans="1:31" ht="12.75">
       <c r="O94" s="2"/>
     </row>
-    <row r="95" spans="1:31" ht="13.2">
+    <row r="95" spans="1:31" ht="12.75">
       <c r="O95" s="2"/>
     </row>
-    <row r="96" spans="1:31" ht="13.2">
+    <row r="96" spans="1:31" ht="12.75">
       <c r="O96" s="2"/>
     </row>
-    <row r="97" spans="15:15" ht="13.2">
+    <row r="97" spans="15:15" ht="12.75">
       <c r="O97" s="2"/>
     </row>
-    <row r="98" spans="15:15" ht="13.2">
+    <row r="98" spans="15:15" ht="12.75">
       <c r="O98" s="2"/>
     </row>
-    <row r="99" spans="15:15" ht="13.2">
+    <row r="99" spans="15:15" ht="12.75">
       <c r="O99" s="2"/>
     </row>
-    <row r="100" spans="15:15" ht="13.2">
+    <row r="100" spans="15:15" ht="12.75">
       <c r="O100" s="2"/>
     </row>
-    <row r="101" spans="15:15" ht="13.2">
+    <row r="101" spans="15:15" ht="12.75">
       <c r="O101" s="2"/>
     </row>
-    <row r="102" spans="15:15" ht="13.2">
+    <row r="102" spans="15:15" ht="12.75">
       <c r="O102" s="2"/>
     </row>
-    <row r="103" spans="15:15" ht="13.2">
+    <row r="103" spans="15:15" ht="12.75">
       <c r="O103" s="2"/>
     </row>
-    <row r="104" spans="15:15" ht="13.2">
+    <row r="104" spans="15:15" ht="12.75">
       <c r="O104" s="2"/>
     </row>
-    <row r="105" spans="15:15" ht="13.2">
+    <row r="105" spans="15:15" ht="12.75">
       <c r="O105" s="2"/>
     </row>
-    <row r="106" spans="15:15" ht="13.2">
+    <row r="106" spans="15:15" ht="12.75">
       <c r="O106" s="2"/>
     </row>
-    <row r="107" spans="15:15" ht="13.2">
+    <row r="107" spans="15:15" ht="12.75">
       <c r="O107" s="2"/>
     </row>
-    <row r="108" spans="15:15" ht="13.2">
+    <row r="108" spans="15:15" ht="12.75">
       <c r="O108" s="2"/>
     </row>
-    <row r="109" spans="15:15" ht="13.2">
+    <row r="109" spans="15:15" ht="12.75">
       <c r="O109" s="2"/>
     </row>
-    <row r="110" spans="15:15" ht="13.2">
+    <row r="110" spans="15:15" ht="12.75">
       <c r="O110" s="2"/>
     </row>
-    <row r="111" spans="15:15" ht="13.2">
+    <row r="111" spans="15:15" ht="12.75">
       <c r="O111" s="2"/>
     </row>
-    <row r="112" spans="15:15" ht="13.2">
+    <row r="112" spans="15:15" ht="12.75">
       <c r="O112" s="2"/>
     </row>
-    <row r="113" spans="1:31" ht="13.2">
+    <row r="113" spans="1:31" ht="12.75">
       <c r="O113" s="2"/>
     </row>
-    <row r="114" spans="1:31" ht="13.2">
+    <row r="114" spans="1:31" ht="12.75">
       <c r="O114" s="2"/>
     </row>
-    <row r="115" spans="1:31" ht="13.2">
+    <row r="115" spans="1:31" ht="12.75">
       <c r="O115" s="2"/>
     </row>
-    <row r="116" spans="1:31" ht="13.2">
+    <row r="116" spans="1:31" ht="12.75">
       <c r="O116" s="2"/>
     </row>
-    <row r="117" spans="1:31" ht="13.2">
+    <row r="117" spans="1:31" ht="12.75">
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -2600,7 +2861,7 @@
       <c r="AD118" s="20"/>
       <c r="AE118" s="20"/>
     </row>
-    <row r="119" spans="1:31" ht="13.2">
+    <row r="119" spans="1:31" ht="12.75">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -2633,58 +2894,58 @@
       <c r="AD119" s="2"/>
       <c r="AE119" s="2"/>
     </row>
-    <row r="120" spans="1:31" ht="13.2">
+    <row r="120" spans="1:31" ht="12.75">
       <c r="O120" s="2"/>
     </row>
-    <row r="121" spans="1:31" ht="13.2">
+    <row r="121" spans="1:31" ht="12.75">
       <c r="O121" s="2"/>
     </row>
-    <row r="122" spans="1:31" ht="13.2">
+    <row r="122" spans="1:31" ht="12.75">
       <c r="O122" s="2"/>
     </row>
-    <row r="123" spans="1:31" ht="13.2">
+    <row r="123" spans="1:31" ht="12.75">
       <c r="O123" s="2"/>
     </row>
-    <row r="124" spans="1:31" ht="13.2">
+    <row r="124" spans="1:31" ht="12.75">
       <c r="O124" s="2"/>
     </row>
-    <row r="125" spans="1:31" ht="13.2">
+    <row r="125" spans="1:31" ht="12.75">
       <c r="O125" s="2"/>
     </row>
-    <row r="126" spans="1:31" ht="13.2">
+    <row r="126" spans="1:31" ht="12.75">
       <c r="O126" s="2"/>
     </row>
-    <row r="127" spans="1:31" ht="13.2">
+    <row r="127" spans="1:31" ht="12.75">
       <c r="O127" s="2"/>
     </row>
-    <row r="128" spans="1:31" ht="13.2">
+    <row r="128" spans="1:31" ht="12.75">
       <c r="O128" s="2"/>
     </row>
-    <row r="129" spans="1:31" ht="13.2">
+    <row r="129" spans="1:31" ht="12.75">
       <c r="O129" s="2"/>
     </row>
-    <row r="130" spans="1:31" ht="13.2">
+    <row r="130" spans="1:31" ht="12.75">
       <c r="O130" s="2"/>
     </row>
-    <row r="131" spans="1:31" ht="13.2">
+    <row r="131" spans="1:31" ht="12.75">
       <c r="O131" s="2"/>
     </row>
-    <row r="132" spans="1:31" ht="13.2">
+    <row r="132" spans="1:31" ht="12.75">
       <c r="O132" s="2"/>
     </row>
-    <row r="133" spans="1:31" ht="13.2">
+    <row r="133" spans="1:31" ht="12.75">
       <c r="O133" s="2"/>
     </row>
-    <row r="134" spans="1:31" ht="13.2">
+    <row r="134" spans="1:31" ht="12.75">
       <c r="O134" s="2"/>
     </row>
-    <row r="135" spans="1:31" ht="13.2">
+    <row r="135" spans="1:31" ht="12.75">
       <c r="O135" s="2"/>
     </row>
-    <row r="136" spans="1:31" ht="13.2">
+    <row r="136" spans="1:31" ht="12.75">
       <c r="O136" s="2"/>
     </row>
-    <row r="137" spans="1:31" ht="13.2">
+    <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="23"/>
       <c r="B137" s="24"/>
       <c r="C137" s="24"/>
@@ -2724,19 +2985,19 @@
     <row r="139" spans="1:31" ht="165.75" customHeight="1">
       <c r="O139" s="2"/>
     </row>
-    <row r="140" spans="1:31" ht="13.2">
+    <row r="140" spans="1:31" ht="12.75">
       <c r="O140" s="2"/>
     </row>
-    <row r="141" spans="1:31" ht="13.2">
+    <row r="141" spans="1:31" ht="12.75">
       <c r="O141" s="2"/>
     </row>
-    <row r="142" spans="1:31" ht="13.2">
+    <row r="142" spans="1:31" ht="12.75">
       <c r="O142" s="2"/>
     </row>
-    <row r="143" spans="1:31" ht="13.2">
+    <row r="143" spans="1:31" ht="12.75">
       <c r="O143" s="2"/>
     </row>
-    <row r="144" spans="1:31" ht="13.2">
+    <row r="144" spans="1:31" ht="12.75">
       <c r="O144" s="2"/>
     </row>
     <row r="145" spans="1:31" ht="1.5" customHeight="1">
@@ -2910,46 +3171,46 @@
       <c r="E152" s="2"/>
       <c r="O152" s="2"/>
     </row>
-    <row r="153" spans="1:31" ht="13.2">
+    <row r="153" spans="1:31" ht="12.75">
       <c r="O153" s="2"/>
     </row>
-    <row r="154" spans="1:31" ht="13.2">
+    <row r="154" spans="1:31" ht="12.75">
       <c r="O154" s="2"/>
     </row>
-    <row r="155" spans="1:31" ht="13.2">
+    <row r="155" spans="1:31" ht="12.75">
       <c r="O155" s="2"/>
     </row>
-    <row r="156" spans="1:31" ht="13.2">
+    <row r="156" spans="1:31" ht="12.75">
       <c r="O156" s="2"/>
     </row>
-    <row r="157" spans="1:31" ht="13.2">
+    <row r="157" spans="1:31" ht="12.75">
       <c r="O157" s="2"/>
     </row>
-    <row r="158" spans="1:31" ht="13.2">
+    <row r="158" spans="1:31" ht="12.75">
       <c r="O158" s="2"/>
     </row>
-    <row r="159" spans="1:31" ht="13.2">
+    <row r="159" spans="1:31" ht="12.75">
       <c r="O159" s="2"/>
     </row>
-    <row r="160" spans="1:31" ht="13.2">
+    <row r="160" spans="1:31" ht="12.75">
       <c r="O160" s="2"/>
     </row>
-    <row r="161" spans="1:22" ht="13.2">
+    <row r="161" spans="1:22" ht="12.75">
       <c r="O161" s="2"/>
     </row>
-    <row r="162" spans="1:22" ht="13.2">
+    <row r="162" spans="1:22" ht="12.75">
       <c r="O162" s="2"/>
     </row>
-    <row r="163" spans="1:22" ht="13.2">
+    <row r="163" spans="1:22" ht="12.75">
       <c r="O163" s="2"/>
     </row>
-    <row r="164" spans="1:22" ht="13.2">
+    <row r="164" spans="1:22" ht="12.75">
       <c r="O164" s="2"/>
     </row>
-    <row r="165" spans="1:22" ht="13.2">
+    <row r="165" spans="1:22" ht="12.75">
       <c r="O165" s="2"/>
     </row>
-    <row r="166" spans="1:22" ht="13.2">
+    <row r="166" spans="1:22" ht="12.75">
       <c r="A166" s="27"/>
       <c r="B166" s="28"/>
       <c r="C166" s="28"/>
@@ -2966,15 +3227,15 @@
       <c r="N166" s="28"/>
       <c r="O166" s="2"/>
     </row>
-    <row r="167" spans="1:22" ht="13.2">
+    <row r="167" spans="1:22" ht="12.75">
       <c r="E167" s="2"/>
       <c r="O167" s="2"/>
     </row>
-    <row r="168" spans="1:22" ht="13.2">
+    <row r="168" spans="1:22" ht="12.75">
       <c r="E168" s="2"/>
       <c r="O168" s="2"/>
     </row>
-    <row r="169" spans="1:22" ht="13.2">
+    <row r="169" spans="1:22" ht="12.75">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
@@ -2998,2278 +3259,2364 @@
       <c r="U169" s="18"/>
       <c r="V169" s="18"/>
     </row>
-    <row r="170" spans="1:22" ht="13.2">
+    <row r="170" spans="1:22" ht="12.75">
       <c r="E170" s="2"/>
       <c r="O170" s="2"/>
     </row>
-    <row r="171" spans="1:22" ht="13.2">
+    <row r="171" spans="1:22" ht="12.75">
       <c r="E171" s="2"/>
       <c r="O171" s="2"/>
     </row>
-    <row r="172" spans="1:22" ht="13.2">
+    <row r="172" spans="1:22" ht="12.75">
       <c r="E172" s="2"/>
       <c r="O172" s="2"/>
     </row>
-    <row r="173" spans="1:22" ht="13.2">
+    <row r="173" spans="1:22" ht="12.75">
       <c r="E173" s="2"/>
       <c r="O173" s="2"/>
     </row>
-    <row r="174" spans="1:22" ht="13.2">
+    <row r="174" spans="1:22" ht="12.75">
       <c r="E174" s="2"/>
       <c r="O174" s="2"/>
     </row>
-    <row r="175" spans="1:22" ht="13.2">
+    <row r="175" spans="1:22" ht="12.75">
       <c r="E175" s="2"/>
       <c r="O175" s="2"/>
     </row>
-    <row r="176" spans="1:22" ht="13.2">
+    <row r="176" spans="1:22" ht="12.75">
       <c r="E176" s="2"/>
       <c r="O176" s="2"/>
     </row>
-    <row r="177" spans="5:15" ht="13.2">
+    <row r="177" spans="5:15" ht="12.75">
       <c r="E177" s="2"/>
       <c r="O177" s="2"/>
     </row>
-    <row r="178" spans="5:15" ht="13.2">
+    <row r="178" spans="5:15" ht="12.75">
       <c r="E178" s="2"/>
       <c r="O178" s="2"/>
     </row>
-    <row r="179" spans="5:15" ht="13.2">
+    <row r="179" spans="5:15" ht="12.75">
       <c r="O179" s="2"/>
     </row>
-    <row r="180" spans="5:15" ht="13.2">
+    <row r="180" spans="5:15" ht="12.75">
       <c r="O180" s="2"/>
     </row>
-    <row r="181" spans="5:15" ht="13.2">
+    <row r="181" spans="5:15" ht="12.75">
       <c r="O181" s="2"/>
     </row>
-    <row r="182" spans="5:15" ht="13.2">
+    <row r="182" spans="5:15" ht="12.75">
       <c r="O182" s="2"/>
     </row>
-    <row r="183" spans="5:15" ht="13.2">
+    <row r="183" spans="5:15" ht="12.75">
       <c r="O183" s="2"/>
     </row>
-    <row r="184" spans="5:15" ht="13.2">
+    <row r="184" spans="5:15" ht="12.75">
       <c r="O184" s="2"/>
     </row>
-    <row r="185" spans="5:15" ht="13.2">
+    <row r="185" spans="5:15" ht="12.75">
       <c r="O185" s="2"/>
     </row>
-    <row r="186" spans="5:15" ht="13.2">
+    <row r="186" spans="5:15" ht="12.75">
       <c r="O186" s="2"/>
     </row>
-    <row r="187" spans="5:15" ht="13.2">
+    <row r="187" spans="5:15" ht="12.75">
       <c r="O187" s="2"/>
     </row>
-    <row r="188" spans="5:15" ht="13.2">
+    <row r="188" spans="5:15" ht="12.75">
       <c r="O188" s="2"/>
     </row>
-    <row r="189" spans="5:15" ht="13.2">
+    <row r="189" spans="5:15" ht="12.75">
       <c r="O189" s="2"/>
     </row>
-    <row r="190" spans="5:15" ht="13.2">
+    <row r="190" spans="5:15" ht="12.75">
       <c r="O190" s="2"/>
     </row>
-    <row r="191" spans="5:15" ht="13.2">
+    <row r="191" spans="5:15" ht="12.75">
       <c r="O191" s="2"/>
     </row>
-    <row r="192" spans="5:15" ht="13.2">
+    <row r="192" spans="5:15" ht="12.75">
       <c r="O192" s="2"/>
     </row>
-    <row r="193" spans="15:15" ht="13.2">
+    <row r="193" spans="15:15" ht="12.75">
       <c r="O193" s="2"/>
     </row>
-    <row r="194" spans="15:15" ht="13.2">
+    <row r="194" spans="15:15" ht="12.75">
       <c r="O194" s="2"/>
     </row>
-    <row r="195" spans="15:15" ht="13.2">
+    <row r="195" spans="15:15" ht="12.75">
       <c r="O195" s="2"/>
     </row>
-    <row r="196" spans="15:15" ht="13.2">
+    <row r="196" spans="15:15" ht="12.75">
       <c r="O196" s="2"/>
     </row>
-    <row r="197" spans="15:15" ht="13.2">
+    <row r="197" spans="15:15" ht="12.75">
       <c r="O197" s="2"/>
     </row>
-    <row r="198" spans="15:15" ht="13.2">
+    <row r="198" spans="15:15" ht="12.75">
       <c r="O198" s="2"/>
     </row>
-    <row r="199" spans="15:15" ht="13.2">
+    <row r="199" spans="15:15" ht="12.75">
       <c r="O199" s="2"/>
     </row>
-    <row r="200" spans="15:15" ht="13.2">
+    <row r="200" spans="15:15" ht="12.75">
       <c r="O200" s="2"/>
     </row>
-    <row r="201" spans="15:15" ht="13.2">
+    <row r="201" spans="15:15" ht="12.75">
       <c r="O201" s="2"/>
     </row>
-    <row r="202" spans="15:15" ht="13.2">
+    <row r="202" spans="15:15" ht="12.75">
       <c r="O202" s="2"/>
     </row>
-    <row r="203" spans="15:15" ht="13.2">
+    <row r="203" spans="15:15" ht="12.75">
       <c r="O203" s="2"/>
     </row>
-    <row r="204" spans="15:15" ht="13.2">
+    <row r="204" spans="15:15" ht="12.75">
       <c r="O204" s="2"/>
     </row>
-    <row r="205" spans="15:15" ht="13.2">
+    <row r="205" spans="15:15" ht="12.75">
       <c r="O205" s="2"/>
     </row>
-    <row r="206" spans="15:15" ht="13.2">
+    <row r="206" spans="15:15" ht="12.75">
       <c r="O206" s="2"/>
     </row>
-    <row r="207" spans="15:15" ht="13.2">
+    <row r="207" spans="15:15" ht="12.75">
       <c r="O207" s="2"/>
     </row>
-    <row r="208" spans="15:15" ht="13.2">
+    <row r="208" spans="15:15" ht="12.75">
       <c r="O208" s="2"/>
     </row>
-    <row r="209" spans="15:15" ht="13.2">
+    <row r="209" spans="15:15" ht="12.75">
       <c r="O209" s="2"/>
     </row>
-    <row r="210" spans="15:15" ht="13.2">
+    <row r="210" spans="15:15" ht="12.75">
       <c r="O210" s="2"/>
     </row>
-    <row r="211" spans="15:15" ht="13.2">
+    <row r="211" spans="15:15" ht="12.75">
       <c r="O211" s="2"/>
     </row>
-    <row r="212" spans="15:15" ht="13.2">
+    <row r="212" spans="15:15" ht="12.75">
       <c r="O212" s="2"/>
     </row>
-    <row r="213" spans="15:15" ht="13.2">
+    <row r="213" spans="15:15" ht="12.75">
       <c r="O213" s="2"/>
     </row>
-    <row r="214" spans="15:15" ht="13.2">
+    <row r="214" spans="15:15" ht="12.75">
       <c r="O214" s="2"/>
     </row>
-    <row r="215" spans="15:15" ht="13.2">
+    <row r="215" spans="15:15" ht="12.75">
       <c r="O215" s="2"/>
     </row>
-    <row r="216" spans="15:15" ht="13.2">
+    <row r="216" spans="15:15" ht="12.75">
       <c r="O216" s="2"/>
     </row>
-    <row r="217" spans="15:15" ht="13.2">
+    <row r="217" spans="15:15" ht="12.75">
       <c r="O217" s="2"/>
     </row>
-    <row r="218" spans="15:15" ht="13.2">
+    <row r="218" spans="15:15" ht="12.75">
       <c r="O218" s="2"/>
     </row>
-    <row r="219" spans="15:15" ht="13.2">
+    <row r="219" spans="15:15" ht="12.75">
       <c r="O219" s="2"/>
     </row>
-    <row r="220" spans="15:15" ht="13.2">
+    <row r="220" spans="15:15" ht="12.75">
       <c r="O220" s="2"/>
     </row>
-    <row r="221" spans="15:15" ht="13.2">
+    <row r="221" spans="15:15" ht="12.75">
       <c r="O221" s="2"/>
     </row>
-    <row r="222" spans="15:15" ht="13.2">
+    <row r="222" spans="15:15" ht="12.75">
       <c r="O222" s="2"/>
     </row>
-    <row r="223" spans="15:15" ht="13.2">
+    <row r="223" spans="15:15" ht="12.75">
       <c r="O223" s="2"/>
     </row>
-    <row r="224" spans="15:15" ht="13.2">
+    <row r="224" spans="15:15" ht="12.75">
       <c r="O224" s="2"/>
     </row>
-    <row r="225" spans="15:15" ht="13.2">
+    <row r="225" spans="15:15" ht="12.75">
       <c r="O225" s="2"/>
     </row>
-    <row r="226" spans="15:15" ht="13.2">
+    <row r="226" spans="15:15" ht="12.75">
       <c r="O226" s="2"/>
     </row>
-    <row r="227" spans="15:15" ht="13.2">
+    <row r="227" spans="15:15" ht="12.75">
       <c r="O227" s="2"/>
     </row>
-    <row r="228" spans="15:15" ht="13.2">
+    <row r="228" spans="15:15" ht="12.75">
       <c r="O228" s="2"/>
     </row>
-    <row r="229" spans="15:15" ht="13.2">
+    <row r="229" spans="15:15" ht="12.75">
       <c r="O229" s="2"/>
     </row>
-    <row r="230" spans="15:15" ht="13.2">
+    <row r="230" spans="15:15" ht="12.75">
       <c r="O230" s="2"/>
     </row>
-    <row r="231" spans="15:15" ht="13.2">
+    <row r="231" spans="15:15" ht="12.75">
       <c r="O231" s="2"/>
     </row>
-    <row r="232" spans="15:15" ht="13.2">
+    <row r="232" spans="15:15" ht="12.75">
       <c r="O232" s="2"/>
     </row>
-    <row r="233" spans="15:15" ht="13.2">
+    <row r="233" spans="15:15" ht="12.75">
       <c r="O233" s="2"/>
     </row>
-    <row r="234" spans="15:15" ht="13.2">
+    <row r="234" spans="15:15" ht="12.75">
       <c r="O234" s="2"/>
     </row>
-    <row r="235" spans="15:15" ht="13.2">
+    <row r="235" spans="15:15" ht="12.75">
       <c r="O235" s="2"/>
     </row>
-    <row r="236" spans="15:15" ht="13.2">
+    <row r="236" spans="15:15" ht="12.75">
       <c r="O236" s="2"/>
     </row>
-    <row r="237" spans="15:15" ht="13.2">
+    <row r="237" spans="15:15" ht="12.75">
       <c r="O237" s="2"/>
     </row>
-    <row r="238" spans="15:15" ht="13.2">
+    <row r="238" spans="15:15" ht="12.75">
       <c r="O238" s="2"/>
     </row>
-    <row r="239" spans="15:15" ht="13.2">
+    <row r="239" spans="15:15" ht="12.75">
       <c r="O239" s="2"/>
     </row>
-    <row r="240" spans="15:15" ht="13.2">
+    <row r="240" spans="15:15" ht="12.75">
       <c r="O240" s="2"/>
     </row>
-    <row r="241" spans="15:15" ht="13.2">
+    <row r="241" spans="15:15" ht="12.75">
       <c r="O241" s="2"/>
     </row>
-    <row r="242" spans="15:15" ht="13.2">
+    <row r="242" spans="15:15" ht="12.75">
       <c r="O242" s="2"/>
     </row>
-    <row r="243" spans="15:15" ht="13.2">
+    <row r="243" spans="15:15" ht="12.75">
       <c r="O243" s="2"/>
     </row>
-    <row r="244" spans="15:15" ht="13.2">
+    <row r="244" spans="15:15" ht="12.75">
       <c r="O244" s="2"/>
     </row>
-    <row r="245" spans="15:15" ht="13.2">
+    <row r="245" spans="15:15" ht="12.75">
       <c r="O245" s="2"/>
     </row>
-    <row r="246" spans="15:15" ht="13.2">
+    <row r="246" spans="15:15" ht="12.75">
       <c r="O246" s="2"/>
     </row>
-    <row r="247" spans="15:15" ht="13.2">
+    <row r="247" spans="15:15" ht="12.75">
       <c r="O247" s="2"/>
     </row>
-    <row r="248" spans="15:15" ht="13.2">
+    <row r="248" spans="15:15" ht="12.75">
       <c r="O248" s="2"/>
     </row>
-    <row r="249" spans="15:15" ht="13.2">
+    <row r="249" spans="15:15" ht="12.75">
       <c r="O249" s="2"/>
     </row>
-    <row r="250" spans="15:15" ht="13.2">
+    <row r="250" spans="15:15" ht="12.75">
       <c r="O250" s="2"/>
     </row>
-    <row r="251" spans="15:15" ht="13.2">
+    <row r="251" spans="15:15" ht="12.75">
       <c r="O251" s="2"/>
     </row>
-    <row r="252" spans="15:15" ht="13.2">
+    <row r="252" spans="15:15" ht="12.75">
       <c r="O252" s="2"/>
     </row>
-    <row r="253" spans="15:15" ht="13.2">
+    <row r="253" spans="15:15" ht="12.75">
       <c r="O253" s="2"/>
     </row>
-    <row r="254" spans="15:15" ht="13.2">
+    <row r="254" spans="15:15" ht="12.75">
       <c r="O254" s="2"/>
     </row>
-    <row r="255" spans="15:15" ht="13.2">
+    <row r="255" spans="15:15" ht="12.75">
       <c r="O255" s="2"/>
     </row>
-    <row r="256" spans="15:15" ht="13.2">
+    <row r="256" spans="15:15" ht="12.75">
       <c r="O256" s="2"/>
     </row>
-    <row r="257" spans="15:15" ht="13.2">
+    <row r="257" spans="15:15" ht="12.75">
       <c r="O257" s="2"/>
     </row>
-    <row r="258" spans="15:15" ht="13.2">
+    <row r="258" spans="15:15" ht="12.75">
       <c r="O258" s="2"/>
     </row>
-    <row r="259" spans="15:15" ht="13.2">
+    <row r="259" spans="15:15" ht="12.75">
       <c r="O259" s="2"/>
     </row>
-    <row r="260" spans="15:15" ht="13.2">
+    <row r="260" spans="15:15" ht="12.75">
       <c r="O260" s="2"/>
     </row>
-    <row r="261" spans="15:15" ht="13.2">
+    <row r="261" spans="15:15" ht="12.75">
       <c r="O261" s="2"/>
     </row>
-    <row r="262" spans="15:15" ht="13.2">
+    <row r="262" spans="15:15" ht="12.75">
       <c r="O262" s="2"/>
     </row>
-    <row r="263" spans="15:15" ht="13.2">
+    <row r="263" spans="15:15" ht="12.75">
       <c r="O263" s="2"/>
     </row>
-    <row r="264" spans="15:15" ht="13.2">
+    <row r="264" spans="15:15" ht="12.75">
       <c r="O264" s="2"/>
     </row>
-    <row r="265" spans="15:15" ht="13.2">
+    <row r="265" spans="15:15" ht="12.75">
       <c r="O265" s="2"/>
     </row>
-    <row r="266" spans="15:15" ht="13.2">
+    <row r="266" spans="15:15" ht="12.75">
       <c r="O266" s="2"/>
     </row>
-    <row r="267" spans="15:15" ht="13.2">
+    <row r="267" spans="15:15" ht="12.75">
       <c r="O267" s="2"/>
     </row>
-    <row r="268" spans="15:15" ht="13.2">
+    <row r="268" spans="15:15" ht="12.75">
       <c r="O268" s="2"/>
     </row>
-    <row r="269" spans="15:15" ht="13.2">
+    <row r="269" spans="15:15" ht="12.75">
       <c r="O269" s="2"/>
     </row>
-    <row r="270" spans="15:15" ht="13.2">
+    <row r="270" spans="15:15" ht="12.75">
       <c r="O270" s="2"/>
     </row>
-    <row r="271" spans="15:15" ht="13.2">
+    <row r="271" spans="15:15" ht="12.75">
       <c r="O271" s="2"/>
     </row>
-    <row r="272" spans="15:15" ht="13.2">
+    <row r="272" spans="15:15" ht="12.75">
       <c r="O272" s="2"/>
     </row>
-    <row r="273" spans="15:15" ht="13.2">
+    <row r="273" spans="15:15" ht="12.75">
       <c r="O273" s="2"/>
     </row>
-    <row r="274" spans="15:15" ht="13.2">
+    <row r="274" spans="15:15" ht="12.75">
       <c r="O274" s="2"/>
     </row>
-    <row r="275" spans="15:15" ht="13.2">
+    <row r="275" spans="15:15" ht="12.75">
       <c r="O275" s="2"/>
     </row>
-    <row r="276" spans="15:15" ht="13.2">
+    <row r="276" spans="15:15" ht="12.75">
       <c r="O276" s="2"/>
     </row>
-    <row r="277" spans="15:15" ht="13.2">
+    <row r="277" spans="15:15" ht="12.75">
       <c r="O277" s="2"/>
     </row>
-    <row r="278" spans="15:15" ht="13.2">
+    <row r="278" spans="15:15" ht="12.75">
       <c r="O278" s="2"/>
     </row>
-    <row r="279" spans="15:15" ht="13.2">
+    <row r="279" spans="15:15" ht="12.75">
       <c r="O279" s="2"/>
     </row>
-    <row r="280" spans="15:15" ht="13.2">
+    <row r="280" spans="15:15" ht="12.75">
       <c r="O280" s="2"/>
     </row>
-    <row r="281" spans="15:15" ht="13.2">
+    <row r="281" spans="15:15" ht="12.75">
       <c r="O281" s="2"/>
     </row>
-    <row r="282" spans="15:15" ht="13.2">
+    <row r="282" spans="15:15" ht="12.75">
       <c r="O282" s="2"/>
     </row>
-    <row r="283" spans="15:15" ht="13.2">
+    <row r="283" spans="15:15" ht="12.75">
       <c r="O283" s="2"/>
     </row>
-    <row r="284" spans="15:15" ht="13.2">
+    <row r="284" spans="15:15" ht="12.75">
       <c r="O284" s="2"/>
     </row>
-    <row r="285" spans="15:15" ht="13.2">
+    <row r="285" spans="15:15" ht="12.75">
       <c r="O285" s="2"/>
     </row>
-    <row r="286" spans="15:15" ht="13.2">
+    <row r="286" spans="15:15" ht="12.75">
       <c r="O286" s="2"/>
     </row>
-    <row r="287" spans="15:15" ht="13.2">
+    <row r="287" spans="15:15" ht="12.75">
       <c r="O287" s="2"/>
     </row>
-    <row r="288" spans="15:15" ht="13.2">
+    <row r="288" spans="15:15" ht="12.75">
       <c r="O288" s="2"/>
     </row>
-    <row r="289" spans="15:15" ht="13.2">
+    <row r="289" spans="15:15" ht="12.75">
       <c r="O289" s="2"/>
     </row>
-    <row r="290" spans="15:15" ht="13.2">
+    <row r="290" spans="15:15" ht="12.75">
       <c r="O290" s="2"/>
     </row>
-    <row r="291" spans="15:15" ht="13.2">
+    <row r="291" spans="15:15" ht="12.75">
       <c r="O291" s="2"/>
     </row>
-    <row r="292" spans="15:15" ht="13.2">
+    <row r="292" spans="15:15" ht="12.75">
       <c r="O292" s="2"/>
     </row>
-    <row r="293" spans="15:15" ht="13.2">
+    <row r="293" spans="15:15" ht="12.75">
       <c r="O293" s="2"/>
     </row>
-    <row r="294" spans="15:15" ht="13.2">
+    <row r="294" spans="15:15" ht="12.75">
       <c r="O294" s="2"/>
     </row>
-    <row r="295" spans="15:15" ht="13.2">
+    <row r="295" spans="15:15" ht="12.75">
       <c r="O295" s="2"/>
     </row>
-    <row r="296" spans="15:15" ht="13.2">
+    <row r="296" spans="15:15" ht="12.75">
       <c r="O296" s="2"/>
     </row>
-    <row r="297" spans="15:15" ht="13.2">
+    <row r="297" spans="15:15" ht="12.75">
       <c r="O297" s="2"/>
     </row>
-    <row r="298" spans="15:15" ht="13.2">
+    <row r="298" spans="15:15" ht="12.75">
       <c r="O298" s="2"/>
     </row>
-    <row r="299" spans="15:15" ht="13.2">
+    <row r="299" spans="15:15" ht="12.75">
       <c r="O299" s="2"/>
     </row>
-    <row r="300" spans="15:15" ht="13.2">
+    <row r="300" spans="15:15" ht="12.75">
       <c r="O300" s="2"/>
     </row>
-    <row r="301" spans="15:15" ht="13.2">
+    <row r="301" spans="15:15" ht="12.75">
       <c r="O301" s="2"/>
     </row>
-    <row r="302" spans="15:15" ht="13.2">
+    <row r="302" spans="15:15" ht="12.75">
       <c r="O302" s="2"/>
     </row>
-    <row r="303" spans="15:15" ht="13.2">
+    <row r="303" spans="15:15" ht="12.75">
       <c r="O303" s="2"/>
     </row>
-    <row r="304" spans="15:15" ht="13.2">
+    <row r="304" spans="15:15" ht="12.75">
       <c r="O304" s="2"/>
     </row>
-    <row r="305" spans="15:15" ht="13.2">
+    <row r="305" spans="15:15" ht="12.75">
       <c r="O305" s="2"/>
     </row>
-    <row r="306" spans="15:15" ht="13.2">
+    <row r="306" spans="15:15" ht="12.75">
       <c r="O306" s="2"/>
     </row>
-    <row r="307" spans="15:15" ht="13.2">
+    <row r="307" spans="15:15" ht="12.75">
       <c r="O307" s="2"/>
     </row>
-    <row r="308" spans="15:15" ht="13.2">
+    <row r="308" spans="15:15" ht="12.75">
       <c r="O308" s="2"/>
     </row>
-    <row r="309" spans="15:15" ht="13.2">
+    <row r="309" spans="15:15" ht="12.75">
       <c r="O309" s="2"/>
     </row>
-    <row r="310" spans="15:15" ht="13.2">
+    <row r="310" spans="15:15" ht="12.75">
       <c r="O310" s="2"/>
     </row>
-    <row r="311" spans="15:15" ht="13.2">
+    <row r="311" spans="15:15" ht="12.75">
       <c r="O311" s="2"/>
     </row>
-    <row r="312" spans="15:15" ht="13.2">
+    <row r="312" spans="15:15" ht="12.75">
       <c r="O312" s="2"/>
     </row>
-    <row r="313" spans="15:15" ht="13.2">
+    <row r="313" spans="15:15" ht="12.75">
       <c r="O313" s="2"/>
     </row>
-    <row r="314" spans="15:15" ht="13.2">
+    <row r="314" spans="15:15" ht="12.75">
       <c r="O314" s="2"/>
     </row>
-    <row r="315" spans="15:15" ht="13.2">
+    <row r="315" spans="15:15" ht="12.75">
       <c r="O315" s="2"/>
     </row>
-    <row r="316" spans="15:15" ht="13.2">
+    <row r="316" spans="15:15" ht="12.75">
       <c r="O316" s="2"/>
     </row>
-    <row r="317" spans="15:15" ht="13.2">
+    <row r="317" spans="15:15" ht="12.75">
       <c r="O317" s="2"/>
     </row>
-    <row r="318" spans="15:15" ht="13.2">
+    <row r="318" spans="15:15" ht="12.75">
       <c r="O318" s="2"/>
     </row>
-    <row r="319" spans="15:15" ht="13.2">
+    <row r="319" spans="15:15" ht="12.75">
       <c r="O319" s="2"/>
     </row>
-    <row r="320" spans="15:15" ht="13.2">
+    <row r="320" spans="15:15" ht="12.75">
       <c r="O320" s="2"/>
     </row>
-    <row r="321" spans="15:15" ht="13.2">
+    <row r="321" spans="15:15" ht="12.75">
       <c r="O321" s="2"/>
     </row>
-    <row r="322" spans="15:15" ht="13.2">
+    <row r="322" spans="15:15" ht="12.75">
       <c r="O322" s="2"/>
     </row>
-    <row r="323" spans="15:15" ht="13.2">
+    <row r="323" spans="15:15" ht="12.75">
       <c r="O323" s="2"/>
     </row>
-    <row r="324" spans="15:15" ht="13.2">
+    <row r="324" spans="15:15" ht="12.75">
       <c r="O324" s="2"/>
     </row>
-    <row r="325" spans="15:15" ht="13.2">
+    <row r="325" spans="15:15" ht="12.75">
       <c r="O325" s="2"/>
     </row>
-    <row r="326" spans="15:15" ht="13.2">
+    <row r="326" spans="15:15" ht="12.75">
       <c r="O326" s="2"/>
     </row>
-    <row r="327" spans="15:15" ht="13.2">
+    <row r="327" spans="15:15" ht="12.75">
       <c r="O327" s="2"/>
     </row>
-    <row r="328" spans="15:15" ht="13.2">
+    <row r="328" spans="15:15" ht="12.75">
       <c r="O328" s="2"/>
     </row>
-    <row r="329" spans="15:15" ht="13.2">
+    <row r="329" spans="15:15" ht="12.75">
       <c r="O329" s="2"/>
     </row>
-    <row r="330" spans="15:15" ht="13.2">
+    <row r="330" spans="15:15" ht="12.75">
       <c r="O330" s="2"/>
     </row>
-    <row r="331" spans="15:15" ht="13.2">
+    <row r="331" spans="15:15" ht="12.75">
       <c r="O331" s="2"/>
     </row>
-    <row r="332" spans="15:15" ht="13.2">
+    <row r="332" spans="15:15" ht="12.75">
       <c r="O332" s="2"/>
     </row>
-    <row r="333" spans="15:15" ht="13.2">
+    <row r="333" spans="15:15" ht="12.75">
       <c r="O333" s="2"/>
     </row>
-    <row r="334" spans="15:15" ht="13.2">
+    <row r="334" spans="15:15" ht="12.75">
       <c r="O334" s="2"/>
     </row>
-    <row r="335" spans="15:15" ht="13.2">
+    <row r="335" spans="15:15" ht="12.75">
       <c r="O335" s="2"/>
     </row>
-    <row r="336" spans="15:15" ht="13.2">
+    <row r="336" spans="15:15" ht="12.75">
       <c r="O336" s="2"/>
     </row>
-    <row r="337" spans="15:15" ht="13.2">
+    <row r="337" spans="15:15" ht="12.75">
       <c r="O337" s="2"/>
     </row>
-    <row r="338" spans="15:15" ht="13.2">
+    <row r="338" spans="15:15" ht="12.75">
       <c r="O338" s="2"/>
     </row>
-    <row r="339" spans="15:15" ht="13.2">
+    <row r="339" spans="15:15" ht="12.75">
       <c r="O339" s="2"/>
     </row>
-    <row r="340" spans="15:15" ht="13.2">
+    <row r="340" spans="15:15" ht="12.75">
       <c r="O340" s="2"/>
     </row>
-    <row r="341" spans="15:15" ht="13.2">
+    <row r="341" spans="15:15" ht="12.75">
       <c r="O341" s="2"/>
     </row>
-    <row r="342" spans="15:15" ht="13.2">
+    <row r="342" spans="15:15" ht="12.75">
       <c r="O342" s="2"/>
     </row>
-    <row r="343" spans="15:15" ht="13.2">
+    <row r="343" spans="15:15" ht="12.75">
       <c r="O343" s="2"/>
     </row>
-    <row r="344" spans="15:15" ht="13.2">
+    <row r="344" spans="15:15" ht="12.75">
       <c r="O344" s="2"/>
     </row>
-    <row r="345" spans="15:15" ht="13.2">
+    <row r="345" spans="15:15" ht="12.75">
       <c r="O345" s="2"/>
     </row>
-    <row r="346" spans="15:15" ht="13.2">
+    <row r="346" spans="15:15" ht="12.75">
       <c r="O346" s="2"/>
     </row>
-    <row r="347" spans="15:15" ht="13.2">
+    <row r="347" spans="15:15" ht="12.75">
       <c r="O347" s="2"/>
     </row>
-    <row r="348" spans="15:15" ht="13.2">
+    <row r="348" spans="15:15" ht="12.75">
       <c r="O348" s="2"/>
     </row>
-    <row r="349" spans="15:15" ht="13.2">
+    <row r="349" spans="15:15" ht="12.75">
       <c r="O349" s="2"/>
     </row>
-    <row r="350" spans="15:15" ht="13.2">
+    <row r="350" spans="15:15" ht="12.75">
       <c r="O350" s="2"/>
     </row>
-    <row r="351" spans="15:15" ht="13.2">
+    <row r="351" spans="15:15" ht="12.75">
       <c r="O351" s="2"/>
     </row>
-    <row r="352" spans="15:15" ht="13.2">
+    <row r="352" spans="15:15" ht="12.75">
       <c r="O352" s="2"/>
     </row>
-    <row r="353" spans="15:15" ht="13.2">
+    <row r="353" spans="15:15" ht="12.75">
       <c r="O353" s="2"/>
     </row>
-    <row r="354" spans="15:15" ht="13.2">
+    <row r="354" spans="15:15" ht="12.75">
       <c r="O354" s="2"/>
     </row>
-    <row r="355" spans="15:15" ht="13.2">
+    <row r="355" spans="15:15" ht="12.75">
       <c r="O355" s="2"/>
     </row>
-    <row r="356" spans="15:15" ht="13.2">
+    <row r="356" spans="15:15" ht="12.75">
       <c r="O356" s="2"/>
     </row>
-    <row r="357" spans="15:15" ht="13.2">
+    <row r="357" spans="15:15" ht="12.75">
       <c r="O357" s="2"/>
     </row>
-    <row r="358" spans="15:15" ht="13.2">
+    <row r="358" spans="15:15" ht="12.75">
       <c r="O358" s="2"/>
     </row>
-    <row r="359" spans="15:15" ht="13.2">
+    <row r="359" spans="15:15" ht="12.75">
       <c r="O359" s="2"/>
     </row>
-    <row r="360" spans="15:15" ht="13.2">
+    <row r="360" spans="15:15" ht="12.75">
       <c r="O360" s="2"/>
     </row>
-    <row r="361" spans="15:15" ht="13.2">
+    <row r="361" spans="15:15" ht="12.75">
       <c r="O361" s="2"/>
     </row>
-    <row r="362" spans="15:15" ht="13.2">
+    <row r="362" spans="15:15" ht="12.75">
       <c r="O362" s="2"/>
     </row>
-    <row r="363" spans="15:15" ht="13.2">
+    <row r="363" spans="15:15" ht="12.75">
       <c r="O363" s="2"/>
     </row>
-    <row r="364" spans="15:15" ht="13.2">
+    <row r="364" spans="15:15" ht="12.75">
       <c r="O364" s="2"/>
     </row>
-    <row r="365" spans="15:15" ht="13.2">
+    <row r="365" spans="15:15" ht="12.75">
       <c r="O365" s="2"/>
     </row>
-    <row r="366" spans="15:15" ht="13.2">
+    <row r="366" spans="15:15" ht="12.75">
       <c r="O366" s="2"/>
     </row>
-    <row r="367" spans="15:15" ht="13.2">
+    <row r="367" spans="15:15" ht="12.75">
       <c r="O367" s="2"/>
     </row>
-    <row r="368" spans="15:15" ht="13.2">
+    <row r="368" spans="15:15" ht="12.75">
       <c r="O368" s="2"/>
     </row>
-    <row r="369" spans="15:15" ht="13.2">
+    <row r="369" spans="15:15" ht="12.75">
       <c r="O369" s="2"/>
     </row>
-    <row r="370" spans="15:15" ht="13.2">
+    <row r="370" spans="15:15" ht="12.75">
       <c r="O370" s="2"/>
     </row>
-    <row r="371" spans="15:15" ht="13.2">
+    <row r="371" spans="15:15" ht="12.75">
       <c r="O371" s="2"/>
     </row>
-    <row r="372" spans="15:15" ht="13.2">
+    <row r="372" spans="15:15" ht="12.75">
       <c r="O372" s="2"/>
     </row>
-    <row r="373" spans="15:15" ht="13.2">
+    <row r="373" spans="15:15" ht="12.75">
       <c r="O373" s="2"/>
     </row>
-    <row r="374" spans="15:15" ht="13.2">
+    <row r="374" spans="15:15" ht="12.75">
       <c r="O374" s="2"/>
     </row>
-    <row r="375" spans="15:15" ht="13.2">
+    <row r="375" spans="15:15" ht="12.75">
       <c r="O375" s="2"/>
     </row>
-    <row r="376" spans="15:15" ht="13.2">
+    <row r="376" spans="15:15" ht="12.75">
       <c r="O376" s="2"/>
     </row>
-    <row r="377" spans="15:15" ht="13.2">
+    <row r="377" spans="15:15" ht="12.75">
       <c r="O377" s="2"/>
     </row>
-    <row r="378" spans="15:15" ht="13.2">
+    <row r="378" spans="15:15" ht="12.75">
       <c r="O378" s="2"/>
     </row>
-    <row r="379" spans="15:15" ht="13.2">
+    <row r="379" spans="15:15" ht="12.75">
       <c r="O379" s="2"/>
     </row>
-    <row r="380" spans="15:15" ht="13.2">
+    <row r="380" spans="15:15" ht="12.75">
       <c r="O380" s="2"/>
     </row>
-    <row r="381" spans="15:15" ht="13.2">
+    <row r="381" spans="15:15" ht="12.75">
       <c r="O381" s="2"/>
     </row>
-    <row r="382" spans="15:15" ht="13.2">
+    <row r="382" spans="15:15" ht="12.75">
       <c r="O382" s="2"/>
     </row>
-    <row r="383" spans="15:15" ht="13.2">
+    <row r="383" spans="15:15" ht="12.75">
       <c r="O383" s="2"/>
     </row>
-    <row r="384" spans="15:15" ht="13.2">
+    <row r="384" spans="15:15" ht="12.75">
       <c r="O384" s="2"/>
     </row>
-    <row r="385" spans="15:15" ht="13.2">
+    <row r="385" spans="15:15" ht="12.75">
       <c r="O385" s="2"/>
     </row>
-    <row r="386" spans="15:15" ht="13.2">
+    <row r="386" spans="15:15" ht="12.75">
       <c r="O386" s="2"/>
     </row>
-    <row r="387" spans="15:15" ht="13.2">
+    <row r="387" spans="15:15" ht="12.75">
       <c r="O387" s="2"/>
     </row>
-    <row r="388" spans="15:15" ht="13.2">
+    <row r="388" spans="15:15" ht="12.75">
       <c r="O388" s="2"/>
     </row>
-    <row r="389" spans="15:15" ht="13.2">
+    <row r="389" spans="15:15" ht="12.75">
       <c r="O389" s="2"/>
     </row>
-    <row r="390" spans="15:15" ht="13.2">
+    <row r="390" spans="15:15" ht="12.75">
       <c r="O390" s="2"/>
     </row>
-    <row r="391" spans="15:15" ht="13.2">
+    <row r="391" spans="15:15" ht="12.75">
       <c r="O391" s="2"/>
     </row>
-    <row r="392" spans="15:15" ht="13.2">
+    <row r="392" spans="15:15" ht="12.75">
       <c r="O392" s="2"/>
     </row>
-    <row r="393" spans="15:15" ht="13.2">
+    <row r="393" spans="15:15" ht="12.75">
       <c r="O393" s="2"/>
     </row>
-    <row r="394" spans="15:15" ht="13.2">
+    <row r="394" spans="15:15" ht="12.75">
       <c r="O394" s="2"/>
     </row>
-    <row r="395" spans="15:15" ht="13.2">
+    <row r="395" spans="15:15" ht="12.75">
       <c r="O395" s="2"/>
     </row>
-    <row r="396" spans="15:15" ht="13.2">
+    <row r="396" spans="15:15" ht="12.75">
       <c r="O396" s="2"/>
     </row>
-    <row r="397" spans="15:15" ht="13.2">
+    <row r="397" spans="15:15" ht="12.75">
       <c r="O397" s="2"/>
     </row>
-    <row r="398" spans="15:15" ht="13.2">
+    <row r="398" spans="15:15" ht="12.75">
       <c r="O398" s="2"/>
     </row>
-    <row r="399" spans="15:15" ht="13.2">
+    <row r="399" spans="15:15" ht="12.75">
       <c r="O399" s="2"/>
     </row>
-    <row r="400" spans="15:15" ht="13.2">
+    <row r="400" spans="15:15" ht="12.75">
       <c r="O400" s="2"/>
     </row>
-    <row r="401" spans="15:15" ht="13.2">
+    <row r="401" spans="15:15" ht="12.75">
       <c r="O401" s="2"/>
     </row>
-    <row r="402" spans="15:15" ht="13.2">
+    <row r="402" spans="15:15" ht="12.75">
       <c r="O402" s="2"/>
     </row>
-    <row r="403" spans="15:15" ht="13.2">
+    <row r="403" spans="15:15" ht="12.75">
       <c r="O403" s="2"/>
     </row>
-    <row r="404" spans="15:15" ht="13.2">
+    <row r="404" spans="15:15" ht="12.75">
       <c r="O404" s="2"/>
     </row>
-    <row r="405" spans="15:15" ht="13.2">
+    <row r="405" spans="15:15" ht="12.75">
       <c r="O405" s="2"/>
     </row>
-    <row r="406" spans="15:15" ht="13.2">
+    <row r="406" spans="15:15" ht="12.75">
       <c r="O406" s="2"/>
     </row>
-    <row r="407" spans="15:15" ht="13.2">
+    <row r="407" spans="15:15" ht="12.75">
       <c r="O407" s="2"/>
     </row>
-    <row r="408" spans="15:15" ht="13.2">
+    <row r="408" spans="15:15" ht="12.75">
       <c r="O408" s="2"/>
     </row>
-    <row r="409" spans="15:15" ht="13.2">
+    <row r="409" spans="15:15" ht="12.75">
       <c r="O409" s="2"/>
     </row>
-    <row r="410" spans="15:15" ht="13.2">
+    <row r="410" spans="15:15" ht="12.75">
       <c r="O410" s="2"/>
     </row>
-    <row r="411" spans="15:15" ht="13.2">
+    <row r="411" spans="15:15" ht="12.75">
       <c r="O411" s="2"/>
     </row>
-    <row r="412" spans="15:15" ht="13.2">
+    <row r="412" spans="15:15" ht="12.75">
       <c r="O412" s="2"/>
     </row>
-    <row r="413" spans="15:15" ht="13.2">
+    <row r="413" spans="15:15" ht="12.75">
       <c r="O413" s="2"/>
     </row>
-    <row r="414" spans="15:15" ht="13.2">
+    <row r="414" spans="15:15" ht="12.75">
       <c r="O414" s="2"/>
     </row>
-    <row r="415" spans="15:15" ht="13.2">
+    <row r="415" spans="15:15" ht="12.75">
       <c r="O415" s="2"/>
     </row>
-    <row r="416" spans="15:15" ht="13.2">
+    <row r="416" spans="15:15" ht="12.75">
       <c r="O416" s="2"/>
     </row>
-    <row r="417" spans="15:15" ht="13.2">
+    <row r="417" spans="15:15" ht="12.75">
       <c r="O417" s="2"/>
     </row>
-    <row r="418" spans="15:15" ht="13.2">
+    <row r="418" spans="15:15" ht="12.75">
       <c r="O418" s="2"/>
     </row>
-    <row r="419" spans="15:15" ht="13.2">
+    <row r="419" spans="15:15" ht="12.75">
       <c r="O419" s="2"/>
     </row>
-    <row r="420" spans="15:15" ht="13.2">
+    <row r="420" spans="15:15" ht="12.75">
       <c r="O420" s="2"/>
     </row>
-    <row r="421" spans="15:15" ht="13.2">
+    <row r="421" spans="15:15" ht="12.75">
       <c r="O421" s="2"/>
     </row>
-    <row r="422" spans="15:15" ht="13.2">
+    <row r="422" spans="15:15" ht="12.75">
       <c r="O422" s="2"/>
     </row>
-    <row r="423" spans="15:15" ht="13.2">
+    <row r="423" spans="15:15" ht="12.75">
       <c r="O423" s="2"/>
     </row>
-    <row r="424" spans="15:15" ht="13.2">
+    <row r="424" spans="15:15" ht="12.75">
       <c r="O424" s="2"/>
     </row>
-    <row r="425" spans="15:15" ht="13.2">
+    <row r="425" spans="15:15" ht="12.75">
       <c r="O425" s="2"/>
     </row>
-    <row r="426" spans="15:15" ht="13.2">
+    <row r="426" spans="15:15" ht="12.75">
       <c r="O426" s="2"/>
     </row>
-    <row r="427" spans="15:15" ht="13.2">
+    <row r="427" spans="15:15" ht="12.75">
       <c r="O427" s="2"/>
     </row>
-    <row r="428" spans="15:15" ht="13.2">
+    <row r="428" spans="15:15" ht="12.75">
       <c r="O428" s="2"/>
     </row>
-    <row r="429" spans="15:15" ht="13.2">
+    <row r="429" spans="15:15" ht="12.75">
       <c r="O429" s="2"/>
     </row>
-    <row r="430" spans="15:15" ht="13.2">
+    <row r="430" spans="15:15" ht="12.75">
       <c r="O430" s="2"/>
     </row>
-    <row r="431" spans="15:15" ht="13.2">
+    <row r="431" spans="15:15" ht="12.75">
       <c r="O431" s="2"/>
     </row>
-    <row r="432" spans="15:15" ht="13.2">
+    <row r="432" spans="15:15" ht="12.75">
       <c r="O432" s="2"/>
     </row>
-    <row r="433" spans="15:15" ht="13.2">
+    <row r="433" spans="15:15" ht="12.75">
       <c r="O433" s="2"/>
     </row>
-    <row r="434" spans="15:15" ht="13.2">
+    <row r="434" spans="15:15" ht="12.75">
       <c r="O434" s="2"/>
     </row>
-    <row r="435" spans="15:15" ht="13.2">
+    <row r="435" spans="15:15" ht="12.75">
       <c r="O435" s="2"/>
     </row>
-    <row r="436" spans="15:15" ht="13.2">
+    <row r="436" spans="15:15" ht="12.75">
       <c r="O436" s="2"/>
     </row>
-    <row r="437" spans="15:15" ht="13.2">
+    <row r="437" spans="15:15" ht="12.75">
       <c r="O437" s="2"/>
     </row>
-    <row r="438" spans="15:15" ht="13.2">
+    <row r="438" spans="15:15" ht="12.75">
       <c r="O438" s="2"/>
     </row>
-    <row r="439" spans="15:15" ht="13.2">
+    <row r="439" spans="15:15" ht="12.75">
       <c r="O439" s="2"/>
     </row>
-    <row r="440" spans="15:15" ht="13.2">
+    <row r="440" spans="15:15" ht="12.75">
       <c r="O440" s="2"/>
     </row>
-    <row r="441" spans="15:15" ht="13.2">
+    <row r="441" spans="15:15" ht="12.75">
       <c r="O441" s="2"/>
     </row>
-    <row r="442" spans="15:15" ht="13.2">
+    <row r="442" spans="15:15" ht="12.75">
       <c r="O442" s="2"/>
     </row>
-    <row r="443" spans="15:15" ht="13.2">
+    <row r="443" spans="15:15" ht="12.75">
       <c r="O443" s="2"/>
     </row>
-    <row r="444" spans="15:15" ht="13.2">
+    <row r="444" spans="15:15" ht="12.75">
       <c r="O444" s="2"/>
     </row>
-    <row r="445" spans="15:15" ht="13.2">
+    <row r="445" spans="15:15" ht="12.75">
       <c r="O445" s="2"/>
     </row>
-    <row r="446" spans="15:15" ht="13.2">
+    <row r="446" spans="15:15" ht="12.75">
       <c r="O446" s="2"/>
     </row>
-    <row r="447" spans="15:15" ht="13.2">
+    <row r="447" spans="15:15" ht="12.75">
       <c r="O447" s="2"/>
     </row>
-    <row r="448" spans="15:15" ht="13.2">
+    <row r="448" spans="15:15" ht="12.75">
       <c r="O448" s="2"/>
     </row>
-    <row r="449" spans="15:15" ht="13.2">
+    <row r="449" spans="15:15" ht="12.75">
       <c r="O449" s="2"/>
     </row>
-    <row r="450" spans="15:15" ht="13.2">
+    <row r="450" spans="15:15" ht="12.75">
       <c r="O450" s="2"/>
     </row>
-    <row r="451" spans="15:15" ht="13.2">
+    <row r="451" spans="15:15" ht="12.75">
       <c r="O451" s="2"/>
     </row>
-    <row r="452" spans="15:15" ht="13.2">
+    <row r="452" spans="15:15" ht="12.75">
       <c r="O452" s="2"/>
     </row>
-    <row r="453" spans="15:15" ht="13.2">
+    <row r="453" spans="15:15" ht="12.75">
       <c r="O453" s="2"/>
     </row>
-    <row r="454" spans="15:15" ht="13.2">
+    <row r="454" spans="15:15" ht="12.75">
       <c r="O454" s="2"/>
     </row>
-    <row r="455" spans="15:15" ht="13.2">
+    <row r="455" spans="15:15" ht="12.75">
       <c r="O455" s="2"/>
     </row>
-    <row r="456" spans="15:15" ht="13.2">
+    <row r="456" spans="15:15" ht="12.75">
       <c r="O456" s="2"/>
     </row>
-    <row r="457" spans="15:15" ht="13.2">
+    <row r="457" spans="15:15" ht="12.75">
       <c r="O457" s="2"/>
     </row>
-    <row r="458" spans="15:15" ht="13.2">
+    <row r="458" spans="15:15" ht="12.75">
       <c r="O458" s="2"/>
     </row>
-    <row r="459" spans="15:15" ht="13.2">
+    <row r="459" spans="15:15" ht="12.75">
       <c r="O459" s="2"/>
     </row>
-    <row r="460" spans="15:15" ht="13.2">
+    <row r="460" spans="15:15" ht="12.75">
       <c r="O460" s="2"/>
     </row>
-    <row r="461" spans="15:15" ht="13.2">
+    <row r="461" spans="15:15" ht="12.75">
       <c r="O461" s="2"/>
     </row>
-    <row r="462" spans="15:15" ht="13.2">
+    <row r="462" spans="15:15" ht="12.75">
       <c r="O462" s="2"/>
     </row>
-    <row r="463" spans="15:15" ht="13.2">
+    <row r="463" spans="15:15" ht="12.75">
       <c r="O463" s="2"/>
     </row>
-    <row r="464" spans="15:15" ht="13.2">
+    <row r="464" spans="15:15" ht="12.75">
       <c r="O464" s="2"/>
     </row>
-    <row r="465" spans="15:15" ht="13.2">
+    <row r="465" spans="15:15" ht="12.75">
       <c r="O465" s="2"/>
     </row>
-    <row r="466" spans="15:15" ht="13.2">
+    <row r="466" spans="15:15" ht="12.75">
       <c r="O466" s="2"/>
     </row>
-    <row r="467" spans="15:15" ht="13.2">
+    <row r="467" spans="15:15" ht="12.75">
       <c r="O467" s="2"/>
     </row>
-    <row r="468" spans="15:15" ht="13.2">
+    <row r="468" spans="15:15" ht="12.75">
       <c r="O468" s="2"/>
     </row>
-    <row r="469" spans="15:15" ht="13.2">
+    <row r="469" spans="15:15" ht="12.75">
       <c r="O469" s="2"/>
     </row>
-    <row r="470" spans="15:15" ht="13.2">
+    <row r="470" spans="15:15" ht="12.75">
       <c r="O470" s="2"/>
     </row>
-    <row r="471" spans="15:15" ht="13.2">
+    <row r="471" spans="15:15" ht="12.75">
       <c r="O471" s="2"/>
     </row>
-    <row r="472" spans="15:15" ht="13.2">
+    <row r="472" spans="15:15" ht="12.75">
       <c r="O472" s="2"/>
     </row>
-    <row r="473" spans="15:15" ht="13.2">
+    <row r="473" spans="15:15" ht="12.75">
       <c r="O473" s="2"/>
     </row>
-    <row r="474" spans="15:15" ht="13.2">
+    <row r="474" spans="15:15" ht="12.75">
       <c r="O474" s="2"/>
     </row>
-    <row r="475" spans="15:15" ht="13.2">
+    <row r="475" spans="15:15" ht="12.75">
       <c r="O475" s="2"/>
     </row>
-    <row r="476" spans="15:15" ht="13.2">
+    <row r="476" spans="15:15" ht="12.75">
       <c r="O476" s="2"/>
     </row>
-    <row r="477" spans="15:15" ht="13.2">
+    <row r="477" spans="15:15" ht="12.75">
       <c r="O477" s="2"/>
     </row>
-    <row r="478" spans="15:15" ht="13.2">
+    <row r="478" spans="15:15" ht="12.75">
       <c r="O478" s="2"/>
     </row>
-    <row r="479" spans="15:15" ht="13.2">
+    <row r="479" spans="15:15" ht="12.75">
       <c r="O479" s="2"/>
     </row>
-    <row r="480" spans="15:15" ht="13.2">
+    <row r="480" spans="15:15" ht="12.75">
       <c r="O480" s="2"/>
     </row>
-    <row r="481" spans="15:15" ht="13.2">
+    <row r="481" spans="15:15" ht="12.75">
       <c r="O481" s="2"/>
     </row>
-    <row r="482" spans="15:15" ht="13.2">
+    <row r="482" spans="15:15" ht="12.75">
       <c r="O482" s="2"/>
     </row>
-    <row r="483" spans="15:15" ht="13.2">
+    <row r="483" spans="15:15" ht="12.75">
       <c r="O483" s="2"/>
     </row>
-    <row r="484" spans="15:15" ht="13.2">
+    <row r="484" spans="15:15" ht="12.75">
       <c r="O484" s="2"/>
     </row>
-    <row r="485" spans="15:15" ht="13.2">
+    <row r="485" spans="15:15" ht="12.75">
       <c r="O485" s="2"/>
     </row>
-    <row r="486" spans="15:15" ht="13.2">
+    <row r="486" spans="15:15" ht="12.75">
       <c r="O486" s="2"/>
     </row>
-    <row r="487" spans="15:15" ht="13.2">
+    <row r="487" spans="15:15" ht="12.75">
       <c r="O487" s="2"/>
     </row>
-    <row r="488" spans="15:15" ht="13.2">
+    <row r="488" spans="15:15" ht="12.75">
       <c r="O488" s="2"/>
     </row>
-    <row r="489" spans="15:15" ht="13.2">
+    <row r="489" spans="15:15" ht="12.75">
       <c r="O489" s="2"/>
     </row>
-    <row r="490" spans="15:15" ht="13.2">
+    <row r="490" spans="15:15" ht="12.75">
       <c r="O490" s="2"/>
     </row>
-    <row r="491" spans="15:15" ht="13.2">
+    <row r="491" spans="15:15" ht="12.75">
       <c r="O491" s="2"/>
     </row>
-    <row r="492" spans="15:15" ht="13.2">
+    <row r="492" spans="15:15" ht="12.75">
       <c r="O492" s="2"/>
     </row>
-    <row r="493" spans="15:15" ht="13.2">
+    <row r="493" spans="15:15" ht="12.75">
       <c r="O493" s="2"/>
     </row>
-    <row r="494" spans="15:15" ht="13.2">
+    <row r="494" spans="15:15" ht="12.75">
       <c r="O494" s="2"/>
     </row>
-    <row r="495" spans="15:15" ht="13.2">
+    <row r="495" spans="15:15" ht="12.75">
       <c r="O495" s="2"/>
     </row>
-    <row r="496" spans="15:15" ht="13.2">
+    <row r="496" spans="15:15" ht="12.75">
       <c r="O496" s="2"/>
     </row>
-    <row r="497" spans="15:15" ht="13.2">
+    <row r="497" spans="15:15" ht="12.75">
       <c r="O497" s="2"/>
     </row>
-    <row r="498" spans="15:15" ht="13.2">
+    <row r="498" spans="15:15" ht="12.75">
       <c r="O498" s="2"/>
     </row>
-    <row r="499" spans="15:15" ht="13.2">
+    <row r="499" spans="15:15" ht="12.75">
       <c r="O499" s="2"/>
     </row>
-    <row r="500" spans="15:15" ht="13.2">
+    <row r="500" spans="15:15" ht="12.75">
       <c r="O500" s="2"/>
     </row>
-    <row r="501" spans="15:15" ht="13.2">
+    <row r="501" spans="15:15" ht="12.75">
       <c r="O501" s="2"/>
     </row>
-    <row r="502" spans="15:15" ht="13.2">
+    <row r="502" spans="15:15" ht="12.75">
       <c r="O502" s="2"/>
     </row>
-    <row r="503" spans="15:15" ht="13.2">
+    <row r="503" spans="15:15" ht="12.75">
       <c r="O503" s="2"/>
     </row>
-    <row r="504" spans="15:15" ht="13.2">
+    <row r="504" spans="15:15" ht="12.75">
       <c r="O504" s="2"/>
     </row>
-    <row r="505" spans="15:15" ht="13.2">
+    <row r="505" spans="15:15" ht="12.75">
       <c r="O505" s="2"/>
     </row>
-    <row r="506" spans="15:15" ht="13.2">
+    <row r="506" spans="15:15" ht="12.75">
       <c r="O506" s="2"/>
     </row>
-    <row r="507" spans="15:15" ht="13.2">
+    <row r="507" spans="15:15" ht="12.75">
       <c r="O507" s="2"/>
     </row>
-    <row r="508" spans="15:15" ht="13.2">
+    <row r="508" spans="15:15" ht="12.75">
       <c r="O508" s="2"/>
     </row>
-    <row r="509" spans="15:15" ht="13.2">
+    <row r="509" spans="15:15" ht="12.75">
       <c r="O509" s="2"/>
     </row>
-    <row r="510" spans="15:15" ht="13.2">
+    <row r="510" spans="15:15" ht="12.75">
       <c r="O510" s="2"/>
     </row>
-    <row r="511" spans="15:15" ht="13.2">
+    <row r="511" spans="15:15" ht="12.75">
       <c r="O511" s="2"/>
     </row>
-    <row r="512" spans="15:15" ht="13.2">
+    <row r="512" spans="15:15" ht="12.75">
       <c r="O512" s="2"/>
     </row>
-    <row r="513" spans="15:15" ht="13.2">
+    <row r="513" spans="15:15" ht="12.75">
       <c r="O513" s="2"/>
     </row>
-    <row r="514" spans="15:15" ht="13.2">
+    <row r="514" spans="15:15" ht="12.75">
       <c r="O514" s="2"/>
     </row>
-    <row r="515" spans="15:15" ht="13.2">
+    <row r="515" spans="15:15" ht="12.75">
       <c r="O515" s="2"/>
     </row>
-    <row r="516" spans="15:15" ht="13.2">
+    <row r="516" spans="15:15" ht="12.75">
       <c r="O516" s="2"/>
     </row>
-    <row r="517" spans="15:15" ht="13.2">
+    <row r="517" spans="15:15" ht="12.75">
       <c r="O517" s="2"/>
     </row>
-    <row r="518" spans="15:15" ht="13.2">
+    <row r="518" spans="15:15" ht="12.75">
       <c r="O518" s="2"/>
     </row>
-    <row r="519" spans="15:15" ht="13.2">
+    <row r="519" spans="15:15" ht="12.75">
       <c r="O519" s="2"/>
     </row>
-    <row r="520" spans="15:15" ht="13.2">
+    <row r="520" spans="15:15" ht="12.75">
       <c r="O520" s="2"/>
     </row>
-    <row r="521" spans="15:15" ht="13.2">
+    <row r="521" spans="15:15" ht="12.75">
       <c r="O521" s="2"/>
     </row>
-    <row r="522" spans="15:15" ht="13.2">
+    <row r="522" spans="15:15" ht="12.75">
       <c r="O522" s="2"/>
     </row>
-    <row r="523" spans="15:15" ht="13.2">
+    <row r="523" spans="15:15" ht="12.75">
       <c r="O523" s="2"/>
     </row>
-    <row r="524" spans="15:15" ht="13.2">
+    <row r="524" spans="15:15" ht="12.75">
       <c r="O524" s="2"/>
     </row>
-    <row r="525" spans="15:15" ht="13.2">
+    <row r="525" spans="15:15" ht="12.75">
       <c r="O525" s="2"/>
     </row>
-    <row r="526" spans="15:15" ht="13.2">
+    <row r="526" spans="15:15" ht="12.75">
       <c r="O526" s="2"/>
     </row>
-    <row r="527" spans="15:15" ht="13.2">
+    <row r="527" spans="15:15" ht="12.75">
       <c r="O527" s="2"/>
     </row>
-    <row r="528" spans="15:15" ht="13.2">
+    <row r="528" spans="15:15" ht="12.75">
       <c r="O528" s="2"/>
     </row>
-    <row r="529" spans="15:15" ht="13.2">
+    <row r="529" spans="15:15" ht="12.75">
       <c r="O529" s="2"/>
     </row>
-    <row r="530" spans="15:15" ht="13.2">
+    <row r="530" spans="15:15" ht="12.75">
       <c r="O530" s="2"/>
     </row>
-    <row r="531" spans="15:15" ht="13.2">
+    <row r="531" spans="15:15" ht="12.75">
       <c r="O531" s="2"/>
     </row>
-    <row r="532" spans="15:15" ht="13.2">
+    <row r="532" spans="15:15" ht="12.75">
       <c r="O532" s="2"/>
     </row>
-    <row r="533" spans="15:15" ht="13.2">
+    <row r="533" spans="15:15" ht="12.75">
       <c r="O533" s="2"/>
     </row>
-    <row r="534" spans="15:15" ht="13.2">
+    <row r="534" spans="15:15" ht="12.75">
       <c r="O534" s="2"/>
     </row>
-    <row r="535" spans="15:15" ht="13.2">
+    <row r="535" spans="15:15" ht="12.75">
       <c r="O535" s="2"/>
     </row>
-    <row r="536" spans="15:15" ht="13.2">
+    <row r="536" spans="15:15" ht="12.75">
       <c r="O536" s="2"/>
     </row>
-    <row r="537" spans="15:15" ht="13.2">
+    <row r="537" spans="15:15" ht="12.75">
       <c r="O537" s="2"/>
     </row>
-    <row r="538" spans="15:15" ht="13.2">
+    <row r="538" spans="15:15" ht="12.75">
       <c r="O538" s="2"/>
     </row>
-    <row r="539" spans="15:15" ht="13.2">
+    <row r="539" spans="15:15" ht="12.75">
       <c r="O539" s="2"/>
     </row>
-    <row r="540" spans="15:15" ht="13.2">
+    <row r="540" spans="15:15" ht="12.75">
       <c r="O540" s="2"/>
     </row>
-    <row r="541" spans="15:15" ht="13.2">
+    <row r="541" spans="15:15" ht="12.75">
       <c r="O541" s="2"/>
     </row>
-    <row r="542" spans="15:15" ht="13.2">
+    <row r="542" spans="15:15" ht="12.75">
       <c r="O542" s="2"/>
     </row>
-    <row r="543" spans="15:15" ht="13.2">
+    <row r="543" spans="15:15" ht="12.75">
       <c r="O543" s="2"/>
     </row>
-    <row r="544" spans="15:15" ht="13.2">
+    <row r="544" spans="15:15" ht="12.75">
       <c r="O544" s="2"/>
     </row>
-    <row r="545" spans="15:15" ht="13.2">
+    <row r="545" spans="15:15" ht="12.75">
       <c r="O545" s="2"/>
     </row>
-    <row r="546" spans="15:15" ht="13.2">
+    <row r="546" spans="15:15" ht="12.75">
       <c r="O546" s="2"/>
     </row>
-    <row r="547" spans="15:15" ht="13.2">
+    <row r="547" spans="15:15" ht="12.75">
       <c r="O547" s="2"/>
     </row>
-    <row r="548" spans="15:15" ht="13.2">
+    <row r="548" spans="15:15" ht="12.75">
       <c r="O548" s="2"/>
     </row>
-    <row r="549" spans="15:15" ht="13.2">
+    <row r="549" spans="15:15" ht="12.75">
       <c r="O549" s="2"/>
     </row>
-    <row r="550" spans="15:15" ht="13.2">
+    <row r="550" spans="15:15" ht="12.75">
       <c r="O550" s="2"/>
     </row>
-    <row r="551" spans="15:15" ht="13.2">
+    <row r="551" spans="15:15" ht="12.75">
       <c r="O551" s="2"/>
     </row>
-    <row r="552" spans="15:15" ht="13.2">
+    <row r="552" spans="15:15" ht="12.75">
       <c r="O552" s="2"/>
     </row>
-    <row r="553" spans="15:15" ht="13.2">
+    <row r="553" spans="15:15" ht="12.75">
       <c r="O553" s="2"/>
     </row>
-    <row r="554" spans="15:15" ht="13.2">
+    <row r="554" spans="15:15" ht="12.75">
       <c r="O554" s="2"/>
     </row>
-    <row r="555" spans="15:15" ht="13.2">
+    <row r="555" spans="15:15" ht="12.75">
       <c r="O555" s="2"/>
     </row>
-    <row r="556" spans="15:15" ht="13.2">
+    <row r="556" spans="15:15" ht="12.75">
       <c r="O556" s="2"/>
     </row>
-    <row r="557" spans="15:15" ht="13.2">
+    <row r="557" spans="15:15" ht="12.75">
       <c r="O557" s="2"/>
     </row>
-    <row r="558" spans="15:15" ht="13.2">
+    <row r="558" spans="15:15" ht="12.75">
       <c r="O558" s="2"/>
     </row>
-    <row r="559" spans="15:15" ht="13.2">
+    <row r="559" spans="15:15" ht="12.75">
       <c r="O559" s="2"/>
     </row>
-    <row r="560" spans="15:15" ht="13.2">
+    <row r="560" spans="15:15" ht="12.75">
       <c r="O560" s="2"/>
     </row>
-    <row r="561" spans="15:15" ht="13.2">
+    <row r="561" spans="15:15" ht="12.75">
       <c r="O561" s="2"/>
     </row>
-    <row r="562" spans="15:15" ht="13.2">
+    <row r="562" spans="15:15" ht="12.75">
       <c r="O562" s="2"/>
     </row>
-    <row r="563" spans="15:15" ht="13.2">
+    <row r="563" spans="15:15" ht="12.75">
       <c r="O563" s="2"/>
     </row>
-    <row r="564" spans="15:15" ht="13.2">
+    <row r="564" spans="15:15" ht="12.75">
       <c r="O564" s="2"/>
     </row>
-    <row r="565" spans="15:15" ht="13.2">
+    <row r="565" spans="15:15" ht="12.75">
       <c r="O565" s="2"/>
     </row>
-    <row r="566" spans="15:15" ht="13.2">
+    <row r="566" spans="15:15" ht="12.75">
       <c r="O566" s="2"/>
     </row>
-    <row r="567" spans="15:15" ht="13.2">
+    <row r="567" spans="15:15" ht="12.75">
       <c r="O567" s="2"/>
     </row>
-    <row r="568" spans="15:15" ht="13.2">
+    <row r="568" spans="15:15" ht="12.75">
       <c r="O568" s="2"/>
     </row>
-    <row r="569" spans="15:15" ht="13.2">
+    <row r="569" spans="15:15" ht="12.75">
       <c r="O569" s="2"/>
     </row>
-    <row r="570" spans="15:15" ht="13.2">
+    <row r="570" spans="15:15" ht="12.75">
       <c r="O570" s="2"/>
     </row>
-    <row r="571" spans="15:15" ht="13.2">
+    <row r="571" spans="15:15" ht="12.75">
       <c r="O571" s="2"/>
     </row>
-    <row r="572" spans="15:15" ht="13.2">
+    <row r="572" spans="15:15" ht="12.75">
       <c r="O572" s="2"/>
     </row>
-    <row r="573" spans="15:15" ht="13.2">
+    <row r="573" spans="15:15" ht="12.75">
       <c r="O573" s="2"/>
     </row>
-    <row r="574" spans="15:15" ht="13.2">
+    <row r="574" spans="15:15" ht="12.75">
       <c r="O574" s="2"/>
     </row>
-    <row r="575" spans="15:15" ht="13.2">
+    <row r="575" spans="15:15" ht="12.75">
       <c r="O575" s="2"/>
     </row>
-    <row r="576" spans="15:15" ht="13.2">
+    <row r="576" spans="15:15" ht="12.75">
       <c r="O576" s="2"/>
     </row>
-    <row r="577" spans="15:15" ht="13.2">
+    <row r="577" spans="15:15" ht="12.75">
       <c r="O577" s="2"/>
     </row>
-    <row r="578" spans="15:15" ht="13.2">
+    <row r="578" spans="15:15" ht="12.75">
       <c r="O578" s="2"/>
     </row>
-    <row r="579" spans="15:15" ht="13.2">
+    <row r="579" spans="15:15" ht="12.75">
       <c r="O579" s="2"/>
     </row>
-    <row r="580" spans="15:15" ht="13.2">
+    <row r="580" spans="15:15" ht="12.75">
       <c r="O580" s="2"/>
     </row>
-    <row r="581" spans="15:15" ht="13.2">
+    <row r="581" spans="15:15" ht="12.75">
       <c r="O581" s="2"/>
     </row>
-    <row r="582" spans="15:15" ht="13.2">
+    <row r="582" spans="15:15" ht="12.75">
       <c r="O582" s="2"/>
     </row>
-    <row r="583" spans="15:15" ht="13.2">
+    <row r="583" spans="15:15" ht="12.75">
       <c r="O583" s="2"/>
     </row>
-    <row r="584" spans="15:15" ht="13.2">
+    <row r="584" spans="15:15" ht="12.75">
       <c r="O584" s="2"/>
     </row>
-    <row r="585" spans="15:15" ht="13.2">
+    <row r="585" spans="15:15" ht="12.75">
       <c r="O585" s="2"/>
     </row>
-    <row r="586" spans="15:15" ht="13.2">
+    <row r="586" spans="15:15" ht="12.75">
       <c r="O586" s="2"/>
     </row>
-    <row r="587" spans="15:15" ht="13.2">
+    <row r="587" spans="15:15" ht="12.75">
       <c r="O587" s="2"/>
     </row>
-    <row r="588" spans="15:15" ht="13.2">
+    <row r="588" spans="15:15" ht="12.75">
       <c r="O588" s="2"/>
     </row>
-    <row r="589" spans="15:15" ht="13.2">
+    <row r="589" spans="15:15" ht="12.75">
       <c r="O589" s="2"/>
     </row>
-    <row r="590" spans="15:15" ht="13.2">
+    <row r="590" spans="15:15" ht="12.75">
       <c r="O590" s="2"/>
     </row>
-    <row r="591" spans="15:15" ht="13.2">
+    <row r="591" spans="15:15" ht="12.75">
       <c r="O591" s="2"/>
     </row>
-    <row r="592" spans="15:15" ht="13.2">
+    <row r="592" spans="15:15" ht="12.75">
       <c r="O592" s="2"/>
     </row>
-    <row r="593" spans="15:15" ht="13.2">
+    <row r="593" spans="15:15" ht="12.75">
       <c r="O593" s="2"/>
     </row>
-    <row r="594" spans="15:15" ht="13.2">
+    <row r="594" spans="15:15" ht="12.75">
       <c r="O594" s="2"/>
     </row>
-    <row r="595" spans="15:15" ht="13.2">
+    <row r="595" spans="15:15" ht="12.75">
       <c r="O595" s="2"/>
     </row>
-    <row r="596" spans="15:15" ht="13.2">
+    <row r="596" spans="15:15" ht="12.75">
       <c r="O596" s="2"/>
     </row>
-    <row r="597" spans="15:15" ht="13.2">
+    <row r="597" spans="15:15" ht="12.75">
       <c r="O597" s="2"/>
     </row>
-    <row r="598" spans="15:15" ht="13.2">
+    <row r="598" spans="15:15" ht="12.75">
       <c r="O598" s="2"/>
     </row>
-    <row r="599" spans="15:15" ht="13.2">
+    <row r="599" spans="15:15" ht="12.75">
       <c r="O599" s="2"/>
     </row>
-    <row r="600" spans="15:15" ht="13.2">
+    <row r="600" spans="15:15" ht="12.75">
       <c r="O600" s="2"/>
     </row>
-    <row r="601" spans="15:15" ht="13.2">
+    <row r="601" spans="15:15" ht="12.75">
       <c r="O601" s="2"/>
     </row>
-    <row r="602" spans="15:15" ht="13.2">
+    <row r="602" spans="15:15" ht="12.75">
       <c r="O602" s="2"/>
     </row>
-    <row r="603" spans="15:15" ht="13.2">
+    <row r="603" spans="15:15" ht="12.75">
       <c r="O603" s="2"/>
     </row>
-    <row r="604" spans="15:15" ht="13.2">
+    <row r="604" spans="15:15" ht="12.75">
       <c r="O604" s="2"/>
     </row>
-    <row r="605" spans="15:15" ht="13.2">
+    <row r="605" spans="15:15" ht="12.75">
       <c r="O605" s="2"/>
     </row>
-    <row r="606" spans="15:15" ht="13.2">
+    <row r="606" spans="15:15" ht="12.75">
       <c r="O606" s="2"/>
     </row>
-    <row r="607" spans="15:15" ht="13.2">
+    <row r="607" spans="15:15" ht="12.75">
       <c r="O607" s="2"/>
     </row>
-    <row r="608" spans="15:15" ht="13.2">
+    <row r="608" spans="15:15" ht="12.75">
       <c r="O608" s="2"/>
     </row>
-    <row r="609" spans="15:15" ht="13.2">
+    <row r="609" spans="15:15" ht="12.75">
       <c r="O609" s="2"/>
     </row>
-    <row r="610" spans="15:15" ht="13.2">
+    <row r="610" spans="15:15" ht="12.75">
       <c r="O610" s="2"/>
     </row>
-    <row r="611" spans="15:15" ht="13.2">
+    <row r="611" spans="15:15" ht="12.75">
       <c r="O611" s="2"/>
     </row>
-    <row r="612" spans="15:15" ht="13.2">
+    <row r="612" spans="15:15" ht="12.75">
       <c r="O612" s="2"/>
     </row>
-    <row r="613" spans="15:15" ht="13.2">
+    <row r="613" spans="15:15" ht="12.75">
       <c r="O613" s="2"/>
     </row>
-    <row r="614" spans="15:15" ht="13.2">
+    <row r="614" spans="15:15" ht="12.75">
       <c r="O614" s="2"/>
     </row>
-    <row r="615" spans="15:15" ht="13.2">
+    <row r="615" spans="15:15" ht="12.75">
       <c r="O615" s="2"/>
     </row>
-    <row r="616" spans="15:15" ht="13.2">
+    <row r="616" spans="15:15" ht="12.75">
       <c r="O616" s="2"/>
     </row>
-    <row r="617" spans="15:15" ht="13.2">
+    <row r="617" spans="15:15" ht="12.75">
       <c r="O617" s="2"/>
     </row>
-    <row r="618" spans="15:15" ht="13.2">
+    <row r="618" spans="15:15" ht="12.75">
       <c r="O618" s="2"/>
     </row>
-    <row r="619" spans="15:15" ht="13.2">
+    <row r="619" spans="15:15" ht="12.75">
       <c r="O619" s="2"/>
     </row>
-    <row r="620" spans="15:15" ht="13.2">
+    <row r="620" spans="15:15" ht="12.75">
       <c r="O620" s="2"/>
     </row>
-    <row r="621" spans="15:15" ht="13.2">
+    <row r="621" spans="15:15" ht="12.75">
       <c r="O621" s="2"/>
     </row>
-    <row r="622" spans="15:15" ht="13.2">
+    <row r="622" spans="15:15" ht="12.75">
       <c r="O622" s="2"/>
     </row>
-    <row r="623" spans="15:15" ht="13.2">
+    <row r="623" spans="15:15" ht="12.75">
       <c r="O623" s="2"/>
     </row>
-    <row r="624" spans="15:15" ht="13.2">
+    <row r="624" spans="15:15" ht="12.75">
       <c r="O624" s="2"/>
     </row>
-    <row r="625" spans="15:15" ht="13.2">
+    <row r="625" spans="15:15" ht="12.75">
       <c r="O625" s="2"/>
     </row>
-    <row r="626" spans="15:15" ht="13.2">
+    <row r="626" spans="15:15" ht="12.75">
       <c r="O626" s="2"/>
     </row>
-    <row r="627" spans="15:15" ht="13.2">
+    <row r="627" spans="15:15" ht="12.75">
       <c r="O627" s="2"/>
     </row>
-    <row r="628" spans="15:15" ht="13.2">
+    <row r="628" spans="15:15" ht="12.75">
       <c r="O628" s="2"/>
     </row>
-    <row r="629" spans="15:15" ht="13.2">
+    <row r="629" spans="15:15" ht="12.75">
       <c r="O629" s="2"/>
     </row>
-    <row r="630" spans="15:15" ht="13.2">
+    <row r="630" spans="15:15" ht="12.75">
       <c r="O630" s="2"/>
     </row>
-    <row r="631" spans="15:15" ht="13.2">
+    <row r="631" spans="15:15" ht="12.75">
       <c r="O631" s="2"/>
     </row>
-    <row r="632" spans="15:15" ht="13.2">
+    <row r="632" spans="15:15" ht="12.75">
       <c r="O632" s="2"/>
     </row>
-    <row r="633" spans="15:15" ht="13.2">
+    <row r="633" spans="15:15" ht="12.75">
       <c r="O633" s="2"/>
     </row>
-    <row r="634" spans="15:15" ht="13.2">
+    <row r="634" spans="15:15" ht="12.75">
       <c r="O634" s="2"/>
     </row>
-    <row r="635" spans="15:15" ht="13.2">
+    <row r="635" spans="15:15" ht="12.75">
       <c r="O635" s="2"/>
     </row>
-    <row r="636" spans="15:15" ht="13.2">
+    <row r="636" spans="15:15" ht="12.75">
       <c r="O636" s="2"/>
     </row>
-    <row r="637" spans="15:15" ht="13.2">
+    <row r="637" spans="15:15" ht="12.75">
       <c r="O637" s="2"/>
     </row>
-    <row r="638" spans="15:15" ht="13.2">
+    <row r="638" spans="15:15" ht="12.75">
       <c r="O638" s="2"/>
     </row>
-    <row r="639" spans="15:15" ht="13.2">
+    <row r="639" spans="15:15" ht="12.75">
       <c r="O639" s="2"/>
     </row>
-    <row r="640" spans="15:15" ht="13.2">
+    <row r="640" spans="15:15" ht="12.75">
       <c r="O640" s="2"/>
     </row>
-    <row r="641" spans="15:15" ht="13.2">
+    <row r="641" spans="15:15" ht="12.75">
       <c r="O641" s="2"/>
     </row>
-    <row r="642" spans="15:15" ht="13.2">
+    <row r="642" spans="15:15" ht="12.75">
       <c r="O642" s="2"/>
     </row>
-    <row r="643" spans="15:15" ht="13.2">
+    <row r="643" spans="15:15" ht="12.75">
       <c r="O643" s="2"/>
     </row>
-    <row r="644" spans="15:15" ht="13.2">
+    <row r="644" spans="15:15" ht="12.75">
       <c r="O644" s="2"/>
     </row>
-    <row r="645" spans="15:15" ht="13.2">
+    <row r="645" spans="15:15" ht="12.75">
       <c r="O645" s="2"/>
     </row>
-    <row r="646" spans="15:15" ht="13.2">
+    <row r="646" spans="15:15" ht="12.75">
       <c r="O646" s="2"/>
     </row>
-    <row r="647" spans="15:15" ht="13.2">
+    <row r="647" spans="15:15" ht="12.75">
       <c r="O647" s="2"/>
     </row>
-    <row r="648" spans="15:15" ht="13.2">
+    <row r="648" spans="15:15" ht="12.75">
       <c r="O648" s="2"/>
     </row>
-    <row r="649" spans="15:15" ht="13.2">
+    <row r="649" spans="15:15" ht="12.75">
       <c r="O649" s="2"/>
     </row>
-    <row r="650" spans="15:15" ht="13.2">
+    <row r="650" spans="15:15" ht="12.75">
       <c r="O650" s="2"/>
     </row>
-    <row r="651" spans="15:15" ht="13.2">
+    <row r="651" spans="15:15" ht="12.75">
       <c r="O651" s="2"/>
     </row>
-    <row r="652" spans="15:15" ht="13.2">
+    <row r="652" spans="15:15" ht="12.75">
       <c r="O652" s="2"/>
     </row>
-    <row r="653" spans="15:15" ht="13.2">
+    <row r="653" spans="15:15" ht="12.75">
       <c r="O653" s="2"/>
     </row>
-    <row r="654" spans="15:15" ht="13.2">
+    <row r="654" spans="15:15" ht="12.75">
       <c r="O654" s="2"/>
     </row>
-    <row r="655" spans="15:15" ht="13.2">
+    <row r="655" spans="15:15" ht="12.75">
       <c r="O655" s="2"/>
     </row>
-    <row r="656" spans="15:15" ht="13.2">
+    <row r="656" spans="15:15" ht="12.75">
       <c r="O656" s="2"/>
     </row>
-    <row r="657" spans="15:15" ht="13.2">
+    <row r="657" spans="15:15" ht="12.75">
       <c r="O657" s="2"/>
     </row>
-    <row r="658" spans="15:15" ht="13.2">
+    <row r="658" spans="15:15" ht="12.75">
       <c r="O658" s="2"/>
     </row>
-    <row r="659" spans="15:15" ht="13.2">
+    <row r="659" spans="15:15" ht="12.75">
       <c r="O659" s="2"/>
     </row>
-    <row r="660" spans="15:15" ht="13.2">
+    <row r="660" spans="15:15" ht="12.75">
       <c r="O660" s="2"/>
     </row>
-    <row r="661" spans="15:15" ht="13.2">
+    <row r="661" spans="15:15" ht="12.75">
       <c r="O661" s="2"/>
     </row>
-    <row r="662" spans="15:15" ht="13.2">
+    <row r="662" spans="15:15" ht="12.75">
       <c r="O662" s="2"/>
     </row>
-    <row r="663" spans="15:15" ht="13.2">
+    <row r="663" spans="15:15" ht="12.75">
       <c r="O663" s="2"/>
     </row>
-    <row r="664" spans="15:15" ht="13.2">
+    <row r="664" spans="15:15" ht="12.75">
       <c r="O664" s="2"/>
     </row>
-    <row r="665" spans="15:15" ht="13.2">
+    <row r="665" spans="15:15" ht="12.75">
       <c r="O665" s="2"/>
     </row>
-    <row r="666" spans="15:15" ht="13.2">
+    <row r="666" spans="15:15" ht="12.75">
       <c r="O666" s="2"/>
     </row>
-    <row r="667" spans="15:15" ht="13.2">
+    <row r="667" spans="15:15" ht="12.75">
       <c r="O667" s="2"/>
     </row>
-    <row r="668" spans="15:15" ht="13.2">
+    <row r="668" spans="15:15" ht="12.75">
       <c r="O668" s="2"/>
     </row>
-    <row r="669" spans="15:15" ht="13.2">
+    <row r="669" spans="15:15" ht="12.75">
       <c r="O669" s="2"/>
     </row>
-    <row r="670" spans="15:15" ht="13.2">
+    <row r="670" spans="15:15" ht="12.75">
       <c r="O670" s="2"/>
     </row>
-    <row r="671" spans="15:15" ht="13.2">
+    <row r="671" spans="15:15" ht="12.75">
       <c r="O671" s="2"/>
     </row>
-    <row r="672" spans="15:15" ht="13.2">
+    <row r="672" spans="15:15" ht="12.75">
       <c r="O672" s="2"/>
     </row>
-    <row r="673" spans="15:15" ht="13.2">
+    <row r="673" spans="15:15" ht="12.75">
       <c r="O673" s="2"/>
     </row>
-    <row r="674" spans="15:15" ht="13.2">
+    <row r="674" spans="15:15" ht="12.75">
       <c r="O674" s="2"/>
     </row>
-    <row r="675" spans="15:15" ht="13.2">
+    <row r="675" spans="15:15" ht="12.75">
       <c r="O675" s="2"/>
     </row>
-    <row r="676" spans="15:15" ht="13.2">
+    <row r="676" spans="15:15" ht="12.75">
       <c r="O676" s="2"/>
     </row>
-    <row r="677" spans="15:15" ht="13.2">
+    <row r="677" spans="15:15" ht="12.75">
       <c r="O677" s="2"/>
     </row>
-    <row r="678" spans="15:15" ht="13.2">
+    <row r="678" spans="15:15" ht="12.75">
       <c r="O678" s="2"/>
     </row>
-    <row r="679" spans="15:15" ht="13.2">
+    <row r="679" spans="15:15" ht="12.75">
       <c r="O679" s="2"/>
     </row>
-    <row r="680" spans="15:15" ht="13.2">
+    <row r="680" spans="15:15" ht="12.75">
       <c r="O680" s="2"/>
     </row>
-    <row r="681" spans="15:15" ht="13.2">
+    <row r="681" spans="15:15" ht="12.75">
       <c r="O681" s="2"/>
     </row>
-    <row r="682" spans="15:15" ht="13.2">
+    <row r="682" spans="15:15" ht="12.75">
       <c r="O682" s="2"/>
     </row>
-    <row r="683" spans="15:15" ht="13.2">
+    <row r="683" spans="15:15" ht="12.75">
       <c r="O683" s="2"/>
     </row>
-    <row r="684" spans="15:15" ht="13.2">
+    <row r="684" spans="15:15" ht="12.75">
       <c r="O684" s="2"/>
     </row>
-    <row r="685" spans="15:15" ht="13.2">
+    <row r="685" spans="15:15" ht="12.75">
       <c r="O685" s="2"/>
     </row>
-    <row r="686" spans="15:15" ht="13.2">
+    <row r="686" spans="15:15" ht="12.75">
       <c r="O686" s="2"/>
     </row>
-    <row r="687" spans="15:15" ht="13.2">
+    <row r="687" spans="15:15" ht="12.75">
       <c r="O687" s="2"/>
     </row>
-    <row r="688" spans="15:15" ht="13.2">
+    <row r="688" spans="15:15" ht="12.75">
       <c r="O688" s="2"/>
     </row>
-    <row r="689" spans="15:15" ht="13.2">
+    <row r="689" spans="15:15" ht="12.75">
       <c r="O689" s="2"/>
     </row>
-    <row r="690" spans="15:15" ht="13.2">
+    <row r="690" spans="15:15" ht="12.75">
       <c r="O690" s="2"/>
     </row>
-    <row r="691" spans="15:15" ht="13.2">
+    <row r="691" spans="15:15" ht="12.75">
       <c r="O691" s="2"/>
     </row>
-    <row r="692" spans="15:15" ht="13.2">
+    <row r="692" spans="15:15" ht="12.75">
       <c r="O692" s="2"/>
     </row>
-    <row r="693" spans="15:15" ht="13.2">
+    <row r="693" spans="15:15" ht="12.75">
       <c r="O693" s="2"/>
     </row>
-    <row r="694" spans="15:15" ht="13.2">
+    <row r="694" spans="15:15" ht="12.75">
       <c r="O694" s="2"/>
     </row>
-    <row r="695" spans="15:15" ht="13.2">
+    <row r="695" spans="15:15" ht="12.75">
       <c r="O695" s="2"/>
     </row>
-    <row r="696" spans="15:15" ht="13.2">
+    <row r="696" spans="15:15" ht="12.75">
       <c r="O696" s="2"/>
     </row>
-    <row r="697" spans="15:15" ht="13.2">
+    <row r="697" spans="15:15" ht="12.75">
       <c r="O697" s="2"/>
     </row>
-    <row r="698" spans="15:15" ht="13.2">
+    <row r="698" spans="15:15" ht="12.75">
       <c r="O698" s="2"/>
     </row>
-    <row r="699" spans="15:15" ht="13.2">
+    <row r="699" spans="15:15" ht="12.75">
       <c r="O699" s="2"/>
     </row>
-    <row r="700" spans="15:15" ht="13.2">
+    <row r="700" spans="15:15" ht="12.75">
       <c r="O700" s="2"/>
     </row>
-    <row r="701" spans="15:15" ht="13.2">
+    <row r="701" spans="15:15" ht="12.75">
       <c r="O701" s="2"/>
     </row>
-    <row r="702" spans="15:15" ht="13.2">
+    <row r="702" spans="15:15" ht="12.75">
       <c r="O702" s="2"/>
     </row>
-    <row r="703" spans="15:15" ht="13.2">
+    <row r="703" spans="15:15" ht="12.75">
       <c r="O703" s="2"/>
     </row>
-    <row r="704" spans="15:15" ht="13.2">
+    <row r="704" spans="15:15" ht="12.75">
       <c r="O704" s="2"/>
     </row>
-    <row r="705" spans="15:15" ht="13.2">
+    <row r="705" spans="15:15" ht="12.75">
       <c r="O705" s="2"/>
     </row>
-    <row r="706" spans="15:15" ht="13.2">
+    <row r="706" spans="15:15" ht="12.75">
       <c r="O706" s="2"/>
     </row>
-    <row r="707" spans="15:15" ht="13.2">
+    <row r="707" spans="15:15" ht="12.75">
       <c r="O707" s="2"/>
     </row>
-    <row r="708" spans="15:15" ht="13.2">
+    <row r="708" spans="15:15" ht="12.75">
       <c r="O708" s="2"/>
     </row>
-    <row r="709" spans="15:15" ht="13.2">
+    <row r="709" spans="15:15" ht="12.75">
       <c r="O709" s="2"/>
     </row>
-    <row r="710" spans="15:15" ht="13.2">
+    <row r="710" spans="15:15" ht="12.75">
       <c r="O710" s="2"/>
     </row>
-    <row r="711" spans="15:15" ht="13.2">
+    <row r="711" spans="15:15" ht="12.75">
       <c r="O711" s="2"/>
     </row>
-    <row r="712" spans="15:15" ht="13.2">
+    <row r="712" spans="15:15" ht="12.75">
       <c r="O712" s="2"/>
     </row>
-    <row r="713" spans="15:15" ht="13.2">
+    <row r="713" spans="15:15" ht="12.75">
       <c r="O713" s="2"/>
     </row>
-    <row r="714" spans="15:15" ht="13.2">
+    <row r="714" spans="15:15" ht="12.75">
       <c r="O714" s="2"/>
     </row>
-    <row r="715" spans="15:15" ht="13.2">
+    <row r="715" spans="15:15" ht="12.75">
       <c r="O715" s="2"/>
     </row>
-    <row r="716" spans="15:15" ht="13.2">
+    <row r="716" spans="15:15" ht="12.75">
       <c r="O716" s="2"/>
     </row>
-    <row r="717" spans="15:15" ht="13.2">
+    <row r="717" spans="15:15" ht="12.75">
       <c r="O717" s="2"/>
     </row>
-    <row r="718" spans="15:15" ht="13.2">
+    <row r="718" spans="15:15" ht="12.75">
       <c r="O718" s="2"/>
     </row>
-    <row r="719" spans="15:15" ht="13.2">
+    <row r="719" spans="15:15" ht="12.75">
       <c r="O719" s="2"/>
     </row>
-    <row r="720" spans="15:15" ht="13.2">
+    <row r="720" spans="15:15" ht="12.75">
       <c r="O720" s="2"/>
     </row>
-    <row r="721" spans="15:15" ht="13.2">
+    <row r="721" spans="15:15" ht="12.75">
       <c r="O721" s="2"/>
     </row>
-    <row r="722" spans="15:15" ht="13.2">
+    <row r="722" spans="15:15" ht="12.75">
       <c r="O722" s="2"/>
     </row>
-    <row r="723" spans="15:15" ht="13.2">
+    <row r="723" spans="15:15" ht="12.75">
       <c r="O723" s="2"/>
     </row>
-    <row r="724" spans="15:15" ht="13.2">
+    <row r="724" spans="15:15" ht="12.75">
       <c r="O724" s="2"/>
     </row>
-    <row r="725" spans="15:15" ht="13.2">
+    <row r="725" spans="15:15" ht="12.75">
       <c r="O725" s="2"/>
     </row>
-    <row r="726" spans="15:15" ht="13.2">
+    <row r="726" spans="15:15" ht="12.75">
       <c r="O726" s="2"/>
     </row>
-    <row r="727" spans="15:15" ht="13.2">
+    <row r="727" spans="15:15" ht="12.75">
       <c r="O727" s="2"/>
     </row>
-    <row r="728" spans="15:15" ht="13.2">
+    <row r="728" spans="15:15" ht="12.75">
       <c r="O728" s="2"/>
     </row>
-    <row r="729" spans="15:15" ht="13.2">
+    <row r="729" spans="15:15" ht="12.75">
       <c r="O729" s="2"/>
     </row>
-    <row r="730" spans="15:15" ht="13.2">
+    <row r="730" spans="15:15" ht="12.75">
       <c r="O730" s="2"/>
     </row>
-    <row r="731" spans="15:15" ht="13.2">
+    <row r="731" spans="15:15" ht="12.75">
       <c r="O731" s="2"/>
     </row>
-    <row r="732" spans="15:15" ht="13.2">
+    <row r="732" spans="15:15" ht="12.75">
       <c r="O732" s="2"/>
     </row>
-    <row r="733" spans="15:15" ht="13.2">
+    <row r="733" spans="15:15" ht="12.75">
       <c r="O733" s="2"/>
     </row>
-    <row r="734" spans="15:15" ht="13.2">
+    <row r="734" spans="15:15" ht="12.75">
       <c r="O734" s="2"/>
     </row>
-    <row r="735" spans="15:15" ht="13.2">
+    <row r="735" spans="15:15" ht="12.75">
       <c r="O735" s="2"/>
     </row>
-    <row r="736" spans="15:15" ht="13.2">
+    <row r="736" spans="15:15" ht="12.75">
       <c r="O736" s="2"/>
     </row>
-    <row r="737" spans="15:15" ht="13.2">
+    <row r="737" spans="15:15" ht="12.75">
       <c r="O737" s="2"/>
     </row>
-    <row r="738" spans="15:15" ht="13.2">
+    <row r="738" spans="15:15" ht="12.75">
       <c r="O738" s="2"/>
     </row>
-    <row r="739" spans="15:15" ht="13.2">
+    <row r="739" spans="15:15" ht="12.75">
       <c r="O739" s="2"/>
     </row>
-    <row r="740" spans="15:15" ht="13.2">
+    <row r="740" spans="15:15" ht="12.75">
       <c r="O740" s="2"/>
     </row>
-    <row r="741" spans="15:15" ht="13.2">
+    <row r="741" spans="15:15" ht="12.75">
       <c r="O741" s="2"/>
     </row>
-    <row r="742" spans="15:15" ht="13.2">
+    <row r="742" spans="15:15" ht="12.75">
       <c r="O742" s="2"/>
     </row>
-    <row r="743" spans="15:15" ht="13.2">
+    <row r="743" spans="15:15" ht="12.75">
       <c r="O743" s="2"/>
     </row>
-    <row r="744" spans="15:15" ht="13.2">
+    <row r="744" spans="15:15" ht="12.75">
       <c r="O744" s="2"/>
     </row>
-    <row r="745" spans="15:15" ht="13.2">
+    <row r="745" spans="15:15" ht="12.75">
       <c r="O745" s="2"/>
     </row>
-    <row r="746" spans="15:15" ht="13.2">
+    <row r="746" spans="15:15" ht="12.75">
       <c r="O746" s="2"/>
     </row>
-    <row r="747" spans="15:15" ht="13.2">
+    <row r="747" spans="15:15" ht="12.75">
       <c r="O747" s="2"/>
     </row>
-    <row r="748" spans="15:15" ht="13.2">
+    <row r="748" spans="15:15" ht="12.75">
       <c r="O748" s="2"/>
     </row>
-    <row r="749" spans="15:15" ht="13.2">
+    <row r="749" spans="15:15" ht="12.75">
       <c r="O749" s="2"/>
     </row>
-    <row r="750" spans="15:15" ht="13.2">
+    <row r="750" spans="15:15" ht="12.75">
       <c r="O750" s="2"/>
     </row>
-    <row r="751" spans="15:15" ht="13.2">
+    <row r="751" spans="15:15" ht="12.75">
       <c r="O751" s="2"/>
     </row>
-    <row r="752" spans="15:15" ht="13.2">
+    <row r="752" spans="15:15" ht="12.75">
       <c r="O752" s="2"/>
     </row>
-    <row r="753" spans="15:15" ht="13.2">
+    <row r="753" spans="15:15" ht="12.75">
       <c r="O753" s="2"/>
     </row>
-    <row r="754" spans="15:15" ht="13.2">
+    <row r="754" spans="15:15" ht="12.75">
       <c r="O754" s="2"/>
     </row>
-    <row r="755" spans="15:15" ht="13.2">
+    <row r="755" spans="15:15" ht="12.75">
       <c r="O755" s="2"/>
     </row>
-    <row r="756" spans="15:15" ht="13.2">
+    <row r="756" spans="15:15" ht="12.75">
       <c r="O756" s="2"/>
     </row>
-    <row r="757" spans="15:15" ht="13.2">
+    <row r="757" spans="15:15" ht="12.75">
       <c r="O757" s="2"/>
     </row>
-    <row r="758" spans="15:15" ht="13.2">
+    <row r="758" spans="15:15" ht="12.75">
       <c r="O758" s="2"/>
     </row>
-    <row r="759" spans="15:15" ht="13.2">
+    <row r="759" spans="15:15" ht="12.75">
       <c r="O759" s="2"/>
     </row>
-    <row r="760" spans="15:15" ht="13.2">
+    <row r="760" spans="15:15" ht="12.75">
       <c r="O760" s="2"/>
     </row>
-    <row r="761" spans="15:15" ht="13.2">
+    <row r="761" spans="15:15" ht="12.75">
       <c r="O761" s="2"/>
     </row>
-    <row r="762" spans="15:15" ht="13.2">
+    <row r="762" spans="15:15" ht="12.75">
       <c r="O762" s="2"/>
     </row>
-    <row r="763" spans="15:15" ht="13.2">
+    <row r="763" spans="15:15" ht="12.75">
       <c r="O763" s="2"/>
     </row>
-    <row r="764" spans="15:15" ht="13.2">
+    <row r="764" spans="15:15" ht="12.75">
       <c r="O764" s="2"/>
     </row>
-    <row r="765" spans="15:15" ht="13.2">
+    <row r="765" spans="15:15" ht="12.75">
       <c r="O765" s="2"/>
     </row>
-    <row r="766" spans="15:15" ht="13.2">
+    <row r="766" spans="15:15" ht="12.75">
       <c r="O766" s="2"/>
     </row>
-    <row r="767" spans="15:15" ht="13.2">
+    <row r="767" spans="15:15" ht="12.75">
       <c r="O767" s="2"/>
     </row>
-    <row r="768" spans="15:15" ht="13.2">
+    <row r="768" spans="15:15" ht="12.75">
       <c r="O768" s="2"/>
     </row>
-    <row r="769" spans="15:15" ht="13.2">
+    <row r="769" spans="15:15" ht="12.75">
       <c r="O769" s="2"/>
     </row>
-    <row r="770" spans="15:15" ht="13.2">
+    <row r="770" spans="15:15" ht="12.75">
       <c r="O770" s="2"/>
     </row>
-    <row r="771" spans="15:15" ht="13.2">
+    <row r="771" spans="15:15" ht="12.75">
       <c r="O771" s="2"/>
     </row>
-    <row r="772" spans="15:15" ht="13.2">
+    <row r="772" spans="15:15" ht="12.75">
       <c r="O772" s="2"/>
     </row>
-    <row r="773" spans="15:15" ht="13.2">
+    <row r="773" spans="15:15" ht="12.75">
       <c r="O773" s="2"/>
     </row>
-    <row r="774" spans="15:15" ht="13.2">
+    <row r="774" spans="15:15" ht="12.75">
       <c r="O774" s="2"/>
     </row>
-    <row r="775" spans="15:15" ht="13.2">
+    <row r="775" spans="15:15" ht="12.75">
       <c r="O775" s="2"/>
     </row>
-    <row r="776" spans="15:15" ht="13.2">
+    <row r="776" spans="15:15" ht="12.75">
       <c r="O776" s="2"/>
     </row>
-    <row r="777" spans="15:15" ht="13.2">
+    <row r="777" spans="15:15" ht="12.75">
       <c r="O777" s="2"/>
     </row>
-    <row r="778" spans="15:15" ht="13.2">
+    <row r="778" spans="15:15" ht="12.75">
       <c r="O778" s="2"/>
     </row>
-    <row r="779" spans="15:15" ht="13.2">
+    <row r="779" spans="15:15" ht="12.75">
       <c r="O779" s="2"/>
     </row>
-    <row r="780" spans="15:15" ht="13.2">
+    <row r="780" spans="15:15" ht="12.75">
       <c r="O780" s="2"/>
     </row>
-    <row r="781" spans="15:15" ht="13.2">
+    <row r="781" spans="15:15" ht="12.75">
       <c r="O781" s="2"/>
     </row>
-    <row r="782" spans="15:15" ht="13.2">
+    <row r="782" spans="15:15" ht="12.75">
       <c r="O782" s="2"/>
     </row>
-    <row r="783" spans="15:15" ht="13.2">
+    <row r="783" spans="15:15" ht="12.75">
       <c r="O783" s="2"/>
     </row>
-    <row r="784" spans="15:15" ht="13.2">
+    <row r="784" spans="15:15" ht="12.75">
       <c r="O784" s="2"/>
     </row>
-    <row r="785" spans="15:15" ht="13.2">
+    <row r="785" spans="15:15" ht="12.75">
       <c r="O785" s="2"/>
     </row>
-    <row r="786" spans="15:15" ht="13.2">
+    <row r="786" spans="15:15" ht="12.75">
       <c r="O786" s="2"/>
     </row>
-    <row r="787" spans="15:15" ht="13.2">
+    <row r="787" spans="15:15" ht="12.75">
       <c r="O787" s="2"/>
     </row>
-    <row r="788" spans="15:15" ht="13.2">
+    <row r="788" spans="15:15" ht="12.75">
       <c r="O788" s="2"/>
     </row>
-    <row r="789" spans="15:15" ht="13.2">
+    <row r="789" spans="15:15" ht="12.75">
       <c r="O789" s="2"/>
     </row>
-    <row r="790" spans="15:15" ht="13.2">
+    <row r="790" spans="15:15" ht="12.75">
       <c r="O790" s="2"/>
     </row>
-    <row r="791" spans="15:15" ht="13.2">
+    <row r="791" spans="15:15" ht="12.75">
       <c r="O791" s="2"/>
     </row>
-    <row r="792" spans="15:15" ht="13.2">
+    <row r="792" spans="15:15" ht="12.75">
       <c r="O792" s="2"/>
     </row>
-    <row r="793" spans="15:15" ht="13.2">
+    <row r="793" spans="15:15" ht="12.75">
       <c r="O793" s="2"/>
     </row>
-    <row r="794" spans="15:15" ht="13.2">
+    <row r="794" spans="15:15" ht="12.75">
       <c r="O794" s="2"/>
     </row>
-    <row r="795" spans="15:15" ht="13.2">
+    <row r="795" spans="15:15" ht="12.75">
       <c r="O795" s="2"/>
     </row>
-    <row r="796" spans="15:15" ht="13.2">
+    <row r="796" spans="15:15" ht="12.75">
       <c r="O796" s="2"/>
     </row>
-    <row r="797" spans="15:15" ht="13.2">
+    <row r="797" spans="15:15" ht="12.75">
       <c r="O797" s="2"/>
     </row>
-    <row r="798" spans="15:15" ht="13.2">
+    <row r="798" spans="15:15" ht="12.75">
       <c r="O798" s="2"/>
     </row>
-    <row r="799" spans="15:15" ht="13.2">
+    <row r="799" spans="15:15" ht="12.75">
       <c r="O799" s="2"/>
     </row>
-    <row r="800" spans="15:15" ht="13.2">
+    <row r="800" spans="15:15" ht="12.75">
       <c r="O800" s="2"/>
     </row>
-    <row r="801" spans="15:15" ht="13.2">
+    <row r="801" spans="15:15" ht="12.75">
       <c r="O801" s="2"/>
     </row>
-    <row r="802" spans="15:15" ht="13.2">
+    <row r="802" spans="15:15" ht="12.75">
       <c r="O802" s="2"/>
     </row>
-    <row r="803" spans="15:15" ht="13.2">
+    <row r="803" spans="15:15" ht="12.75">
       <c r="O803" s="2"/>
     </row>
-    <row r="804" spans="15:15" ht="13.2">
+    <row r="804" spans="15:15" ht="12.75">
       <c r="O804" s="2"/>
     </row>
-    <row r="805" spans="15:15" ht="13.2">
+    <row r="805" spans="15:15" ht="12.75">
       <c r="O805" s="2"/>
     </row>
-    <row r="806" spans="15:15" ht="13.2">
+    <row r="806" spans="15:15" ht="12.75">
       <c r="O806" s="2"/>
     </row>
-    <row r="807" spans="15:15" ht="13.2">
+    <row r="807" spans="15:15" ht="12.75">
       <c r="O807" s="2"/>
     </row>
-    <row r="808" spans="15:15" ht="13.2">
+    <row r="808" spans="15:15" ht="12.75">
       <c r="O808" s="2"/>
     </row>
-    <row r="809" spans="15:15" ht="13.2">
+    <row r="809" spans="15:15" ht="12.75">
       <c r="O809" s="2"/>
     </row>
-    <row r="810" spans="15:15" ht="13.2">
+    <row r="810" spans="15:15" ht="12.75">
       <c r="O810" s="2"/>
     </row>
-    <row r="811" spans="15:15" ht="13.2">
+    <row r="811" spans="15:15" ht="12.75">
       <c r="O811" s="2"/>
     </row>
-    <row r="812" spans="15:15" ht="13.2">
+    <row r="812" spans="15:15" ht="12.75">
       <c r="O812" s="2"/>
     </row>
-    <row r="813" spans="15:15" ht="13.2">
+    <row r="813" spans="15:15" ht="12.75">
       <c r="O813" s="2"/>
     </row>
-    <row r="814" spans="15:15" ht="13.2">
+    <row r="814" spans="15:15" ht="12.75">
       <c r="O814" s="2"/>
     </row>
-    <row r="815" spans="15:15" ht="13.2">
+    <row r="815" spans="15:15" ht="12.75">
       <c r="O815" s="2"/>
     </row>
-    <row r="816" spans="15:15" ht="13.2">
+    <row r="816" spans="15:15" ht="12.75">
       <c r="O816" s="2"/>
     </row>
-    <row r="817" spans="15:15" ht="13.2">
+    <row r="817" spans="15:15" ht="12.75">
       <c r="O817" s="2"/>
     </row>
-    <row r="818" spans="15:15" ht="13.2">
+    <row r="818" spans="15:15" ht="12.75">
       <c r="O818" s="2"/>
     </row>
-    <row r="819" spans="15:15" ht="13.2">
+    <row r="819" spans="15:15" ht="12.75">
       <c r="O819" s="2"/>
     </row>
-    <row r="820" spans="15:15" ht="13.2">
+    <row r="820" spans="15:15" ht="12.75">
       <c r="O820" s="2"/>
     </row>
-    <row r="821" spans="15:15" ht="13.2">
+    <row r="821" spans="15:15" ht="12.75">
       <c r="O821" s="2"/>
     </row>
-    <row r="822" spans="15:15" ht="13.2">
+    <row r="822" spans="15:15" ht="12.75">
       <c r="O822" s="2"/>
     </row>
-    <row r="823" spans="15:15" ht="13.2">
+    <row r="823" spans="15:15" ht="12.75">
       <c r="O823" s="2"/>
     </row>
-    <row r="824" spans="15:15" ht="13.2">
+    <row r="824" spans="15:15" ht="12.75">
       <c r="O824" s="2"/>
     </row>
-    <row r="825" spans="15:15" ht="13.2">
+    <row r="825" spans="15:15" ht="12.75">
       <c r="O825" s="2"/>
     </row>
-    <row r="826" spans="15:15" ht="13.2">
+    <row r="826" spans="15:15" ht="12.75">
       <c r="O826" s="2"/>
     </row>
-    <row r="827" spans="15:15" ht="13.2">
+    <row r="827" spans="15:15" ht="12.75">
       <c r="O827" s="2"/>
     </row>
-    <row r="828" spans="15:15" ht="13.2">
+    <row r="828" spans="15:15" ht="12.75">
       <c r="O828" s="2"/>
     </row>
-    <row r="829" spans="15:15" ht="13.2">
+    <row r="829" spans="15:15" ht="12.75">
       <c r="O829" s="2"/>
     </row>
-    <row r="830" spans="15:15" ht="13.2">
+    <row r="830" spans="15:15" ht="12.75">
       <c r="O830" s="2"/>
     </row>
-    <row r="831" spans="15:15" ht="13.2">
+    <row r="831" spans="15:15" ht="12.75">
       <c r="O831" s="2"/>
     </row>
-    <row r="832" spans="15:15" ht="13.2">
+    <row r="832" spans="15:15" ht="12.75">
       <c r="O832" s="2"/>
     </row>
-    <row r="833" spans="15:15" ht="13.2">
+    <row r="833" spans="15:15" ht="12.75">
       <c r="O833" s="2"/>
     </row>
-    <row r="834" spans="15:15" ht="13.2">
+    <row r="834" spans="15:15" ht="12.75">
       <c r="O834" s="2"/>
     </row>
-    <row r="835" spans="15:15" ht="13.2">
+    <row r="835" spans="15:15" ht="12.75">
       <c r="O835" s="2"/>
     </row>
-    <row r="836" spans="15:15" ht="13.2">
+    <row r="836" spans="15:15" ht="12.75">
       <c r="O836" s="2"/>
     </row>
-    <row r="837" spans="15:15" ht="13.2">
+    <row r="837" spans="15:15" ht="12.75">
       <c r="O837" s="2"/>
     </row>
-    <row r="838" spans="15:15" ht="13.2">
+    <row r="838" spans="15:15" ht="12.75">
       <c r="O838" s="2"/>
     </row>
-    <row r="839" spans="15:15" ht="13.2">
+    <row r="839" spans="15:15" ht="12.75">
       <c r="O839" s="2"/>
     </row>
-    <row r="840" spans="15:15" ht="13.2">
+    <row r="840" spans="15:15" ht="12.75">
       <c r="O840" s="2"/>
     </row>
-    <row r="841" spans="15:15" ht="13.2">
+    <row r="841" spans="15:15" ht="12.75">
       <c r="O841" s="2"/>
     </row>
-    <row r="842" spans="15:15" ht="13.2">
+    <row r="842" spans="15:15" ht="12.75">
       <c r="O842" s="2"/>
     </row>
-    <row r="843" spans="15:15" ht="13.2">
+    <row r="843" spans="15:15" ht="12.75">
       <c r="O843" s="2"/>
     </row>
-    <row r="844" spans="15:15" ht="13.2">
+    <row r="844" spans="15:15" ht="12.75">
       <c r="O844" s="2"/>
     </row>
-    <row r="845" spans="15:15" ht="13.2">
+    <row r="845" spans="15:15" ht="12.75">
       <c r="O845" s="2"/>
     </row>
-    <row r="846" spans="15:15" ht="13.2">
+    <row r="846" spans="15:15" ht="12.75">
       <c r="O846" s="2"/>
     </row>
-    <row r="847" spans="15:15" ht="13.2">
+    <row r="847" spans="15:15" ht="12.75">
       <c r="O847" s="2"/>
     </row>
-    <row r="848" spans="15:15" ht="13.2">
+    <row r="848" spans="15:15" ht="12.75">
       <c r="O848" s="2"/>
     </row>
-    <row r="849" spans="15:15" ht="13.2">
+    <row r="849" spans="15:15" ht="12.75">
       <c r="O849" s="2"/>
     </row>
-    <row r="850" spans="15:15" ht="13.2">
+    <row r="850" spans="15:15" ht="12.75">
       <c r="O850" s="2"/>
     </row>
-    <row r="851" spans="15:15" ht="13.2">
+    <row r="851" spans="15:15" ht="12.75">
       <c r="O851" s="2"/>
     </row>
-    <row r="852" spans="15:15" ht="13.2">
+    <row r="852" spans="15:15" ht="12.75">
       <c r="O852" s="2"/>
     </row>
-    <row r="853" spans="15:15" ht="13.2">
+    <row r="853" spans="15:15" ht="12.75">
       <c r="O853" s="2"/>
     </row>
-    <row r="854" spans="15:15" ht="13.2">
+    <row r="854" spans="15:15" ht="12.75">
       <c r="O854" s="2"/>
     </row>
-    <row r="855" spans="15:15" ht="13.2">
+    <row r="855" spans="15:15" ht="12.75">
       <c r="O855" s="2"/>
     </row>
-    <row r="856" spans="15:15" ht="13.2">
+    <row r="856" spans="15:15" ht="12.75">
       <c r="O856" s="2"/>
     </row>
-    <row r="857" spans="15:15" ht="13.2">
+    <row r="857" spans="15:15" ht="12.75">
       <c r="O857" s="2"/>
     </row>
-    <row r="858" spans="15:15" ht="13.2">
+    <row r="858" spans="15:15" ht="12.75">
       <c r="O858" s="2"/>
     </row>
-    <row r="859" spans="15:15" ht="13.2">
+    <row r="859" spans="15:15" ht="12.75">
       <c r="O859" s="2"/>
     </row>
-    <row r="860" spans="15:15" ht="13.2">
+    <row r="860" spans="15:15" ht="12.75">
       <c r="O860" s="2"/>
     </row>
-    <row r="861" spans="15:15" ht="13.2">
+    <row r="861" spans="15:15" ht="12.75">
       <c r="O861" s="2"/>
     </row>
-    <row r="862" spans="15:15" ht="13.2">
+    <row r="862" spans="15:15" ht="12.75">
       <c r="O862" s="2"/>
     </row>
-    <row r="863" spans="15:15" ht="13.2">
+    <row r="863" spans="15:15" ht="12.75">
       <c r="O863" s="2"/>
     </row>
-    <row r="864" spans="15:15" ht="13.2">
+    <row r="864" spans="15:15" ht="12.75">
       <c r="O864" s="2"/>
     </row>
-    <row r="865" spans="15:15" ht="13.2">
+    <row r="865" spans="15:15" ht="12.75">
       <c r="O865" s="2"/>
     </row>
-    <row r="866" spans="15:15" ht="13.2">
+    <row r="866" spans="15:15" ht="12.75">
       <c r="O866" s="2"/>
     </row>
-    <row r="867" spans="15:15" ht="13.2">
+    <row r="867" spans="15:15" ht="12.75">
       <c r="O867" s="2"/>
     </row>
-    <row r="868" spans="15:15" ht="13.2">
+    <row r="868" spans="15:15" ht="12.75">
       <c r="O868" s="2"/>
     </row>
-    <row r="869" spans="15:15" ht="13.2">
+    <row r="869" spans="15:15" ht="12.75">
       <c r="O869" s="2"/>
     </row>
-    <row r="870" spans="15:15" ht="13.2">
+    <row r="870" spans="15:15" ht="12.75">
       <c r="O870" s="2"/>
     </row>
-    <row r="871" spans="15:15" ht="13.2">
+    <row r="871" spans="15:15" ht="12.75">
       <c r="O871" s="2"/>
     </row>
-    <row r="872" spans="15:15" ht="13.2">
+    <row r="872" spans="15:15" ht="12.75">
       <c r="O872" s="2"/>
     </row>
-    <row r="873" spans="15:15" ht="13.2">
+    <row r="873" spans="15:15" ht="12.75">
       <c r="O873" s="2"/>
     </row>
-    <row r="874" spans="15:15" ht="13.2">
+    <row r="874" spans="15:15" ht="12.75">
       <c r="O874" s="2"/>
     </row>
-    <row r="875" spans="15:15" ht="13.2">
+    <row r="875" spans="15:15" ht="12.75">
       <c r="O875" s="2"/>
     </row>
-    <row r="876" spans="15:15" ht="13.2">
+    <row r="876" spans="15:15" ht="12.75">
       <c r="O876" s="2"/>
     </row>
-    <row r="877" spans="15:15" ht="13.2">
+    <row r="877" spans="15:15" ht="12.75">
       <c r="O877" s="2"/>
     </row>
-    <row r="878" spans="15:15" ht="13.2">
+    <row r="878" spans="15:15" ht="12.75">
       <c r="O878" s="2"/>
     </row>
-    <row r="879" spans="15:15" ht="13.2">
+    <row r="879" spans="15:15" ht="12.75">
       <c r="O879" s="2"/>
     </row>
-    <row r="880" spans="15:15" ht="13.2">
+    <row r="880" spans="15:15" ht="12.75">
       <c r="O880" s="2"/>
     </row>
-    <row r="881" spans="15:15" ht="13.2">
+    <row r="881" spans="15:15" ht="12.75">
       <c r="O881" s="2"/>
     </row>
-    <row r="882" spans="15:15" ht="13.2">
+    <row r="882" spans="15:15" ht="12.75">
       <c r="O882" s="2"/>
     </row>
-    <row r="883" spans="15:15" ht="13.2">
+    <row r="883" spans="15:15" ht="12.75">
       <c r="O883" s="2"/>
     </row>
-    <row r="884" spans="15:15" ht="13.2">
+    <row r="884" spans="15:15" ht="12.75">
       <c r="O884" s="2"/>
     </row>
-    <row r="885" spans="15:15" ht="13.2">
+    <row r="885" spans="15:15" ht="12.75">
       <c r="O885" s="2"/>
     </row>
-    <row r="886" spans="15:15" ht="13.2">
+    <row r="886" spans="15:15" ht="12.75">
       <c r="O886" s="2"/>
     </row>
-    <row r="887" spans="15:15" ht="13.2">
+    <row r="887" spans="15:15" ht="12.75">
       <c r="O887" s="2"/>
     </row>
-    <row r="888" spans="15:15" ht="13.2">
+    <row r="888" spans="15:15" ht="12.75">
       <c r="O888" s="2"/>
     </row>
-    <row r="889" spans="15:15" ht="13.2">
+    <row r="889" spans="15:15" ht="12.75">
       <c r="O889" s="2"/>
     </row>
-    <row r="890" spans="15:15" ht="13.2">
+    <row r="890" spans="15:15" ht="12.75">
       <c r="O890" s="2"/>
     </row>
-    <row r="891" spans="15:15" ht="13.2">
+    <row r="891" spans="15:15" ht="12.75">
       <c r="O891" s="2"/>
     </row>
-    <row r="892" spans="15:15" ht="13.2">
+    <row r="892" spans="15:15" ht="12.75">
       <c r="O892" s="2"/>
     </row>
-    <row r="893" spans="15:15" ht="13.2">
+    <row r="893" spans="15:15" ht="12.75">
       <c r="O893" s="2"/>
     </row>
-    <row r="894" spans="15:15" ht="13.2">
+    <row r="894" spans="15:15" ht="12.75">
       <c r="O894" s="2"/>
     </row>
-    <row r="895" spans="15:15" ht="13.2">
+    <row r="895" spans="15:15" ht="12.75">
       <c r="O895" s="2"/>
     </row>
-    <row r="896" spans="15:15" ht="13.2">
+    <row r="896" spans="15:15" ht="12.75">
       <c r="O896" s="2"/>
     </row>
-    <row r="897" spans="15:15" ht="13.2">
+    <row r="897" spans="15:15" ht="12.75">
       <c r="O897" s="2"/>
     </row>
-    <row r="898" spans="15:15" ht="13.2">
+    <row r="898" spans="15:15" ht="12.75">
       <c r="O898" s="2"/>
     </row>
-    <row r="899" spans="15:15" ht="13.2">
+    <row r="899" spans="15:15" ht="12.75">
       <c r="O899" s="2"/>
     </row>
-    <row r="900" spans="15:15" ht="13.2">
+    <row r="900" spans="15:15" ht="12.75">
       <c r="O900" s="2"/>
     </row>
-    <row r="901" spans="15:15" ht="13.2">
+    <row r="901" spans="15:15" ht="12.75">
       <c r="O901" s="2"/>
     </row>
-    <row r="902" spans="15:15" ht="13.2">
+    <row r="902" spans="15:15" ht="12.75">
       <c r="O902" s="2"/>
     </row>
-    <row r="903" spans="15:15" ht="13.2">
+    <row r="903" spans="15:15" ht="12.75">
       <c r="O903" s="2"/>
     </row>
-    <row r="904" spans="15:15" ht="13.2">
+    <row r="904" spans="15:15" ht="12.75">
       <c r="O904" s="2"/>
     </row>
-    <row r="905" spans="15:15" ht="13.2">
+    <row r="905" spans="15:15" ht="12.75">
       <c r="O905" s="2"/>
     </row>
-    <row r="906" spans="15:15" ht="13.2">
+    <row r="906" spans="15:15" ht="12.75">
       <c r="O906" s="2"/>
     </row>
-    <row r="907" spans="15:15" ht="13.2">
+    <row r="907" spans="15:15" ht="12.75">
       <c r="O907" s="2"/>
     </row>
-    <row r="908" spans="15:15" ht="13.2">
+    <row r="908" spans="15:15" ht="12.75">
       <c r="O908" s="2"/>
     </row>
-    <row r="909" spans="15:15" ht="13.2">
+    <row r="909" spans="15:15" ht="12.75">
       <c r="O909" s="2"/>
     </row>
-    <row r="910" spans="15:15" ht="13.2">
+    <row r="910" spans="15:15" ht="12.75">
       <c r="O910" s="2"/>
     </row>
-    <row r="911" spans="15:15" ht="13.2">
+    <row r="911" spans="15:15" ht="12.75">
       <c r="O911" s="2"/>
     </row>
-    <row r="912" spans="15:15" ht="13.2">
+    <row r="912" spans="15:15" ht="12.75">
       <c r="O912" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
       <formula>"New"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+  <conditionalFormatting sqref="O1:O9 O11:O1048576">
+    <cfRule type="cellIs" dxfId="33" priority="34" operator="equal">
       <formula>"New"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="33" operator="equal">
+      <formula>"Opened"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+      <formula>"Fixed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
+      <formula>"Retest"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="30" operator="equal">
+      <formula>"Reopened"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>"Closed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="28" operator="equal">
+      <formula>"Approved"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+      <formula>"Rejected"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:C10 E10">
+    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
+      <formula>"valid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
+      <formula>"invalid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
+      <formula>"blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
+      <formula>"not executed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+      <formula>"passed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
+      <formula>"failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:G10">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
+      <formula>"valid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
+      <formula>"invalid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
+      <formula>"blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+      <formula>"not executed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
+      <formula>"passed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+      <formula>"failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+      <formula>"valid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+      <formula>"invalid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+      <formula>"blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+      <formula>"not executed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
+      <formula>"passed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+      <formula>"failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O10">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Rejected"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Approved"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Closed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Reopened"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Retest"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Fixed"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"Opened"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"Fixed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Retest"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Reopened"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Closed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"Approved"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Rejected"</formula>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"New"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576" xr:uid="{F8B02710-B98F-493D-A38F-7AABD420EB42}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576">
       <formula1>"New,Opened,Fixed,Retest,Reopened,Closed,Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
